--- a/ASML.xlsx
+++ b/ASML.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD28C1F5-EA68-426C-BA0C-AE5433C907C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCFF263-3C55-44A1-BDD8-7525192DA638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{40E26FA9-FA23-47D9-8A0D-17BDAE3930EB}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{40E26FA9-FA23-47D9-8A0D-17BDAE3930EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="55">
   <si>
     <t>numbers in mio EUR</t>
   </si>
@@ -200,6 +200,9 @@
   <si>
     <t>n.a.</t>
   </si>
+  <si>
+    <t>FY25</t>
+  </si>
 </sst>
 </file>
 
@@ -210,13 +213,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -280,25 +289,28 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -719,11 +731,11 @@
       <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="3">
-        <v>388.2</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>42</v>
+      <c r="H3" s="7">
+        <v>388.5</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -741,7 +753,7 @@
       </c>
       <c r="H4" s="3">
         <f>+H2*H3</f>
-        <v>255862.62</v>
+        <v>256060.35</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -752,11 +764,11 @@
         <v>5</v>
       </c>
       <c r="H5" s="3">
-        <f>9098.4+5.2</f>
-        <v>9103.6</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>42</v>
+        <f>12916+405.9</f>
+        <v>13321.9</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -764,10 +776,11 @@
         <v>6</v>
       </c>
       <c r="H6" s="3">
-        <v>3681</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>42</v>
+        <f>1681.9+2709</f>
+        <v>4390.8999999999996</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -776,7 +789,7 @@
       </c>
       <c r="H7" s="3">
         <f>+H4-H5+H6</f>
-        <v>250440.02</v>
+        <v>247129.35</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -861,6 +874,9 @@
       <c r="U2" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="V2" s="13" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -892,7 +908,9 @@
       <c r="L3" s="7">
         <v>5596.1</v>
       </c>
-      <c r="M3" s="7"/>
+      <c r="M3" s="7">
+        <v>5553.8</v>
+      </c>
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
@@ -907,7 +925,9 @@
       <c r="U3" s="7">
         <v>21768.7</v>
       </c>
-      <c r="V3" s="7"/>
+      <c r="V3" s="7">
+        <v>24474.3</v>
+      </c>
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
@@ -958,7 +978,9 @@
       <c r="L4" s="7">
         <v>2095.6</v>
       </c>
-      <c r="M4" s="7"/>
+      <c r="M4" s="7">
+        <v>1962.2</v>
+      </c>
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
@@ -973,7 +995,9 @@
       <c r="U4" s="7">
         <v>6494.2</v>
       </c>
-      <c r="V4" s="7"/>
+      <c r="V4" s="7">
+        <v>8193</v>
+      </c>
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
@@ -1040,7 +1064,7 @@
       </c>
       <c r="M5" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7516</v>
       </c>
       <c r="N5" s="8">
         <f t="shared" si="1"/>
@@ -1071,7 +1095,10 @@
         <f>+U3+U4</f>
         <v>28262.9</v>
       </c>
-      <c r="V5" s="7"/>
+      <c r="V5" s="8">
+        <f>+V3+V4</f>
+        <v>32667.3</v>
+      </c>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
@@ -1122,7 +1149,9 @@
       <c r="L6" s="7">
         <v>3562.2</v>
       </c>
-      <c r="M6" s="7"/>
+      <c r="M6" s="7">
+        <v>3635.7</v>
+      </c>
       <c r="N6" s="7"/>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
@@ -1137,7 +1166,9 @@
       <c r="U6" s="7">
         <v>10406.9</v>
       </c>
-      <c r="V6" s="7"/>
+      <c r="V6" s="7">
+        <v>11384</v>
+      </c>
       <c r="W6" s="7"/>
       <c r="X6" s="7"/>
       <c r="Y6" s="7"/>
@@ -1211,7 +1242,9 @@
       <c r="U7" s="7">
         <v>3364</v>
       </c>
-      <c r="V7" s="7"/>
+      <c r="V7" s="7">
+        <v>4025.3</v>
+      </c>
       <c r="W7" s="7"/>
       <c r="X7" s="7"/>
       <c r="Y7" s="7"/>
@@ -1278,7 +1311,7 @@
       </c>
       <c r="M8" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3880.3</v>
       </c>
       <c r="N8" s="7">
         <f t="shared" si="3"/>
@@ -1309,7 +1342,10 @@
         <f>+U5-SUM(U6:U7)</f>
         <v>14492.000000000002</v>
       </c>
-      <c r="V8" s="7"/>
+      <c r="V8" s="7">
+        <f>+V5-SUM(V6:V7)</f>
+        <v>17258</v>
+      </c>
       <c r="W8" s="7"/>
       <c r="X8" s="7"/>
       <c r="Y8" s="7"/>
@@ -1360,7 +1396,9 @@
       <c r="L9" s="7">
         <v>1166.7</v>
       </c>
-      <c r="M9" s="7"/>
+      <c r="M9" s="7">
+        <v>1108.7</v>
+      </c>
       <c r="N9" s="7"/>
       <c r="O9" s="7"/>
       <c r="P9" s="7"/>
@@ -1375,7 +1413,9 @@
       <c r="U9" s="7">
         <v>4303.7</v>
       </c>
-      <c r="V9" s="7"/>
+      <c r="V9" s="7">
+        <v>4698.8</v>
+      </c>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
       <c r="Y9" s="7"/>
@@ -1426,7 +1466,9 @@
       <c r="L10" s="7">
         <v>298.7</v>
       </c>
-      <c r="M10" s="7"/>
+      <c r="M10" s="7">
+        <v>303.2</v>
+      </c>
       <c r="N10" s="7"/>
       <c r="O10" s="7"/>
       <c r="P10" s="7"/>
@@ -1441,7 +1483,9 @@
       <c r="U10" s="7">
         <v>1165.7</v>
       </c>
-      <c r="V10" s="7"/>
+      <c r="V10" s="7">
+        <v>1257.8</v>
+      </c>
       <c r="W10" s="7"/>
       <c r="X10" s="7"/>
       <c r="Y10" s="7"/>
@@ -1475,7 +1519,7 @@
         <v>1834.5999999999995</v>
       </c>
       <c r="E11" s="7">
-        <f t="shared" ref="E11:U11" si="5">+E8-SUM(E9:E10)</f>
+        <f t="shared" ref="E11:V11" si="5">+E8-SUM(E9:E10)</f>
         <v>2391.9</v>
       </c>
       <c r="F11" s="7">
@@ -1508,7 +1552,7 @@
       </c>
       <c r="M11" s="7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2468.4</v>
       </c>
       <c r="N11" s="7">
         <f t="shared" si="5"/>
@@ -1539,7 +1583,10 @@
         <f t="shared" si="5"/>
         <v>9022.6000000000022</v>
       </c>
-      <c r="V11" s="7"/>
+      <c r="V11" s="7">
+        <f t="shared" si="5"/>
+        <v>11301.4</v>
+      </c>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
       <c r="Y11" s="7"/>
@@ -1590,7 +1637,9 @@
       <c r="L12" s="7">
         <v>24.8</v>
       </c>
-      <c r="M12" s="7"/>
+      <c r="M12" s="7">
+        <v>19.399999999999999</v>
+      </c>
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
@@ -1605,7 +1654,9 @@
       <c r="U12" s="7">
         <v>19.8</v>
       </c>
-      <c r="V12" s="7"/>
+      <c r="V12" s="7">
+        <v>104.7</v>
+      </c>
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
       <c r="Y12" s="7"/>
@@ -1639,7 +1690,7 @@
         <v>1822.6999999999994</v>
       </c>
       <c r="E13" s="7">
-        <f t="shared" ref="E13:U13" si="7">+E11+E12</f>
+        <f t="shared" ref="E13:V13" si="7">+E11+E12</f>
         <v>2397.1</v>
       </c>
       <c r="F13" s="7">
@@ -1672,7 +1723,7 @@
       </c>
       <c r="M13" s="7">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2487.8000000000002</v>
       </c>
       <c r="N13" s="7">
         <f t="shared" si="7"/>
@@ -1703,7 +1754,10 @@
         <f t="shared" si="7"/>
         <v>9042.4000000000015</v>
       </c>
-      <c r="V13" s="7"/>
+      <c r="V13" s="7">
+        <f t="shared" si="7"/>
+        <v>11406.1</v>
+      </c>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
@@ -1754,7 +1808,9 @@
       <c r="L14" s="7">
         <v>487.4</v>
       </c>
-      <c r="M14" s="7"/>
+      <c r="M14" s="7">
+        <v>442.2</v>
+      </c>
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
@@ -1769,7 +1825,9 @@
       <c r="U14" s="7">
         <v>1680.6</v>
       </c>
-      <c r="V14" s="7"/>
+      <c r="V14" s="7">
+        <v>2013.4</v>
+      </c>
       <c r="W14" s="7"/>
       <c r="X14" s="7"/>
       <c r="Y14" s="7"/>
@@ -1819,7 +1877,7 @@
         <v>1875.7999999999997</v>
       </c>
       <c r="I15" s="7">
-        <f t="shared" ref="I15:U15" si="9">+I13-I14</f>
+        <f t="shared" ref="I15:V15" si="9">+I13-I14</f>
         <v>1845.7999999999995</v>
       </c>
       <c r="J15" s="7">
@@ -1836,7 +1894,7 @@
       </c>
       <c r="M15" s="7">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2045.6000000000001</v>
       </c>
       <c r="N15" s="7">
         <f t="shared" si="9"/>
@@ -1867,7 +1925,10 @@
         <f t="shared" si="9"/>
         <v>7361.8000000000011</v>
       </c>
-      <c r="V15" s="7"/>
+      <c r="V15" s="7">
+        <f t="shared" si="9"/>
+        <v>9392.7000000000007</v>
+      </c>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
@@ -1918,7 +1979,9 @@
       <c r="L16" s="7">
         <v>88.8</v>
       </c>
-      <c r="M16" s="7"/>
+      <c r="M16" s="7">
+        <v>78.900000000000006</v>
+      </c>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
@@ -1933,7 +1996,9 @@
       <c r="U16" s="7">
         <v>209.8</v>
       </c>
-      <c r="V16" s="7"/>
+      <c r="V16" s="7">
+        <v>216.7</v>
+      </c>
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
       <c r="Y16" s="7"/>
@@ -1983,7 +2048,7 @@
         <v>1941.6999999999998</v>
       </c>
       <c r="I17" s="7">
-        <f t="shared" ref="I17:U17" si="11">+I15+I16</f>
+        <f t="shared" ref="I17:V17" si="11">+I15+I16</f>
         <v>1893.3999999999994</v>
       </c>
       <c r="J17" s="7">
@@ -2000,7 +2065,7 @@
       </c>
       <c r="M17" s="7">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2124.5</v>
       </c>
       <c r="N17" s="7">
         <f t="shared" si="11"/>
@@ -2031,7 +2096,10 @@
         <f t="shared" si="11"/>
         <v>7571.6000000000013</v>
       </c>
-      <c r="V17" s="7"/>
+      <c r="V17" s="7">
+        <f t="shared" si="11"/>
+        <v>9609.4000000000015</v>
+      </c>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
@@ -2137,9 +2205,9 @@
         <f t="shared" si="13"/>
         <v>5.899793920659457</v>
       </c>
-      <c r="M19" s="9" t="e">
+      <c r="M19" s="9">
         <f t="shared" si="13"/>
-        <v>#DIV/0!</v>
+        <v>5.4854118254583009</v>
       </c>
       <c r="N19" s="9" t="e">
         <f t="shared" si="13"/>
@@ -2161,7 +2229,10 @@
         <f>+U17/U20</f>
         <v>19.251461988304097</v>
       </c>
-      <c r="V19" s="7"/>
+      <c r="V19" s="9">
+        <f>+V17/V20</f>
+        <v>24.734620334620338</v>
+      </c>
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
@@ -2210,7 +2281,9 @@
       <c r="L20" s="7">
         <v>388.2</v>
       </c>
-      <c r="M20" s="7"/>
+      <c r="M20" s="7">
+        <v>387.3</v>
+      </c>
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
       <c r="P20" s="7"/>
@@ -2225,7 +2298,9 @@
       <c r="U20" s="7">
         <v>393.3</v>
       </c>
-      <c r="V20" s="7"/>
+      <c r="V20" s="7">
+        <v>388.5</v>
+      </c>
       <c r="W20" s="7"/>
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
@@ -2321,7 +2396,7 @@
       </c>
       <c r="M22" s="10">
         <f t="shared" ref="M22:M24" si="21">+M3/I3-1</f>
-        <v>-1</v>
+        <v>4.6268038129686273E-2</v>
       </c>
       <c r="N22" s="10">
         <f t="shared" ref="N22:N24" si="22">+N3/J3-1</f>
@@ -2333,14 +2408,17 @@
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
       <c r="T22" s="10">
-        <f t="shared" ref="T22:U23" si="23">+T3/S3-1</f>
+        <f t="shared" ref="T22:V23" si="23">+T3/S3-1</f>
         <v>0.42178700349312703</v>
       </c>
       <c r="U22" s="10">
         <f t="shared" si="23"/>
         <v>-7.7443410244955047E-3</v>
       </c>
-      <c r="V22" s="7"/>
+      <c r="V22" s="10">
+        <f t="shared" si="23"/>
+        <v>0.12428854272418643</v>
+      </c>
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
       <c r="Y22" s="7"/>
@@ -2395,7 +2473,7 @@
       </c>
       <c r="M23" s="10">
         <f t="shared" si="21"/>
-        <v>-1</v>
+        <v>0.43771981242672919</v>
       </c>
       <c r="N23" s="10">
         <f t="shared" si="22"/>
@@ -2414,7 +2492,10 @@
         <f t="shared" si="23"/>
         <v>0.15557216320575096</v>
       </c>
-      <c r="V23" s="7"/>
+      <c r="V23" s="10">
+        <f t="shared" si="23"/>
+        <v>0.26158726248036723</v>
+      </c>
       <c r="W23" s="7"/>
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
@@ -2469,7 +2550,7 @@
       </c>
       <c r="M24" s="11">
         <f t="shared" si="21"/>
-        <v>-1</v>
+        <v>0.12632998651281291</v>
       </c>
       <c r="N24" s="11">
         <f t="shared" si="22"/>
@@ -2491,7 +2572,10 @@
         <f>+U5/T5-1</f>
         <v>2.5560171997750292E-2</v>
       </c>
-      <c r="V24" s="7"/>
+      <c r="V24" s="11">
+        <f>+V5/U5-1</f>
+        <v>0.15583680372502462</v>
+      </c>
       <c r="W24" s="7"/>
       <c r="X24" s="7"/>
       <c r="Y24" s="7"/>
@@ -2568,7 +2652,10 @@
         <f>+(U3-U6)/U3</f>
         <v>0.52193286691442309</v>
       </c>
-      <c r="V25" s="7"/>
+      <c r="V25" s="10">
+        <f>+(V3-V6)/V3</f>
+        <v>0.534859015375312</v>
+      </c>
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
@@ -2645,7 +2732,10 @@
         <f>+(U4-U7)/U4</f>
         <v>0.48199932247235994</v>
       </c>
-      <c r="V26" s="7"/>
+      <c r="V26" s="10">
+        <f>+(V4-V7)/V4</f>
+        <v>0.50869034541681923</v>
+      </c>
       <c r="W26" s="7"/>
       <c r="X26" s="7"/>
       <c r="Y26" s="7"/>
@@ -2710,9 +2800,9 @@
         <f t="shared" si="28"/>
         <v>0.53687741331565197</v>
       </c>
-      <c r="M27" s="10" t="e">
+      <c r="M27" s="10">
         <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
+        <v>0.51627195316657803</v>
       </c>
       <c r="N27" s="10" t="e">
         <f t="shared" si="28"/>
@@ -2743,7 +2833,10 @@
         <f t="shared" si="29"/>
         <v>0.51275700653506895</v>
       </c>
-      <c r="V27" s="7"/>
+      <c r="V27" s="10">
+        <f t="shared" ref="V27" si="30">+V8/V5</f>
+        <v>0.52829587997783722</v>
+      </c>
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
       <c r="Y27" s="7"/>
@@ -2769,27 +2862,27 @@
         <v>49</v>
       </c>
       <c r="C28" s="10" t="e">
-        <f t="shared" ref="C28:H28" si="30">+C11/C5</f>
+        <f t="shared" ref="C28:H28" si="31">+C11/C5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.29387454347408209</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.33050987978444107</v>
       </c>
       <c r="F28" s="10" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.26302457466918711</v>
       </c>
       <c r="H28" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.32786172725033685</v>
       </c>
       <c r="I28" s="10">
@@ -2797,51 +2890,54 @@
         <v>0.32704930316199604</v>
       </c>
       <c r="J28" s="10">
-        <f t="shared" ref="J28:N28" si="31">+J11/J5</f>
+        <f t="shared" ref="J28:N28" si="32">+J11/J5</f>
         <v>0.36224467763527224</v>
       </c>
       <c r="K28" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.35366531034037324</v>
       </c>
       <c r="L28" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.34636036246863511</v>
       </c>
-      <c r="M28" s="10" t="e">
-        <f t="shared" si="31"/>
-        <v>#DIV/0!</v>
+      <c r="M28" s="10">
+        <f t="shared" si="32"/>
+        <v>0.32841937200638638</v>
       </c>
       <c r="N28" s="10" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O28" s="7"/>
       <c r="P28" s="10" t="e">
-        <f t="shared" ref="P28:U28" si="32">+P11/P5</f>
+        <f t="shared" ref="P28:U28" si="33">+P11/P5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q28" s="10" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R28" s="10" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S28" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.30702201819263802</v>
       </c>
       <c r="T28" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.3281129234174574</v>
       </c>
       <c r="U28" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.3192382947255944</v>
       </c>
-      <c r="V28" s="7"/>
+      <c r="V28" s="10">
+        <f t="shared" ref="V28" si="34">+V11/V5</f>
+        <v>0.34595451720833986</v>
+      </c>
       <c r="W28" s="7"/>
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
@@ -2867,27 +2963,27 @@
         <v>50</v>
       </c>
       <c r="C29" s="10" t="e">
-        <f t="shared" ref="C29:H29" si="33">+C14/C13</f>
+        <f t="shared" ref="C29:H29" si="35">+C14/C13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D29" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.15998244362758551</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.1608610404238455</v>
       </c>
       <c r="F29" s="10" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G29" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.1580135440180587</v>
       </c>
       <c r="H29" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.17717243496951354</v>
       </c>
       <c r="I29" s="10">
@@ -2895,51 +2991,54 @@
         <v>0.15697647864809319</v>
       </c>
       <c r="J29" s="10">
-        <f t="shared" ref="J29:N29" si="34">+J14/J13</f>
+        <f t="shared" ref="J29:N29" si="36">+J14/J13</f>
         <v>0.21530773120742483</v>
       </c>
       <c r="K29" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.16687596426393028</v>
       </c>
       <c r="L29" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.1812637137863066</v>
       </c>
-      <c r="M29" s="10" t="e">
-        <f t="shared" si="34"/>
-        <v>#DIV/0!</v>
+      <c r="M29" s="10">
+        <f t="shared" si="36"/>
+        <v>0.17774740734785752</v>
       </c>
       <c r="N29" s="10" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O29" s="7"/>
       <c r="P29" s="10" t="e">
-        <f t="shared" ref="P29:U29" si="35">+P14/P13</f>
+        <f t="shared" ref="P29:U29" si="37">+P14/P13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q29" s="10" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R29" s="10" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S29" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.15023001502455038</v>
       </c>
       <c r="T29" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.15806682446193648</v>
       </c>
       <c r="U29" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.18585773688401305</v>
       </c>
-      <c r="V29" s="7"/>
+      <c r="V29" s="10">
+        <f t="shared" ref="V29" si="38">+V14/V13</f>
+        <v>0.17651958162737483</v>
+      </c>
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>

--- a/ASML.xlsx
+++ b/ASML.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCFF263-3C55-44A1-BDD8-7525192DA638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BB28B4-8873-4B45-9F3B-C46881BC08FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{40E26FA9-FA23-47D9-8A0D-17BDAE3930EB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="60">
   <si>
     <t>numbers in mio EUR</t>
   </si>
@@ -203,6 +203,21 @@
   <si>
     <t>FY25</t>
   </si>
+  <si>
+    <t>Supply Chain</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -213,13 +228,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -289,25 +310,28 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -336,16 +360,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>123826</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>247649</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>19052</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>350022</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>157164</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>273821</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>52390</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -374,7 +398,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6419850" y="504826"/>
+          <a:off x="247649" y="1962152"/>
           <a:ext cx="3331347" cy="3919538"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -704,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{549F8A75-D845-4CB2-8AA6-DF55F6437223}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.85546875" style="2" customWidth="1"/>
@@ -724,7 +748,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="2">
-        <v>659.1</v>
+        <v>1250.8</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -732,7 +756,7 @@
         <v>3</v>
       </c>
       <c r="H3" s="7">
-        <v>388.5</v>
+        <v>385.4</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>44</v>
@@ -753,7 +777,7 @@
       </c>
       <c r="H4" s="3">
         <f>+H2*H3</f>
-        <v>256060.35</v>
+        <v>482058.31999999995</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -764,8 +788,8 @@
         <v>5</v>
       </c>
       <c r="H5" s="3">
-        <f>12916+405.9</f>
-        <v>13321.9</v>
+        <f>7970.4+405.9</f>
+        <v>8376.2999999999993</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>44</v>
@@ -776,8 +800,7 @@
         <v>6</v>
       </c>
       <c r="H6" s="3">
-        <f>1681.9+2709</f>
-        <v>4390.8999999999996</v>
+        <v>2705.6</v>
       </c>
       <c r="I6" s="13" t="s">
         <v>44</v>
@@ -789,11 +812,16 @@
       </c>
       <c r="H7" s="3">
         <f>+H4-H5+H6</f>
-        <v>247129.35</v>
+        <v>476387.61999999994</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B9" s="6"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B12" s="6" t="s">
+        <v>55</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -806,7 +834,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{220A5578-A882-4F6B-ABA9-9B08D3236B05}">
-  <dimension ref="A1:AO360"/>
+  <dimension ref="A1:AS360"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -814,12 +842,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
@@ -856,29 +884,41 @@
       <c r="N2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="O2" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="R2" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="V2" s="13" t="s">
+      <c r="Z2" s="13" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
@@ -912,26 +952,28 @@
         <v>5553.8</v>
       </c>
       <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
+      <c r="O3" s="7">
+        <v>6279.4</v>
+      </c>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
-      <c r="S3" s="7">
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7">
         <v>15430.3</v>
       </c>
-      <c r="T3" s="7">
+      <c r="X3" s="7">
         <v>21938.6</v>
       </c>
-      <c r="U3" s="7">
+      <c r="Y3" s="7">
         <v>21768.7</v>
       </c>
-      <c r="V3" s="7">
+      <c r="Z3" s="7">
         <v>24474.3</v>
       </c>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
       <c r="AA3" s="7"/>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
@@ -947,8 +989,12 @@
       <c r="AM3" s="7"/>
       <c r="AN3" s="7"/>
       <c r="AO3" s="7"/>
-    </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="AP3" s="7"/>
+      <c r="AQ3" s="7"/>
+      <c r="AR3" s="7"/>
+      <c r="AS3" s="7"/>
+    </row>
+    <row r="4" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
@@ -982,26 +1028,28 @@
         <v>1962.2</v>
       </c>
       <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
+      <c r="O4" s="7">
+        <v>2487.5</v>
+      </c>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
-      <c r="S4" s="7">
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7">
         <v>5743.1</v>
       </c>
-      <c r="T4" s="7">
+      <c r="X4" s="7">
         <v>5619.9</v>
       </c>
-      <c r="U4" s="7">
+      <c r="Y4" s="7">
         <v>6494.2</v>
       </c>
-      <c r="V4" s="7">
+      <c r="Z4" s="7">
         <v>8193</v>
       </c>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
       <c r="AA4" s="7"/>
       <c r="AB4" s="7"/>
       <c r="AC4" s="7"/>
@@ -1017,8 +1065,12 @@
       <c r="AM4" s="7"/>
       <c r="AN4" s="7"/>
       <c r="AO4" s="7"/>
-    </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="AP4" s="7"/>
+      <c r="AQ4" s="7"/>
+      <c r="AR4" s="7"/>
+      <c r="AS4" s="7"/>
+    </row>
+    <row r="5" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>20</v>
       </c>
@@ -1047,7 +1099,7 @@
         <v>6902.3</v>
       </c>
       <c r="I5" s="8">
-        <f t="shared" ref="I5:N5" si="1">+I3+I4</f>
+        <f t="shared" ref="I5:O5" si="1">+I3+I4</f>
         <v>6673</v>
       </c>
       <c r="J5" s="8">
@@ -1070,39 +1122,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O5" s="7"/>
-      <c r="P5" s="8">
-        <f t="shared" ref="P5:T5" si="2">+P3+P4</f>
+      <c r="O5" s="8">
+        <f t="shared" si="1"/>
+        <v>8766.9</v>
+      </c>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="8">
+        <f t="shared" ref="T5:X5" si="2">+T3+T4</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="U5" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R5" s="8">
+      <c r="V5" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S5" s="8">
+      <c r="W5" s="8">
         <f t="shared" si="2"/>
         <v>21173.4</v>
       </c>
-      <c r="T5" s="8">
+      <c r="X5" s="8">
         <f t="shared" si="2"/>
         <v>27558.5</v>
       </c>
-      <c r="U5" s="8">
-        <f>+U3+U4</f>
+      <c r="Y5" s="8">
+        <f>+Y3+Y4</f>
         <v>28262.9</v>
       </c>
-      <c r="V5" s="8">
-        <f>+V3+V4</f>
+      <c r="Z5" s="8">
+        <f>+Z3+Z4</f>
         <v>32667.3</v>
       </c>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
       <c r="AA5" s="7"/>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
@@ -1118,8 +1173,12 @@
       <c r="AM5" s="7"/>
       <c r="AN5" s="7"/>
       <c r="AO5" s="7"/>
-    </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="AP5" s="7"/>
+      <c r="AQ5" s="7"/>
+      <c r="AR5" s="7"/>
+      <c r="AS5" s="7"/>
+    </row>
+    <row r="6" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>39</v>
       </c>
@@ -1153,26 +1212,28 @@
         <v>3635.7</v>
       </c>
       <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
+      <c r="O6" s="7">
+        <v>4121.8999999999996</v>
+      </c>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
-      <c r="S6" s="7">
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7">
         <v>7582.3</v>
       </c>
-      <c r="T6" s="7">
+      <c r="X6" s="7">
         <v>10151</v>
       </c>
-      <c r="U6" s="7">
+      <c r="Y6" s="7">
         <v>10406.9</v>
       </c>
-      <c r="V6" s="7">
+      <c r="Z6" s="7">
         <v>11384</v>
       </c>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
@@ -1188,8 +1249,12 @@
       <c r="AM6" s="7"/>
       <c r="AN6" s="7"/>
       <c r="AO6" s="7"/>
-    </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="AP6" s="7"/>
+      <c r="AQ6" s="7"/>
+      <c r="AR6" s="7"/>
+      <c r="AS6" s="7"/>
+    </row>
+    <row r="7" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>40</v>
       </c>
@@ -1229,26 +1294,28 @@
       <c r="N7" s="7">
         <v>0</v>
       </c>
-      <c r="O7" s="7"/>
+      <c r="O7" s="7">
+        <v>0</v>
+      </c>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
-      <c r="S7" s="7">
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7">
         <v>2891</v>
       </c>
-      <c r="T7" s="7">
+      <c r="X7" s="7">
         <v>3271.4</v>
       </c>
-      <c r="U7" s="7">
+      <c r="Y7" s="7">
         <v>3364</v>
       </c>
-      <c r="V7" s="7">
+      <c r="Z7" s="7">
         <v>4025.3</v>
       </c>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="7"/>
       <c r="AA7" s="7"/>
       <c r="AB7" s="7"/>
       <c r="AC7" s="7"/>
@@ -1264,8 +1331,12 @@
       <c r="AM7" s="7"/>
       <c r="AN7" s="7"/>
       <c r="AO7" s="7"/>
-    </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="AP7" s="7"/>
+      <c r="AQ7" s="7"/>
+      <c r="AR7" s="7"/>
+      <c r="AS7" s="7"/>
+    </row>
+    <row r="8" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>21</v>
       </c>
@@ -1278,7 +1349,7 @@
         <v>3212.1999999999994</v>
       </c>
       <c r="E8" s="7">
-        <f t="shared" ref="E8:N8" si="3">+E5-E6</f>
+        <f t="shared" ref="E8:O8" si="3">+E5-E6</f>
         <v>3717.3</v>
       </c>
       <c r="F8" s="7">
@@ -1317,39 +1388,42 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7">
-        <f t="shared" ref="P8:T8" si="4">+P5-SUM(P6:P7)</f>
+      <c r="O8" s="7">
+        <f t="shared" si="3"/>
+        <v>4645</v>
+      </c>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7">
+        <f t="shared" ref="T8:X8" si="4">+T5-SUM(T6:T7)</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="7">
+      <c r="U8" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R8" s="7">
+      <c r="V8" s="7">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S8" s="7">
+      <c r="W8" s="7">
         <f t="shared" si="4"/>
         <v>10700.100000000002</v>
       </c>
-      <c r="T8" s="7">
+      <c r="X8" s="7">
         <f t="shared" si="4"/>
         <v>14136.1</v>
       </c>
-      <c r="U8" s="7">
-        <f>+U5-SUM(U6:U7)</f>
+      <c r="Y8" s="7">
+        <f>+Y5-SUM(Y6:Y7)</f>
         <v>14492.000000000002</v>
       </c>
-      <c r="V8" s="7">
-        <f>+V5-SUM(V6:V7)</f>
+      <c r="Z8" s="7">
+        <f>+Z5-SUM(Z6:Z7)</f>
         <v>17258</v>
       </c>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
       <c r="AA8" s="7"/>
       <c r="AB8" s="7"/>
       <c r="AC8" s="7"/>
@@ -1365,8 +1439,12 @@
       <c r="AM8" s="7"/>
       <c r="AN8" s="7"/>
       <c r="AO8" s="7"/>
-    </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="AP8" s="7"/>
+      <c r="AQ8" s="7"/>
+      <c r="AR8" s="7"/>
+      <c r="AS8" s="7"/>
+    </row>
+    <row r="9" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1400,26 +1478,28 @@
         <v>1108.7</v>
       </c>
       <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
+      <c r="O9" s="7">
+        <v>1184.9000000000001</v>
+      </c>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
-      <c r="S9" s="7">
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7">
         <v>3253.5</v>
       </c>
-      <c r="T9" s="7">
+      <c r="X9" s="7">
         <v>3980.6</v>
       </c>
-      <c r="U9" s="7">
+      <c r="Y9" s="7">
         <v>4303.7</v>
       </c>
-      <c r="V9" s="7">
+      <c r="Z9" s="7">
         <v>4698.8</v>
       </c>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
       <c r="AA9" s="7"/>
       <c r="AB9" s="7"/>
       <c r="AC9" s="7"/>
@@ -1435,8 +1515,12 @@
       <c r="AM9" s="7"/>
       <c r="AN9" s="7"/>
       <c r="AO9" s="7"/>
-    </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="AP9" s="7"/>
+      <c r="AQ9" s="7"/>
+      <c r="AR9" s="7"/>
+      <c r="AS9" s="7"/>
+    </row>
+    <row r="10" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>23</v>
       </c>
@@ -1470,26 +1554,28 @@
         <v>303.2</v>
       </c>
       <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
+      <c r="O10" s="7">
+        <v>302.3</v>
+      </c>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
-      <c r="S10" s="7">
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7">
         <v>945.9</v>
       </c>
-      <c r="T10" s="7">
+      <c r="X10" s="7">
         <v>1113.2</v>
       </c>
-      <c r="U10" s="7">
+      <c r="Y10" s="7">
         <v>1165.7</v>
       </c>
-      <c r="V10" s="7">
+      <c r="Z10" s="7">
         <v>1257.8</v>
       </c>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="7"/>
       <c r="AA10" s="7"/>
       <c r="AB10" s="7"/>
       <c r="AC10" s="7"/>
@@ -1505,8 +1591,12 @@
       <c r="AM10" s="7"/>
       <c r="AN10" s="7"/>
       <c r="AO10" s="7"/>
-    </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="AP10" s="7"/>
+      <c r="AQ10" s="7"/>
+      <c r="AR10" s="7"/>
+      <c r="AS10" s="7"/>
+    </row>
+    <row r="11" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>24</v>
       </c>
@@ -1519,7 +1609,7 @@
         <v>1834.5999999999995</v>
       </c>
       <c r="E11" s="7">
-        <f t="shared" ref="E11:V11" si="5">+E8-SUM(E9:E10)</f>
+        <f t="shared" ref="E11:Z11" si="5">+E8-SUM(E9:E10)</f>
         <v>2391.9</v>
       </c>
       <c r="F11" s="7">
@@ -1558,39 +1648,42 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7">
+      <c r="O11" s="7">
+        <f t="shared" si="5"/>
+        <v>3157.8</v>
+      </c>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="7">
+      <c r="U11" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R11" s="7">
+      <c r="V11" s="7">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="S11" s="7">
+      <c r="W11" s="7">
         <f t="shared" si="5"/>
         <v>6500.7000000000025</v>
       </c>
-      <c r="T11" s="7">
+      <c r="X11" s="7">
         <f t="shared" si="5"/>
         <v>9042.2999999999993</v>
       </c>
-      <c r="U11" s="7">
+      <c r="Y11" s="7">
         <f t="shared" si="5"/>
         <v>9022.6000000000022</v>
       </c>
-      <c r="V11" s="7">
+      <c r="Z11" s="7">
         <f t="shared" si="5"/>
         <v>11301.4</v>
       </c>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
       <c r="AA11" s="7"/>
       <c r="AB11" s="7"/>
       <c r="AC11" s="7"/>
@@ -1606,8 +1699,12 @@
       <c r="AM11" s="7"/>
       <c r="AN11" s="7"/>
       <c r="AO11" s="7"/>
-    </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="AP11" s="7"/>
+      <c r="AQ11" s="7"/>
+      <c r="AR11" s="7"/>
+      <c r="AS11" s="7"/>
+    </row>
+    <row r="12" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>25</v>
       </c>
@@ -1641,26 +1738,28 @@
         <v>19.399999999999999</v>
       </c>
       <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
+      <c r="O12" s="7">
+        <v>40.9</v>
+      </c>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
-      <c r="S12" s="7">
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7">
         <v>-44.6</v>
       </c>
-      <c r="T12" s="7">
+      <c r="X12" s="7">
         <v>41.2</v>
       </c>
-      <c r="U12" s="7">
+      <c r="Y12" s="7">
         <v>19.8</v>
       </c>
-      <c r="V12" s="7">
+      <c r="Z12" s="7">
         <v>104.7</v>
       </c>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
       <c r="AA12" s="7"/>
       <c r="AB12" s="7"/>
       <c r="AC12" s="7"/>
@@ -1676,8 +1775,12 @@
       <c r="AM12" s="7"/>
       <c r="AN12" s="7"/>
       <c r="AO12" s="7"/>
-    </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="AP12" s="7"/>
+      <c r="AQ12" s="7"/>
+      <c r="AR12" s="7"/>
+      <c r="AS12" s="7"/>
+    </row>
+    <row r="13" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>26</v>
       </c>
@@ -1690,7 +1793,7 @@
         <v>1822.6999999999994</v>
       </c>
       <c r="E13" s="7">
-        <f t="shared" ref="E13:V13" si="7">+E11+E12</f>
+        <f t="shared" ref="E13:Z13" si="7">+E11+E12</f>
         <v>2397.1</v>
       </c>
       <c r="F13" s="7">
@@ -1729,39 +1832,42 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7">
+      <c r="O13" s="7">
+        <f t="shared" si="7"/>
+        <v>3198.7000000000003</v>
+      </c>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="7">
+      <c r="U13" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="R13" s="7">
+      <c r="V13" s="7">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="S13" s="7">
+      <c r="W13" s="7">
         <f t="shared" si="7"/>
         <v>6456.1000000000022</v>
       </c>
-      <c r="T13" s="7">
+      <c r="X13" s="7">
         <f t="shared" si="7"/>
         <v>9083.5</v>
       </c>
-      <c r="U13" s="7">
+      <c r="Y13" s="7">
         <f t="shared" si="7"/>
         <v>9042.4000000000015</v>
       </c>
-      <c r="V13" s="7">
+      <c r="Z13" s="7">
         <f t="shared" si="7"/>
         <v>11406.1</v>
       </c>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7"/>
       <c r="AA13" s="7"/>
       <c r="AB13" s="7"/>
       <c r="AC13" s="7"/>
@@ -1777,8 +1883,12 @@
       <c r="AM13" s="7"/>
       <c r="AN13" s="7"/>
       <c r="AO13" s="7"/>
-    </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="AP13" s="7"/>
+      <c r="AQ13" s="7"/>
+      <c r="AR13" s="7"/>
+      <c r="AS13" s="7"/>
+    </row>
+    <row r="14" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
@@ -1812,26 +1922,28 @@
         <v>442.2</v>
       </c>
       <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
+      <c r="O14" s="7">
+        <v>546.6</v>
+      </c>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
-      <c r="S14" s="7">
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7">
         <v>969.9</v>
       </c>
-      <c r="T14" s="7">
+      <c r="X14" s="7">
         <v>1435.8</v>
       </c>
-      <c r="U14" s="7">
+      <c r="Y14" s="7">
         <v>1680.6</v>
       </c>
-      <c r="V14" s="7">
+      <c r="Z14" s="7">
         <v>2013.4</v>
       </c>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
       <c r="AB14" s="7"/>
       <c r="AC14" s="7"/>
@@ -1847,8 +1959,12 @@
       <c r="AM14" s="7"/>
       <c r="AN14" s="7"/>
       <c r="AO14" s="7"/>
-    </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="AP14" s="7"/>
+      <c r="AQ14" s="7"/>
+      <c r="AR14" s="7"/>
+      <c r="AS14" s="7"/>
+    </row>
+    <row r="15" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
@@ -1877,7 +1993,7 @@
         <v>1875.7999999999997</v>
       </c>
       <c r="I15" s="7">
-        <f t="shared" ref="I15:V15" si="9">+I13-I14</f>
+        <f t="shared" ref="I15:Z15" si="9">+I13-I14</f>
         <v>1845.7999999999995</v>
       </c>
       <c r="J15" s="7">
@@ -1900,39 +2016,42 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7">
+      <c r="O15" s="7">
+        <f t="shared" si="9"/>
+        <v>2652.1000000000004</v>
+      </c>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q15" s="7">
+      <c r="U15" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R15" s="7">
+      <c r="V15" s="7">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S15" s="7">
+      <c r="W15" s="7">
         <f t="shared" si="9"/>
         <v>5486.2000000000025</v>
       </c>
-      <c r="T15" s="7">
+      <c r="X15" s="7">
         <f t="shared" si="9"/>
         <v>7647.7</v>
       </c>
-      <c r="U15" s="7">
+      <c r="Y15" s="7">
         <f t="shared" si="9"/>
         <v>7361.8000000000011</v>
       </c>
-      <c r="V15" s="7">
+      <c r="Z15" s="7">
         <f t="shared" si="9"/>
         <v>9392.7000000000007</v>
       </c>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
       <c r="AA15" s="7"/>
       <c r="AB15" s="7"/>
       <c r="AC15" s="7"/>
@@ -1948,8 +2067,12 @@
       <c r="AM15" s="7"/>
       <c r="AN15" s="7"/>
       <c r="AO15" s="7"/>
-    </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="AP15" s="7"/>
+      <c r="AQ15" s="7"/>
+      <c r="AR15" s="7"/>
+      <c r="AS15" s="7"/>
+    </row>
+    <row r="16" spans="1:45" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>30</v>
       </c>
@@ -1983,26 +2106,28 @@
         <v>78.900000000000006</v>
       </c>
       <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
+      <c r="O16" s="7">
+        <v>104.6</v>
+      </c>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
-      <c r="S16" s="7">
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7">
         <v>138</v>
       </c>
-      <c r="T16" s="7">
+      <c r="X16" s="7">
         <v>191.3</v>
       </c>
-      <c r="U16" s="7">
+      <c r="Y16" s="7">
         <v>209.8</v>
       </c>
-      <c r="V16" s="7">
+      <c r="Z16" s="7">
         <v>216.7</v>
       </c>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="7"/>
       <c r="AA16" s="7"/>
       <c r="AB16" s="7"/>
       <c r="AC16" s="7"/>
@@ -2018,8 +2143,12 @@
       <c r="AM16" s="7"/>
       <c r="AN16" s="7"/>
       <c r="AO16" s="7"/>
-    </row>
-    <row r="17" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP16" s="7"/>
+      <c r="AQ16" s="7"/>
+      <c r="AR16" s="7"/>
+      <c r="AS16" s="7"/>
+    </row>
+    <row r="17" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>28</v>
       </c>
@@ -2048,7 +2177,7 @@
         <v>1941.6999999999998</v>
       </c>
       <c r="I17" s="7">
-        <f t="shared" ref="I17:V17" si="11">+I15+I16</f>
+        <f t="shared" ref="I17:Z17" si="11">+I15+I16</f>
         <v>1893.3999999999994</v>
       </c>
       <c r="J17" s="7">
@@ -2071,39 +2200,42 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7">
+      <c r="O17" s="7">
+        <f t="shared" si="11"/>
+        <v>2756.7000000000003</v>
+      </c>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="7">
+      <c r="U17" s="7">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="R17" s="7">
+      <c r="V17" s="7">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="S17" s="7">
+      <c r="W17" s="7">
         <f t="shared" si="11"/>
         <v>5624.2000000000025</v>
       </c>
-      <c r="T17" s="7">
+      <c r="X17" s="7">
         <f t="shared" si="11"/>
         <v>7839</v>
       </c>
-      <c r="U17" s="7">
+      <c r="Y17" s="7">
         <f t="shared" si="11"/>
         <v>7571.6000000000013</v>
       </c>
-      <c r="V17" s="7">
+      <c r="Z17" s="7">
         <f t="shared" si="11"/>
         <v>9609.4000000000015</v>
       </c>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="7"/>
       <c r="AA17" s="7"/>
       <c r="AB17" s="7"/>
       <c r="AC17" s="7"/>
@@ -2119,8 +2251,12 @@
       <c r="AM17" s="7"/>
       <c r="AN17" s="7"/>
       <c r="AO17" s="7"/>
-    </row>
-    <row r="18" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP17" s="7"/>
+      <c r="AQ17" s="7"/>
+      <c r="AR17" s="7"/>
+      <c r="AS17" s="7"/>
+    </row>
+    <row r="18" spans="2:45" x14ac:dyDescent="0.2">
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
@@ -2160,8 +2296,12 @@
       <c r="AM18" s="7"/>
       <c r="AN18" s="7"/>
       <c r="AO18" s="7"/>
-    </row>
-    <row r="19" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP18" s="7"/>
+      <c r="AQ18" s="7"/>
+      <c r="AR18" s="7"/>
+      <c r="AS18" s="7"/>
+    </row>
+    <row r="19" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>32</v>
       </c>
@@ -2194,7 +2334,7 @@
         <v>4.8129130655821033</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" ref="J19:N19" si="13">+J17/J20</f>
+        <f t="shared" ref="J19:O19" si="13">+J17/J20</f>
         <v>6.8482074752097626</v>
       </c>
       <c r="K19" s="9">
@@ -2213,30 +2353,33 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="9">
-        <f t="shared" ref="S19:T19" si="14">+S17/S20</f>
+      <c r="O19" s="9">
+        <f t="shared" si="13"/>
+        <v>7.1528282304099644</v>
+      </c>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="9">
+        <f t="shared" ref="W19:X19" si="14">+W17/W20</f>
         <v>14.141815438772952</v>
       </c>
-      <c r="T19" s="9">
+      <c r="X19" s="9">
         <f t="shared" si="14"/>
         <v>19.906043676993399</v>
       </c>
-      <c r="U19" s="9">
-        <f>+U17/U20</f>
+      <c r="Y19" s="9">
+        <f>+Y17/Y20</f>
         <v>19.251461988304097</v>
       </c>
-      <c r="V19" s="9">
-        <f>+V17/V20</f>
+      <c r="Z19" s="9">
+        <f>+Z17/Z20</f>
         <v>24.734620334620338</v>
       </c>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="7"/>
       <c r="AA19" s="7"/>
       <c r="AB19" s="7"/>
       <c r="AC19" s="7"/>
@@ -2252,8 +2395,12 @@
       <c r="AM19" s="7"/>
       <c r="AN19" s="7"/>
       <c r="AO19" s="7"/>
-    </row>
-    <row r="20" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP19" s="7"/>
+      <c r="AQ19" s="7"/>
+      <c r="AR19" s="7"/>
+      <c r="AS19" s="7"/>
+    </row>
+    <row r="20" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>3</v>
       </c>
@@ -2285,26 +2432,28 @@
         <v>387.3</v>
       </c>
       <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
+      <c r="O20" s="7">
+        <v>385.4</v>
+      </c>
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
-      <c r="S20" s="7">
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
+      <c r="V20" s="7"/>
+      <c r="W20" s="7">
         <v>397.7</v>
       </c>
-      <c r="T20" s="7">
+      <c r="X20" s="7">
         <v>393.8</v>
       </c>
-      <c r="U20" s="7">
+      <c r="Y20" s="7">
         <v>393.3</v>
       </c>
-      <c r="V20" s="7">
+      <c r="Z20" s="7">
         <v>388.5</v>
       </c>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7"/>
-      <c r="Z20" s="7"/>
       <c r="AA20" s="7"/>
       <c r="AB20" s="7"/>
       <c r="AC20" s="7"/>
@@ -2320,8 +2469,12 @@
       <c r="AM20" s="7"/>
       <c r="AN20" s="7"/>
       <c r="AO20" s="7"/>
-    </row>
-    <row r="21" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP20" s="7"/>
+      <c r="AQ20" s="7"/>
+      <c r="AR20" s="7"/>
+      <c r="AS20" s="7"/>
+    </row>
+    <row r="21" spans="2:45" x14ac:dyDescent="0.2">
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -2361,8 +2514,12 @@
       <c r="AM21" s="7"/>
       <c r="AN21" s="7"/>
       <c r="AO21" s="7"/>
-    </row>
-    <row r="22" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP21" s="7"/>
+      <c r="AQ21" s="7"/>
+      <c r="AR21" s="7"/>
+      <c r="AS21" s="7"/>
+    </row>
+    <row r="22" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>45</v>
       </c>
@@ -2399,30 +2556,33 @@
         <v>4.6268038129686273E-2</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" ref="N22:N24" si="22">+N3/J3-1</f>
+        <f t="shared" ref="N22:O24" si="22">+N3/J3-1</f>
         <v>-1</v>
       </c>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
+      <c r="O22" s="10">
+        <f t="shared" si="22"/>
+        <v>9.3895895756393344E-2</v>
+      </c>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
       <c r="S22" s="7"/>
-      <c r="T22" s="10">
-        <f t="shared" ref="T22:V23" si="23">+T3/S3-1</f>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7"/>
+      <c r="X22" s="10">
+        <f t="shared" ref="X22:Z23" si="23">+X3/W3-1</f>
         <v>0.42178700349312703</v>
       </c>
-      <c r="U22" s="10">
+      <c r="Y22" s="10">
         <f t="shared" si="23"/>
         <v>-7.7443410244955047E-3</v>
       </c>
-      <c r="V22" s="10">
+      <c r="Z22" s="10">
         <f t="shared" si="23"/>
         <v>0.12428854272418643</v>
       </c>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
-      <c r="Y22" s="7"/>
-      <c r="Z22" s="7"/>
       <c r="AA22" s="7"/>
       <c r="AB22" s="7"/>
       <c r="AC22" s="7"/>
@@ -2438,8 +2598,12 @@
       <c r="AM22" s="7"/>
       <c r="AN22" s="7"/>
       <c r="AO22" s="7"/>
-    </row>
-    <row r="23" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP22" s="7"/>
+      <c r="AQ22" s="7"/>
+      <c r="AR22" s="7"/>
+      <c r="AS22" s="7"/>
+    </row>
+    <row r="23" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>51</v>
       </c>
@@ -2479,27 +2643,30 @@
         <f t="shared" si="22"/>
         <v>-1</v>
       </c>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
+      <c r="O23" s="10">
+        <f t="shared" si="22"/>
+        <v>0.24306631352755992</v>
+      </c>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
       <c r="S23" s="7"/>
-      <c r="T23" s="10">
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="10">
         <f t="shared" si="23"/>
         <v>-2.1451829151503676E-2</v>
       </c>
-      <c r="U23" s="10">
+      <c r="Y23" s="10">
         <f t="shared" si="23"/>
         <v>0.15557216320575096</v>
       </c>
-      <c r="V23" s="10">
+      <c r="Z23" s="10">
         <f t="shared" si="23"/>
         <v>0.26158726248036723</v>
       </c>
-      <c r="W23" s="7"/>
-      <c r="X23" s="7"/>
-      <c r="Y23" s="7"/>
-      <c r="Z23" s="7"/>
       <c r="AA23" s="7"/>
       <c r="AB23" s="7"/>
       <c r="AC23" s="7"/>
@@ -2515,8 +2682,12 @@
       <c r="AM23" s="7"/>
       <c r="AN23" s="7"/>
       <c r="AO23" s="7"/>
-    </row>
-    <row r="24" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP23" s="7"/>
+      <c r="AQ23" s="7"/>
+      <c r="AR23" s="7"/>
+      <c r="AS23" s="7"/>
+    </row>
+    <row r="24" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
         <v>46</v>
       </c>
@@ -2556,30 +2727,33 @@
         <f t="shared" si="22"/>
         <v>-1</v>
       </c>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="11" t="e">
-        <f t="shared" ref="S24:T24" si="24">+S5/R5-1</f>
+      <c r="O24" s="11">
+        <f t="shared" si="22"/>
+        <v>0.13245495059097068</v>
+      </c>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
+      <c r="V24" s="7"/>
+      <c r="W24" s="11" t="e">
+        <f t="shared" ref="W24:X24" si="24">+W5/V5-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T24" s="11">
+      <c r="X24" s="11">
         <f t="shared" si="24"/>
         <v>0.30156233765007023</v>
       </c>
-      <c r="U24" s="11">
-        <f>+U5/T5-1</f>
+      <c r="Y24" s="11">
+        <f>+Y5/X5-1</f>
         <v>2.5560171997750292E-2</v>
       </c>
-      <c r="V24" s="11">
-        <f>+V5/U5-1</f>
+      <c r="Z24" s="11">
+        <f>+Z5/Y5-1</f>
         <v>0.15583680372502462</v>
       </c>
-      <c r="W24" s="7"/>
-      <c r="X24" s="7"/>
-      <c r="Y24" s="7"/>
-      <c r="Z24" s="7"/>
       <c r="AA24" s="7"/>
       <c r="AB24" s="7"/>
       <c r="AC24" s="7"/>
@@ -2595,8 +2769,12 @@
       <c r="AM24" s="7"/>
       <c r="AN24" s="7"/>
       <c r="AO24" s="7"/>
-    </row>
-    <row r="25" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP24" s="7"/>
+      <c r="AQ24" s="7"/>
+      <c r="AR24" s="7"/>
+      <c r="AS24" s="7"/>
+    </row>
+    <row r="25" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>47</v>
       </c>
@@ -2636,30 +2814,32 @@
       <c r="N25" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="10">
-        <f t="shared" ref="S25:T25" si="25">+(S3-S6)/S3</f>
+      <c r="O25" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="12"/>
+      <c r="R25" s="12"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="10">
+        <f t="shared" ref="W25:X25" si="25">+(W3-W6)/W3</f>
         <v>0.50860968354471392</v>
       </c>
-      <c r="T25" s="10">
+      <c r="X25" s="10">
         <f t="shared" si="25"/>
         <v>0.53729955421038711</v>
       </c>
-      <c r="U25" s="10">
-        <f>+(U3-U6)/U3</f>
+      <c r="Y25" s="10">
+        <f>+(Y3-Y6)/Y3</f>
         <v>0.52193286691442309</v>
       </c>
-      <c r="V25" s="10">
-        <f>+(V3-V6)/V3</f>
+      <c r="Z25" s="10">
+        <f>+(Z3-Z6)/Z3</f>
         <v>0.534859015375312</v>
       </c>
-      <c r="W25" s="7"/>
-      <c r="X25" s="7"/>
-      <c r="Y25" s="7"/>
-      <c r="Z25" s="7"/>
       <c r="AA25" s="7"/>
       <c r="AB25" s="7"/>
       <c r="AC25" s="7"/>
@@ -2675,8 +2855,12 @@
       <c r="AM25" s="7"/>
       <c r="AN25" s="7"/>
       <c r="AO25" s="7"/>
-    </row>
-    <row r="26" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP25" s="7"/>
+      <c r="AQ25" s="7"/>
+      <c r="AR25" s="7"/>
+      <c r="AS25" s="7"/>
+    </row>
+    <row r="26" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>52</v>
       </c>
@@ -2716,30 +2900,32 @@
       <c r="N26" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="O26" s="7"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="7"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="10">
-        <f t="shared" ref="S26:T26" si="26">+(S4-S7)/S4</f>
+      <c r="O26" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="12"/>
+      <c r="R26" s="12"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="10">
+        <f t="shared" ref="W26:X26" si="26">+(W4-W7)/W4</f>
         <v>0.49661332729710439</v>
       </c>
-      <c r="T26" s="10">
+      <c r="X26" s="10">
         <f t="shared" si="26"/>
         <v>0.41788999804266974</v>
       </c>
-      <c r="U26" s="10">
-        <f>+(U4-U7)/U4</f>
+      <c r="Y26" s="10">
+        <f>+(Y4-Y7)/Y4</f>
         <v>0.48199932247235994</v>
       </c>
-      <c r="V26" s="10">
-        <f>+(V4-V7)/V4</f>
+      <c r="Z26" s="10">
+        <f>+(Z4-Z7)/Z4</f>
         <v>0.50869034541681923</v>
       </c>
-      <c r="W26" s="7"/>
-      <c r="X26" s="7"/>
-      <c r="Y26" s="7"/>
-      <c r="Z26" s="7"/>
       <c r="AA26" s="7"/>
       <c r="AB26" s="7"/>
       <c r="AC26" s="7"/>
@@ -2755,8 +2941,12 @@
       <c r="AM26" s="7"/>
       <c r="AN26" s="7"/>
       <c r="AO26" s="7"/>
-    </row>
-    <row r="27" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP26" s="7"/>
+      <c r="AQ26" s="7"/>
+      <c r="AR26" s="7"/>
+      <c r="AS26" s="7"/>
+    </row>
+    <row r="27" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>48</v>
       </c>
@@ -2808,39 +2998,42 @@
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O27" s="7"/>
-      <c r="P27" s="10" t="e">
-        <f t="shared" ref="P27:U27" si="29">+P8/P5</f>
+      <c r="O27" s="10">
+        <f t="shared" ref="O27" si="29">+O8/O5</f>
+        <v>0.52983380670476454</v>
+      </c>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="10" t="e">
+        <f t="shared" ref="T27:Y27" si="30">+T8/T5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q27" s="10" t="e">
-        <f t="shared" si="29"/>
+      <c r="U27" s="10" t="e">
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R27" s="10" t="e">
-        <f t="shared" si="29"/>
+      <c r="V27" s="10" t="e">
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S27" s="10">
-        <f t="shared" si="29"/>
+      <c r="W27" s="10">
+        <f t="shared" si="30"/>
         <v>0.50535577658760522</v>
       </c>
-      <c r="T27" s="10">
-        <f t="shared" si="29"/>
+      <c r="X27" s="10">
+        <f t="shared" si="30"/>
         <v>0.51294881796904768</v>
       </c>
-      <c r="U27" s="10">
-        <f t="shared" si="29"/>
+      <c r="Y27" s="10">
+        <f t="shared" si="30"/>
         <v>0.51275700653506895</v>
       </c>
-      <c r="V27" s="10">
-        <f t="shared" ref="V27" si="30">+V8/V5</f>
+      <c r="Z27" s="10">
+        <f t="shared" ref="Z27" si="31">+Z8/Z5</f>
         <v>0.52829587997783722</v>
       </c>
-      <c r="W27" s="7"/>
-      <c r="X27" s="7"/>
-      <c r="Y27" s="7"/>
-      <c r="Z27" s="7"/>
       <c r="AA27" s="7"/>
       <c r="AB27" s="7"/>
       <c r="AC27" s="7"/>
@@ -2856,33 +3049,37 @@
       <c r="AM27" s="7"/>
       <c r="AN27" s="7"/>
       <c r="AO27" s="7"/>
-    </row>
-    <row r="28" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP27" s="7"/>
+      <c r="AQ27" s="7"/>
+      <c r="AR27" s="7"/>
+      <c r="AS27" s="7"/>
+    </row>
+    <row r="28" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C28" s="10" t="e">
-        <f t="shared" ref="C28:H28" si="31">+C11/C5</f>
+        <f t="shared" ref="C28:H28" si="32">+C11/C5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.29387454347408209</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.33050987978444107</v>
       </c>
       <c r="F28" s="10" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.26302457466918711</v>
       </c>
       <c r="H28" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.32786172725033685</v>
       </c>
       <c r="I28" s="10">
@@ -2890,58 +3087,61 @@
         <v>0.32704930316199604</v>
       </c>
       <c r="J28" s="10">
-        <f t="shared" ref="J28:N28" si="32">+J11/J5</f>
+        <f t="shared" ref="J28:N28" si="33">+J11/J5</f>
         <v>0.36224467763527224</v>
       </c>
       <c r="K28" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.35366531034037324</v>
       </c>
       <c r="L28" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.34636036246863511</v>
       </c>
       <c r="M28" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.32841937200638638</v>
       </c>
       <c r="N28" s="10" t="e">
-        <f t="shared" si="32"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O28" s="7"/>
-      <c r="P28" s="10" t="e">
-        <f t="shared" ref="P28:U28" si="33">+P11/P5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q28" s="10" t="e">
         <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R28" s="10" t="e">
-        <f t="shared" si="33"/>
+      <c r="O28" s="10">
+        <f t="shared" ref="O28" si="34">+O11/O5</f>
+        <v>0.36019573623515727</v>
+      </c>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="10" t="e">
+        <f t="shared" ref="T28:Y28" si="35">+T11/T5</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="S28" s="10">
-        <f t="shared" si="33"/>
+      <c r="U28" s="10" t="e">
+        <f t="shared" si="35"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V28" s="10" t="e">
+        <f t="shared" si="35"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W28" s="10">
+        <f t="shared" si="35"/>
         <v>0.30702201819263802</v>
       </c>
-      <c r="T28" s="10">
-        <f t="shared" si="33"/>
+      <c r="X28" s="10">
+        <f t="shared" si="35"/>
         <v>0.3281129234174574</v>
       </c>
-      <c r="U28" s="10">
-        <f t="shared" si="33"/>
+      <c r="Y28" s="10">
+        <f t="shared" si="35"/>
         <v>0.3192382947255944</v>
       </c>
-      <c r="V28" s="10">
-        <f t="shared" ref="V28" si="34">+V11/V5</f>
+      <c r="Z28" s="10">
+        <f t="shared" ref="Z28" si="36">+Z11/Z5</f>
         <v>0.34595451720833986</v>
       </c>
-      <c r="W28" s="7"/>
-      <c r="X28" s="7"/>
-      <c r="Y28" s="7"/>
-      <c r="Z28" s="7"/>
       <c r="AA28" s="7"/>
       <c r="AB28" s="7"/>
       <c r="AC28" s="7"/>
@@ -2957,33 +3157,37 @@
       <c r="AM28" s="7"/>
       <c r="AN28" s="7"/>
       <c r="AO28" s="7"/>
-    </row>
-    <row r="29" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP28" s="7"/>
+      <c r="AQ28" s="7"/>
+      <c r="AR28" s="7"/>
+      <c r="AS28" s="7"/>
+    </row>
+    <row r="29" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C29" s="10" t="e">
-        <f t="shared" ref="C29:H29" si="35">+C14/C13</f>
+        <f t="shared" ref="C29:H29" si="37">+C14/C13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D29" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.15998244362758551</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.1608610404238455</v>
       </c>
       <c r="F29" s="10" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G29" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.1580135440180587</v>
       </c>
       <c r="H29" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.17717243496951354</v>
       </c>
       <c r="I29" s="10">
@@ -2991,58 +3195,61 @@
         <v>0.15697647864809319</v>
       </c>
       <c r="J29" s="10">
-        <f t="shared" ref="J29:N29" si="36">+J14/J13</f>
+        <f t="shared" ref="J29:N29" si="38">+J14/J13</f>
         <v>0.21530773120742483</v>
       </c>
       <c r="K29" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.16687596426393028</v>
       </c>
       <c r="L29" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.1812637137863066</v>
       </c>
       <c r="M29" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0.17774740734785752</v>
       </c>
       <c r="N29" s="10" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O29" s="7"/>
-      <c r="P29" s="10" t="e">
-        <f t="shared" ref="P29:U29" si="37">+P14/P13</f>
+      <c r="O29" s="10">
+        <f t="shared" ref="O29" si="39">+O14/O13</f>
+        <v>0.170881920780317</v>
+      </c>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="10" t="e">
+        <f t="shared" ref="T29:Y29" si="40">+T14/T13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q29" s="10" t="e">
-        <f t="shared" si="37"/>
+      <c r="U29" s="10" t="e">
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R29" s="10" t="e">
-        <f t="shared" si="37"/>
+      <c r="V29" s="10" t="e">
+        <f t="shared" si="40"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S29" s="10">
-        <f t="shared" si="37"/>
+      <c r="W29" s="10">
+        <f t="shared" si="40"/>
         <v>0.15023001502455038</v>
       </c>
-      <c r="T29" s="10">
-        <f t="shared" si="37"/>
+      <c r="X29" s="10">
+        <f t="shared" si="40"/>
         <v>0.15806682446193648</v>
       </c>
-      <c r="U29" s="10">
-        <f t="shared" si="37"/>
+      <c r="Y29" s="10">
+        <f t="shared" si="40"/>
         <v>0.18585773688401305</v>
       </c>
-      <c r="V29" s="10">
-        <f t="shared" ref="V29" si="38">+V14/V13</f>
+      <c r="Z29" s="10">
+        <f t="shared" ref="Z29" si="41">+Z14/Z13</f>
         <v>0.17651958162737483</v>
       </c>
-      <c r="W29" s="7"/>
-      <c r="X29" s="7"/>
-      <c r="Y29" s="7"/>
-      <c r="Z29" s="7"/>
       <c r="AA29" s="7"/>
       <c r="AB29" s="7"/>
       <c r="AC29" s="7"/>
@@ -3058,8 +3265,12 @@
       <c r="AM29" s="7"/>
       <c r="AN29" s="7"/>
       <c r="AO29" s="7"/>
-    </row>
-    <row r="30" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP29" s="7"/>
+      <c r="AQ29" s="7"/>
+      <c r="AR29" s="7"/>
+      <c r="AS29" s="7"/>
+    </row>
+    <row r="30" spans="2:45" x14ac:dyDescent="0.2">
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -3099,8 +3310,12 @@
       <c r="AM30" s="7"/>
       <c r="AN30" s="7"/>
       <c r="AO30" s="7"/>
-    </row>
-    <row r="31" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP30" s="7"/>
+      <c r="AQ30" s="7"/>
+      <c r="AR30" s="7"/>
+      <c r="AS30" s="7"/>
+    </row>
+    <row r="31" spans="2:45" x14ac:dyDescent="0.2">
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
@@ -3140,8 +3355,12 @@
       <c r="AM31" s="7"/>
       <c r="AN31" s="7"/>
       <c r="AO31" s="7"/>
-    </row>
-    <row r="32" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP31" s="7"/>
+      <c r="AQ31" s="7"/>
+      <c r="AR31" s="7"/>
+      <c r="AS31" s="7"/>
+    </row>
+    <row r="32" spans="2:45" x14ac:dyDescent="0.2">
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
@@ -3181,8 +3400,12 @@
       <c r="AM32" s="7"/>
       <c r="AN32" s="7"/>
       <c r="AO32" s="7"/>
-    </row>
-    <row r="33" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP32" s="7"/>
+      <c r="AQ32" s="7"/>
+      <c r="AR32" s="7"/>
+      <c r="AS32" s="7"/>
+    </row>
+    <row r="33" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
@@ -3222,8 +3445,12 @@
       <c r="AM33" s="7"/>
       <c r="AN33" s="7"/>
       <c r="AO33" s="7"/>
-    </row>
-    <row r="34" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP33" s="7"/>
+      <c r="AQ33" s="7"/>
+      <c r="AR33" s="7"/>
+      <c r="AS33" s="7"/>
+    </row>
+    <row r="34" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
@@ -3263,8 +3490,12 @@
       <c r="AM34" s="7"/>
       <c r="AN34" s="7"/>
       <c r="AO34" s="7"/>
-    </row>
-    <row r="35" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP34" s="7"/>
+      <c r="AQ34" s="7"/>
+      <c r="AR34" s="7"/>
+      <c r="AS34" s="7"/>
+    </row>
+    <row r="35" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -3304,8 +3535,12 @@
       <c r="AM35" s="7"/>
       <c r="AN35" s="7"/>
       <c r="AO35" s="7"/>
-    </row>
-    <row r="36" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP35" s="7"/>
+      <c r="AQ35" s="7"/>
+      <c r="AR35" s="7"/>
+      <c r="AS35" s="7"/>
+    </row>
+    <row r="36" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -3345,8 +3580,12 @@
       <c r="AM36" s="7"/>
       <c r="AN36" s="7"/>
       <c r="AO36" s="7"/>
-    </row>
-    <row r="37" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP36" s="7"/>
+      <c r="AQ36" s="7"/>
+      <c r="AR36" s="7"/>
+      <c r="AS36" s="7"/>
+    </row>
+    <row r="37" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -3386,8 +3625,12 @@
       <c r="AM37" s="7"/>
       <c r="AN37" s="7"/>
       <c r="AO37" s="7"/>
-    </row>
-    <row r="38" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP37" s="7"/>
+      <c r="AQ37" s="7"/>
+      <c r="AR37" s="7"/>
+      <c r="AS37" s="7"/>
+    </row>
+    <row r="38" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -3427,8 +3670,12 @@
       <c r="AM38" s="7"/>
       <c r="AN38" s="7"/>
       <c r="AO38" s="7"/>
-    </row>
-    <row r="39" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP38" s="7"/>
+      <c r="AQ38" s="7"/>
+      <c r="AR38" s="7"/>
+      <c r="AS38" s="7"/>
+    </row>
+    <row r="39" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -3468,8 +3715,12 @@
       <c r="AM39" s="7"/>
       <c r="AN39" s="7"/>
       <c r="AO39" s="7"/>
-    </row>
-    <row r="40" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP39" s="7"/>
+      <c r="AQ39" s="7"/>
+      <c r="AR39" s="7"/>
+      <c r="AS39" s="7"/>
+    </row>
+    <row r="40" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
@@ -3509,8 +3760,12 @@
       <c r="AM40" s="7"/>
       <c r="AN40" s="7"/>
       <c r="AO40" s="7"/>
-    </row>
-    <row r="41" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP40" s="7"/>
+      <c r="AQ40" s="7"/>
+      <c r="AR40" s="7"/>
+      <c r="AS40" s="7"/>
+    </row>
+    <row r="41" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
@@ -3550,8 +3805,12 @@
       <c r="AM41" s="7"/>
       <c r="AN41" s="7"/>
       <c r="AO41" s="7"/>
-    </row>
-    <row r="42" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP41" s="7"/>
+      <c r="AQ41" s="7"/>
+      <c r="AR41" s="7"/>
+      <c r="AS41" s="7"/>
+    </row>
+    <row r="42" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
@@ -3591,8 +3850,12 @@
       <c r="AM42" s="7"/>
       <c r="AN42" s="7"/>
       <c r="AO42" s="7"/>
-    </row>
-    <row r="43" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP42" s="7"/>
+      <c r="AQ42" s="7"/>
+      <c r="AR42" s="7"/>
+      <c r="AS42" s="7"/>
+    </row>
+    <row r="43" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
@@ -3632,8 +3895,12 @@
       <c r="AM43" s="7"/>
       <c r="AN43" s="7"/>
       <c r="AO43" s="7"/>
-    </row>
-    <row r="44" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP43" s="7"/>
+      <c r="AQ43" s="7"/>
+      <c r="AR43" s="7"/>
+      <c r="AS43" s="7"/>
+    </row>
+    <row r="44" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
@@ -3673,8 +3940,12 @@
       <c r="AM44" s="7"/>
       <c r="AN44" s="7"/>
       <c r="AO44" s="7"/>
-    </row>
-    <row r="45" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP44" s="7"/>
+      <c r="AQ44" s="7"/>
+      <c r="AR44" s="7"/>
+      <c r="AS44" s="7"/>
+    </row>
+    <row r="45" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
@@ -3714,8 +3985,12 @@
       <c r="AM45" s="7"/>
       <c r="AN45" s="7"/>
       <c r="AO45" s="7"/>
-    </row>
-    <row r="46" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP45" s="7"/>
+      <c r="AQ45" s="7"/>
+      <c r="AR45" s="7"/>
+      <c r="AS45" s="7"/>
+    </row>
+    <row r="46" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
@@ -3755,8 +4030,12 @@
       <c r="AM46" s="7"/>
       <c r="AN46" s="7"/>
       <c r="AO46" s="7"/>
-    </row>
-    <row r="47" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP46" s="7"/>
+      <c r="AQ46" s="7"/>
+      <c r="AR46" s="7"/>
+      <c r="AS46" s="7"/>
+    </row>
+    <row r="47" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
@@ -3796,8 +4075,12 @@
       <c r="AM47" s="7"/>
       <c r="AN47" s="7"/>
       <c r="AO47" s="7"/>
-    </row>
-    <row r="48" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP47" s="7"/>
+      <c r="AQ47" s="7"/>
+      <c r="AR47" s="7"/>
+      <c r="AS47" s="7"/>
+    </row>
+    <row r="48" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
@@ -3837,8 +4120,12 @@
       <c r="AM48" s="7"/>
       <c r="AN48" s="7"/>
       <c r="AO48" s="7"/>
-    </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP48" s="7"/>
+      <c r="AQ48" s="7"/>
+      <c r="AR48" s="7"/>
+      <c r="AS48" s="7"/>
+    </row>
+    <row r="49" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
@@ -3878,8 +4165,12 @@
       <c r="AM49" s="7"/>
       <c r="AN49" s="7"/>
       <c r="AO49" s="7"/>
-    </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP49" s="7"/>
+      <c r="AQ49" s="7"/>
+      <c r="AR49" s="7"/>
+      <c r="AS49" s="7"/>
+    </row>
+    <row r="50" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
@@ -3919,8 +4210,12 @@
       <c r="AM50" s="7"/>
       <c r="AN50" s="7"/>
       <c r="AO50" s="7"/>
-    </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP50" s="7"/>
+      <c r="AQ50" s="7"/>
+      <c r="AR50" s="7"/>
+      <c r="AS50" s="7"/>
+    </row>
+    <row r="51" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
@@ -3960,8 +4255,12 @@
       <c r="AM51" s="7"/>
       <c r="AN51" s="7"/>
       <c r="AO51" s="7"/>
-    </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP51" s="7"/>
+      <c r="AQ51" s="7"/>
+      <c r="AR51" s="7"/>
+      <c r="AS51" s="7"/>
+    </row>
+    <row r="52" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
@@ -4001,8 +4300,12 @@
       <c r="AM52" s="7"/>
       <c r="AN52" s="7"/>
       <c r="AO52" s="7"/>
-    </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP52" s="7"/>
+      <c r="AQ52" s="7"/>
+      <c r="AR52" s="7"/>
+      <c r="AS52" s="7"/>
+    </row>
+    <row r="53" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
@@ -4042,8 +4345,12 @@
       <c r="AM53" s="7"/>
       <c r="AN53" s="7"/>
       <c r="AO53" s="7"/>
-    </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP53" s="7"/>
+      <c r="AQ53" s="7"/>
+      <c r="AR53" s="7"/>
+      <c r="AS53" s="7"/>
+    </row>
+    <row r="54" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
@@ -4083,8 +4390,12 @@
       <c r="AM54" s="7"/>
       <c r="AN54" s="7"/>
       <c r="AO54" s="7"/>
-    </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP54" s="7"/>
+      <c r="AQ54" s="7"/>
+      <c r="AR54" s="7"/>
+      <c r="AS54" s="7"/>
+    </row>
+    <row r="55" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
@@ -4124,8 +4435,12 @@
       <c r="AM55" s="7"/>
       <c r="AN55" s="7"/>
       <c r="AO55" s="7"/>
-    </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP55" s="7"/>
+      <c r="AQ55" s="7"/>
+      <c r="AR55" s="7"/>
+      <c r="AS55" s="7"/>
+    </row>
+    <row r="56" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
@@ -4165,8 +4480,12 @@
       <c r="AM56" s="7"/>
       <c r="AN56" s="7"/>
       <c r="AO56" s="7"/>
-    </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP56" s="7"/>
+      <c r="AQ56" s="7"/>
+      <c r="AR56" s="7"/>
+      <c r="AS56" s="7"/>
+    </row>
+    <row r="57" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
@@ -4206,8 +4525,12 @@
       <c r="AM57" s="7"/>
       <c r="AN57" s="7"/>
       <c r="AO57" s="7"/>
-    </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP57" s="7"/>
+      <c r="AQ57" s="7"/>
+      <c r="AR57" s="7"/>
+      <c r="AS57" s="7"/>
+    </row>
+    <row r="58" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
@@ -4247,8 +4570,12 @@
       <c r="AM58" s="7"/>
       <c r="AN58" s="7"/>
       <c r="AO58" s="7"/>
-    </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP58" s="7"/>
+      <c r="AQ58" s="7"/>
+      <c r="AR58" s="7"/>
+      <c r="AS58" s="7"/>
+    </row>
+    <row r="59" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
@@ -4288,8 +4615,12 @@
       <c r="AM59" s="7"/>
       <c r="AN59" s="7"/>
       <c r="AO59" s="7"/>
-    </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP59" s="7"/>
+      <c r="AQ59" s="7"/>
+      <c r="AR59" s="7"/>
+      <c r="AS59" s="7"/>
+    </row>
+    <row r="60" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
@@ -4329,8 +4660,12 @@
       <c r="AM60" s="7"/>
       <c r="AN60" s="7"/>
       <c r="AO60" s="7"/>
-    </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP60" s="7"/>
+      <c r="AQ60" s="7"/>
+      <c r="AR60" s="7"/>
+      <c r="AS60" s="7"/>
+    </row>
+    <row r="61" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
@@ -4370,8 +4705,12 @@
       <c r="AM61" s="7"/>
       <c r="AN61" s="7"/>
       <c r="AO61" s="7"/>
-    </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP61" s="7"/>
+      <c r="AQ61" s="7"/>
+      <c r="AR61" s="7"/>
+      <c r="AS61" s="7"/>
+    </row>
+    <row r="62" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
@@ -4411,8 +4750,12 @@
       <c r="AM62" s="7"/>
       <c r="AN62" s="7"/>
       <c r="AO62" s="7"/>
-    </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP62" s="7"/>
+      <c r="AQ62" s="7"/>
+      <c r="AR62" s="7"/>
+      <c r="AS62" s="7"/>
+    </row>
+    <row r="63" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
@@ -4452,8 +4795,12 @@
       <c r="AM63" s="7"/>
       <c r="AN63" s="7"/>
       <c r="AO63" s="7"/>
-    </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP63" s="7"/>
+      <c r="AQ63" s="7"/>
+      <c r="AR63" s="7"/>
+      <c r="AS63" s="7"/>
+    </row>
+    <row r="64" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
@@ -4493,8 +4840,12 @@
       <c r="AM64" s="7"/>
       <c r="AN64" s="7"/>
       <c r="AO64" s="7"/>
-    </row>
-    <row r="65" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP64" s="7"/>
+      <c r="AQ64" s="7"/>
+      <c r="AR64" s="7"/>
+      <c r="AS64" s="7"/>
+    </row>
+    <row r="65" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
@@ -4534,8 +4885,12 @@
       <c r="AM65" s="7"/>
       <c r="AN65" s="7"/>
       <c r="AO65" s="7"/>
-    </row>
-    <row r="66" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP65" s="7"/>
+      <c r="AQ65" s="7"/>
+      <c r="AR65" s="7"/>
+      <c r="AS65" s="7"/>
+    </row>
+    <row r="66" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7"/>
@@ -4575,8 +4930,12 @@
       <c r="AM66" s="7"/>
       <c r="AN66" s="7"/>
       <c r="AO66" s="7"/>
-    </row>
-    <row r="67" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP66" s="7"/>
+      <c r="AQ66" s="7"/>
+      <c r="AR66" s="7"/>
+      <c r="AS66" s="7"/>
+    </row>
+    <row r="67" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
@@ -4616,8 +4975,12 @@
       <c r="AM67" s="7"/>
       <c r="AN67" s="7"/>
       <c r="AO67" s="7"/>
-    </row>
-    <row r="68" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP67" s="7"/>
+      <c r="AQ67" s="7"/>
+      <c r="AR67" s="7"/>
+      <c r="AS67" s="7"/>
+    </row>
+    <row r="68" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
       <c r="E68" s="7"/>
@@ -4657,8 +5020,12 @@
       <c r="AM68" s="7"/>
       <c r="AN68" s="7"/>
       <c r="AO68" s="7"/>
-    </row>
-    <row r="69" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP68" s="7"/>
+      <c r="AQ68" s="7"/>
+      <c r="AR68" s="7"/>
+      <c r="AS68" s="7"/>
+    </row>
+    <row r="69" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
@@ -4698,8 +5065,12 @@
       <c r="AM69" s="7"/>
       <c r="AN69" s="7"/>
       <c r="AO69" s="7"/>
-    </row>
-    <row r="70" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP69" s="7"/>
+      <c r="AQ69" s="7"/>
+      <c r="AR69" s="7"/>
+      <c r="AS69" s="7"/>
+    </row>
+    <row r="70" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
       <c r="E70" s="7"/>
@@ -4739,8 +5110,12 @@
       <c r="AM70" s="7"/>
       <c r="AN70" s="7"/>
       <c r="AO70" s="7"/>
-    </row>
-    <row r="71" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP70" s="7"/>
+      <c r="AQ70" s="7"/>
+      <c r="AR70" s="7"/>
+      <c r="AS70" s="7"/>
+    </row>
+    <row r="71" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
@@ -4780,8 +5155,12 @@
       <c r="AM71" s="7"/>
       <c r="AN71" s="7"/>
       <c r="AO71" s="7"/>
-    </row>
-    <row r="72" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP71" s="7"/>
+      <c r="AQ71" s="7"/>
+      <c r="AR71" s="7"/>
+      <c r="AS71" s="7"/>
+    </row>
+    <row r="72" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
       <c r="E72" s="7"/>
@@ -4821,8 +5200,12 @@
       <c r="AM72" s="7"/>
       <c r="AN72" s="7"/>
       <c r="AO72" s="7"/>
-    </row>
-    <row r="73" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP72" s="7"/>
+      <c r="AQ72" s="7"/>
+      <c r="AR72" s="7"/>
+      <c r="AS72" s="7"/>
+    </row>
+    <row r="73" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
@@ -4862,8 +5245,12 @@
       <c r="AM73" s="7"/>
       <c r="AN73" s="7"/>
       <c r="AO73" s="7"/>
-    </row>
-    <row r="74" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP73" s="7"/>
+      <c r="AQ73" s="7"/>
+      <c r="AR73" s="7"/>
+      <c r="AS73" s="7"/>
+    </row>
+    <row r="74" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
       <c r="E74" s="7"/>
@@ -4903,8 +5290,12 @@
       <c r="AM74" s="7"/>
       <c r="AN74" s="7"/>
       <c r="AO74" s="7"/>
-    </row>
-    <row r="75" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP74" s="7"/>
+      <c r="AQ74" s="7"/>
+      <c r="AR74" s="7"/>
+      <c r="AS74" s="7"/>
+    </row>
+    <row r="75" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
@@ -4944,8 +5335,12 @@
       <c r="AM75" s="7"/>
       <c r="AN75" s="7"/>
       <c r="AO75" s="7"/>
-    </row>
-    <row r="76" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP75" s="7"/>
+      <c r="AQ75" s="7"/>
+      <c r="AR75" s="7"/>
+      <c r="AS75" s="7"/>
+    </row>
+    <row r="76" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
       <c r="E76" s="7"/>
@@ -4985,8 +5380,12 @@
       <c r="AM76" s="7"/>
       <c r="AN76" s="7"/>
       <c r="AO76" s="7"/>
-    </row>
-    <row r="77" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP76" s="7"/>
+      <c r="AQ76" s="7"/>
+      <c r="AR76" s="7"/>
+      <c r="AS76" s="7"/>
+    </row>
+    <row r="77" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
@@ -5026,8 +5425,12 @@
       <c r="AM77" s="7"/>
       <c r="AN77" s="7"/>
       <c r="AO77" s="7"/>
-    </row>
-    <row r="78" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP77" s="7"/>
+      <c r="AQ77" s="7"/>
+      <c r="AR77" s="7"/>
+      <c r="AS77" s="7"/>
+    </row>
+    <row r="78" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
       <c r="E78" s="7"/>
@@ -5067,8 +5470,12 @@
       <c r="AM78" s="7"/>
       <c r="AN78" s="7"/>
       <c r="AO78" s="7"/>
-    </row>
-    <row r="79" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP78" s="7"/>
+      <c r="AQ78" s="7"/>
+      <c r="AR78" s="7"/>
+      <c r="AS78" s="7"/>
+    </row>
+    <row r="79" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
       <c r="E79" s="7"/>
@@ -5108,8 +5515,12 @@
       <c r="AM79" s="7"/>
       <c r="AN79" s="7"/>
       <c r="AO79" s="7"/>
-    </row>
-    <row r="80" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP79" s="7"/>
+      <c r="AQ79" s="7"/>
+      <c r="AR79" s="7"/>
+      <c r="AS79" s="7"/>
+    </row>
+    <row r="80" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
       <c r="E80" s="7"/>
@@ -5149,8 +5560,12 @@
       <c r="AM80" s="7"/>
       <c r="AN80" s="7"/>
       <c r="AO80" s="7"/>
-    </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP80" s="7"/>
+      <c r="AQ80" s="7"/>
+      <c r="AR80" s="7"/>
+      <c r="AS80" s="7"/>
+    </row>
+    <row r="81" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
       <c r="E81" s="7"/>
@@ -5190,8 +5605,12 @@
       <c r="AM81" s="7"/>
       <c r="AN81" s="7"/>
       <c r="AO81" s="7"/>
-    </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP81" s="7"/>
+      <c r="AQ81" s="7"/>
+      <c r="AR81" s="7"/>
+      <c r="AS81" s="7"/>
+    </row>
+    <row r="82" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
@@ -5231,8 +5650,12 @@
       <c r="AM82" s="7"/>
       <c r="AN82" s="7"/>
       <c r="AO82" s="7"/>
-    </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP82" s="7"/>
+      <c r="AQ82" s="7"/>
+      <c r="AR82" s="7"/>
+      <c r="AS82" s="7"/>
+    </row>
+    <row r="83" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
       <c r="E83" s="7"/>
@@ -5272,8 +5695,12 @@
       <c r="AM83" s="7"/>
       <c r="AN83" s="7"/>
       <c r="AO83" s="7"/>
-    </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP83" s="7"/>
+      <c r="AQ83" s="7"/>
+      <c r="AR83" s="7"/>
+      <c r="AS83" s="7"/>
+    </row>
+    <row r="84" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
@@ -5313,8 +5740,12 @@
       <c r="AM84" s="7"/>
       <c r="AN84" s="7"/>
       <c r="AO84" s="7"/>
-    </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP84" s="7"/>
+      <c r="AQ84" s="7"/>
+      <c r="AR84" s="7"/>
+      <c r="AS84" s="7"/>
+    </row>
+    <row r="85" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
@@ -5354,8 +5785,12 @@
       <c r="AM85" s="7"/>
       <c r="AN85" s="7"/>
       <c r="AO85" s="7"/>
-    </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP85" s="7"/>
+      <c r="AQ85" s="7"/>
+      <c r="AR85" s="7"/>
+      <c r="AS85" s="7"/>
+    </row>
+    <row r="86" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
       <c r="E86" s="7"/>
@@ -5395,8 +5830,12 @@
       <c r="AM86" s="7"/>
       <c r="AN86" s="7"/>
       <c r="AO86" s="7"/>
-    </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP86" s="7"/>
+      <c r="AQ86" s="7"/>
+      <c r="AR86" s="7"/>
+      <c r="AS86" s="7"/>
+    </row>
+    <row r="87" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
       <c r="E87" s="7"/>
@@ -5436,8 +5875,12 @@
       <c r="AM87" s="7"/>
       <c r="AN87" s="7"/>
       <c r="AO87" s="7"/>
-    </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP87" s="7"/>
+      <c r="AQ87" s="7"/>
+      <c r="AR87" s="7"/>
+      <c r="AS87" s="7"/>
+    </row>
+    <row r="88" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
       <c r="E88" s="7"/>
@@ -5477,8 +5920,12 @@
       <c r="AM88" s="7"/>
       <c r="AN88" s="7"/>
       <c r="AO88" s="7"/>
-    </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP88" s="7"/>
+      <c r="AQ88" s="7"/>
+      <c r="AR88" s="7"/>
+      <c r="AS88" s="7"/>
+    </row>
+    <row r="89" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
       <c r="E89" s="7"/>
@@ -5518,8 +5965,12 @@
       <c r="AM89" s="7"/>
       <c r="AN89" s="7"/>
       <c r="AO89" s="7"/>
-    </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP89" s="7"/>
+      <c r="AQ89" s="7"/>
+      <c r="AR89" s="7"/>
+      <c r="AS89" s="7"/>
+    </row>
+    <row r="90" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
@@ -5559,8 +6010,12 @@
       <c r="AM90" s="7"/>
       <c r="AN90" s="7"/>
       <c r="AO90" s="7"/>
-    </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP90" s="7"/>
+      <c r="AQ90" s="7"/>
+      <c r="AR90" s="7"/>
+      <c r="AS90" s="7"/>
+    </row>
+    <row r="91" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
       <c r="E91" s="7"/>
@@ -5600,8 +6055,12 @@
       <c r="AM91" s="7"/>
       <c r="AN91" s="7"/>
       <c r="AO91" s="7"/>
-    </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP91" s="7"/>
+      <c r="AQ91" s="7"/>
+      <c r="AR91" s="7"/>
+      <c r="AS91" s="7"/>
+    </row>
+    <row r="92" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
@@ -5641,8 +6100,12 @@
       <c r="AM92" s="7"/>
       <c r="AN92" s="7"/>
       <c r="AO92" s="7"/>
-    </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP92" s="7"/>
+      <c r="AQ92" s="7"/>
+      <c r="AR92" s="7"/>
+      <c r="AS92" s="7"/>
+    </row>
+    <row r="93" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
       <c r="E93" s="7"/>
@@ -5682,8 +6145,12 @@
       <c r="AM93" s="7"/>
       <c r="AN93" s="7"/>
       <c r="AO93" s="7"/>
-    </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP93" s="7"/>
+      <c r="AQ93" s="7"/>
+      <c r="AR93" s="7"/>
+      <c r="AS93" s="7"/>
+    </row>
+    <row r="94" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
@@ -5723,8 +6190,12 @@
       <c r="AM94" s="7"/>
       <c r="AN94" s="7"/>
       <c r="AO94" s="7"/>
-    </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP94" s="7"/>
+      <c r="AQ94" s="7"/>
+      <c r="AR94" s="7"/>
+      <c r="AS94" s="7"/>
+    </row>
+    <row r="95" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
       <c r="E95" s="7"/>
@@ -5764,8 +6235,12 @@
       <c r="AM95" s="7"/>
       <c r="AN95" s="7"/>
       <c r="AO95" s="7"/>
-    </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP95" s="7"/>
+      <c r="AQ95" s="7"/>
+      <c r="AR95" s="7"/>
+      <c r="AS95" s="7"/>
+    </row>
+    <row r="96" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
@@ -5805,8 +6280,12 @@
       <c r="AM96" s="7"/>
       <c r="AN96" s="7"/>
       <c r="AO96" s="7"/>
-    </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP96" s="7"/>
+      <c r="AQ96" s="7"/>
+      <c r="AR96" s="7"/>
+      <c r="AS96" s="7"/>
+    </row>
+    <row r="97" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
       <c r="E97" s="7"/>
@@ -5846,8 +6325,12 @@
       <c r="AM97" s="7"/>
       <c r="AN97" s="7"/>
       <c r="AO97" s="7"/>
-    </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP97" s="7"/>
+      <c r="AQ97" s="7"/>
+      <c r="AR97" s="7"/>
+      <c r="AS97" s="7"/>
+    </row>
+    <row r="98" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
@@ -5887,8 +6370,12 @@
       <c r="AM98" s="7"/>
       <c r="AN98" s="7"/>
       <c r="AO98" s="7"/>
-    </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP98" s="7"/>
+      <c r="AQ98" s="7"/>
+      <c r="AR98" s="7"/>
+      <c r="AS98" s="7"/>
+    </row>
+    <row r="99" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
       <c r="E99" s="7"/>
@@ -5928,8 +6415,12 @@
       <c r="AM99" s="7"/>
       <c r="AN99" s="7"/>
       <c r="AO99" s="7"/>
-    </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP99" s="7"/>
+      <c r="AQ99" s="7"/>
+      <c r="AR99" s="7"/>
+      <c r="AS99" s="7"/>
+    </row>
+    <row r="100" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
       <c r="E100" s="7"/>
@@ -5969,8 +6460,12 @@
       <c r="AM100" s="7"/>
       <c r="AN100" s="7"/>
       <c r="AO100" s="7"/>
-    </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP100" s="7"/>
+      <c r="AQ100" s="7"/>
+      <c r="AR100" s="7"/>
+      <c r="AS100" s="7"/>
+    </row>
+    <row r="101" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C101" s="7"/>
       <c r="D101" s="7"/>
       <c r="E101" s="7"/>
@@ -6010,8 +6505,12 @@
       <c r="AM101" s="7"/>
       <c r="AN101" s="7"/>
       <c r="AO101" s="7"/>
-    </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP101" s="7"/>
+      <c r="AQ101" s="7"/>
+      <c r="AR101" s="7"/>
+      <c r="AS101" s="7"/>
+    </row>
+    <row r="102" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C102" s="7"/>
       <c r="D102" s="7"/>
       <c r="E102" s="7"/>
@@ -6051,8 +6550,12 @@
       <c r="AM102" s="7"/>
       <c r="AN102" s="7"/>
       <c r="AO102" s="7"/>
-    </row>
-    <row r="103" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP102" s="7"/>
+      <c r="AQ102" s="7"/>
+      <c r="AR102" s="7"/>
+      <c r="AS102" s="7"/>
+    </row>
+    <row r="103" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C103" s="7"/>
       <c r="D103" s="7"/>
       <c r="E103" s="7"/>
@@ -6092,8 +6595,12 @@
       <c r="AM103" s="7"/>
       <c r="AN103" s="7"/>
       <c r="AO103" s="7"/>
-    </row>
-    <row r="104" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP103" s="7"/>
+      <c r="AQ103" s="7"/>
+      <c r="AR103" s="7"/>
+      <c r="AS103" s="7"/>
+    </row>
+    <row r="104" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C104" s="7"/>
       <c r="D104" s="7"/>
       <c r="E104" s="7"/>
@@ -6133,8 +6640,12 @@
       <c r="AM104" s="7"/>
       <c r="AN104" s="7"/>
       <c r="AO104" s="7"/>
-    </row>
-    <row r="105" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP104" s="7"/>
+      <c r="AQ104" s="7"/>
+      <c r="AR104" s="7"/>
+      <c r="AS104" s="7"/>
+    </row>
+    <row r="105" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C105" s="7"/>
       <c r="D105" s="7"/>
       <c r="E105" s="7"/>
@@ -6174,8 +6685,12 @@
       <c r="AM105" s="7"/>
       <c r="AN105" s="7"/>
       <c r="AO105" s="7"/>
-    </row>
-    <row r="106" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP105" s="7"/>
+      <c r="AQ105" s="7"/>
+      <c r="AR105" s="7"/>
+      <c r="AS105" s="7"/>
+    </row>
+    <row r="106" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C106" s="7"/>
       <c r="D106" s="7"/>
       <c r="E106" s="7"/>
@@ -6215,8 +6730,12 @@
       <c r="AM106" s="7"/>
       <c r="AN106" s="7"/>
       <c r="AO106" s="7"/>
-    </row>
-    <row r="107" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP106" s="7"/>
+      <c r="AQ106" s="7"/>
+      <c r="AR106" s="7"/>
+      <c r="AS106" s="7"/>
+    </row>
+    <row r="107" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C107" s="7"/>
       <c r="D107" s="7"/>
       <c r="E107" s="7"/>
@@ -6256,8 +6775,12 @@
       <c r="AM107" s="7"/>
       <c r="AN107" s="7"/>
       <c r="AO107" s="7"/>
-    </row>
-    <row r="108" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP107" s="7"/>
+      <c r="AQ107" s="7"/>
+      <c r="AR107" s="7"/>
+      <c r="AS107" s="7"/>
+    </row>
+    <row r="108" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C108" s="7"/>
       <c r="D108" s="7"/>
       <c r="E108" s="7"/>
@@ -6297,8 +6820,12 @@
       <c r="AM108" s="7"/>
       <c r="AN108" s="7"/>
       <c r="AO108" s="7"/>
-    </row>
-    <row r="109" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP108" s="7"/>
+      <c r="AQ108" s="7"/>
+      <c r="AR108" s="7"/>
+      <c r="AS108" s="7"/>
+    </row>
+    <row r="109" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C109" s="7"/>
       <c r="D109" s="7"/>
       <c r="E109" s="7"/>
@@ -6338,8 +6865,12 @@
       <c r="AM109" s="7"/>
       <c r="AN109" s="7"/>
       <c r="AO109" s="7"/>
-    </row>
-    <row r="110" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP109" s="7"/>
+      <c r="AQ109" s="7"/>
+      <c r="AR109" s="7"/>
+      <c r="AS109" s="7"/>
+    </row>
+    <row r="110" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C110" s="7"/>
       <c r="D110" s="7"/>
       <c r="E110" s="7"/>
@@ -6379,8 +6910,12 @@
       <c r="AM110" s="7"/>
       <c r="AN110" s="7"/>
       <c r="AO110" s="7"/>
-    </row>
-    <row r="111" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP110" s="7"/>
+      <c r="AQ110" s="7"/>
+      <c r="AR110" s="7"/>
+      <c r="AS110" s="7"/>
+    </row>
+    <row r="111" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C111" s="7"/>
       <c r="D111" s="7"/>
       <c r="E111" s="7"/>
@@ -6420,8 +6955,12 @@
       <c r="AM111" s="7"/>
       <c r="AN111" s="7"/>
       <c r="AO111" s="7"/>
-    </row>
-    <row r="112" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP111" s="7"/>
+      <c r="AQ111" s="7"/>
+      <c r="AR111" s="7"/>
+      <c r="AS111" s="7"/>
+    </row>
+    <row r="112" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C112" s="7"/>
       <c r="D112" s="7"/>
       <c r="E112" s="7"/>
@@ -6461,8 +7000,12 @@
       <c r="AM112" s="7"/>
       <c r="AN112" s="7"/>
       <c r="AO112" s="7"/>
-    </row>
-    <row r="113" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP112" s="7"/>
+      <c r="AQ112" s="7"/>
+      <c r="AR112" s="7"/>
+      <c r="AS112" s="7"/>
+    </row>
+    <row r="113" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C113" s="7"/>
       <c r="D113" s="7"/>
       <c r="E113" s="7"/>
@@ -6502,8 +7045,12 @@
       <c r="AM113" s="7"/>
       <c r="AN113" s="7"/>
       <c r="AO113" s="7"/>
-    </row>
-    <row r="114" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP113" s="7"/>
+      <c r="AQ113" s="7"/>
+      <c r="AR113" s="7"/>
+      <c r="AS113" s="7"/>
+    </row>
+    <row r="114" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7"/>
@@ -6543,8 +7090,12 @@
       <c r="AM114" s="7"/>
       <c r="AN114" s="7"/>
       <c r="AO114" s="7"/>
-    </row>
-    <row r="115" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP114" s="7"/>
+      <c r="AQ114" s="7"/>
+      <c r="AR114" s="7"/>
+      <c r="AS114" s="7"/>
+    </row>
+    <row r="115" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C115" s="7"/>
       <c r="D115" s="7"/>
       <c r="E115" s="7"/>
@@ -6584,8 +7135,12 @@
       <c r="AM115" s="7"/>
       <c r="AN115" s="7"/>
       <c r="AO115" s="7"/>
-    </row>
-    <row r="116" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP115" s="7"/>
+      <c r="AQ115" s="7"/>
+      <c r="AR115" s="7"/>
+      <c r="AS115" s="7"/>
+    </row>
+    <row r="116" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C116" s="7"/>
       <c r="D116" s="7"/>
       <c r="E116" s="7"/>
@@ -6625,8 +7180,12 @@
       <c r="AM116" s="7"/>
       <c r="AN116" s="7"/>
       <c r="AO116" s="7"/>
-    </row>
-    <row r="117" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP116" s="7"/>
+      <c r="AQ116" s="7"/>
+      <c r="AR116" s="7"/>
+      <c r="AS116" s="7"/>
+    </row>
+    <row r="117" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C117" s="7"/>
       <c r="D117" s="7"/>
       <c r="E117" s="7"/>
@@ -6666,8 +7225,12 @@
       <c r="AM117" s="7"/>
       <c r="AN117" s="7"/>
       <c r="AO117" s="7"/>
-    </row>
-    <row r="118" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP117" s="7"/>
+      <c r="AQ117" s="7"/>
+      <c r="AR117" s="7"/>
+      <c r="AS117" s="7"/>
+    </row>
+    <row r="118" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C118" s="7"/>
       <c r="D118" s="7"/>
       <c r="E118" s="7"/>
@@ -6707,8 +7270,12 @@
       <c r="AM118" s="7"/>
       <c r="AN118" s="7"/>
       <c r="AO118" s="7"/>
-    </row>
-    <row r="119" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP118" s="7"/>
+      <c r="AQ118" s="7"/>
+      <c r="AR118" s="7"/>
+      <c r="AS118" s="7"/>
+    </row>
+    <row r="119" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C119" s="7"/>
       <c r="D119" s="7"/>
       <c r="E119" s="7"/>
@@ -6748,8 +7315,12 @@
       <c r="AM119" s="7"/>
       <c r="AN119" s="7"/>
       <c r="AO119" s="7"/>
-    </row>
-    <row r="120" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP119" s="7"/>
+      <c r="AQ119" s="7"/>
+      <c r="AR119" s="7"/>
+      <c r="AS119" s="7"/>
+    </row>
+    <row r="120" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C120" s="7"/>
       <c r="D120" s="7"/>
       <c r="E120" s="7"/>
@@ -6789,8 +7360,12 @@
       <c r="AM120" s="7"/>
       <c r="AN120" s="7"/>
       <c r="AO120" s="7"/>
-    </row>
-    <row r="121" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP120" s="7"/>
+      <c r="AQ120" s="7"/>
+      <c r="AR120" s="7"/>
+      <c r="AS120" s="7"/>
+    </row>
+    <row r="121" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C121" s="7"/>
       <c r="D121" s="7"/>
       <c r="E121" s="7"/>
@@ -6830,8 +7405,12 @@
       <c r="AM121" s="7"/>
       <c r="AN121" s="7"/>
       <c r="AO121" s="7"/>
-    </row>
-    <row r="122" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP121" s="7"/>
+      <c r="AQ121" s="7"/>
+      <c r="AR121" s="7"/>
+      <c r="AS121" s="7"/>
+    </row>
+    <row r="122" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C122" s="7"/>
       <c r="D122" s="7"/>
       <c r="E122" s="7"/>
@@ -6871,8 +7450,12 @@
       <c r="AM122" s="7"/>
       <c r="AN122" s="7"/>
       <c r="AO122" s="7"/>
-    </row>
-    <row r="123" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP122" s="7"/>
+      <c r="AQ122" s="7"/>
+      <c r="AR122" s="7"/>
+      <c r="AS122" s="7"/>
+    </row>
+    <row r="123" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C123" s="7"/>
       <c r="D123" s="7"/>
       <c r="E123" s="7"/>
@@ -6912,8 +7495,12 @@
       <c r="AM123" s="7"/>
       <c r="AN123" s="7"/>
       <c r="AO123" s="7"/>
-    </row>
-    <row r="124" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP123" s="7"/>
+      <c r="AQ123" s="7"/>
+      <c r="AR123" s="7"/>
+      <c r="AS123" s="7"/>
+    </row>
+    <row r="124" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
@@ -6953,8 +7540,12 @@
       <c r="AM124" s="7"/>
       <c r="AN124" s="7"/>
       <c r="AO124" s="7"/>
-    </row>
-    <row r="125" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP124" s="7"/>
+      <c r="AQ124" s="7"/>
+      <c r="AR124" s="7"/>
+      <c r="AS124" s="7"/>
+    </row>
+    <row r="125" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
@@ -6994,8 +7585,12 @@
       <c r="AM125" s="7"/>
       <c r="AN125" s="7"/>
       <c r="AO125" s="7"/>
-    </row>
-    <row r="126" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP125" s="7"/>
+      <c r="AQ125" s="7"/>
+      <c r="AR125" s="7"/>
+      <c r="AS125" s="7"/>
+    </row>
+    <row r="126" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
@@ -7035,8 +7630,12 @@
       <c r="AM126" s="7"/>
       <c r="AN126" s="7"/>
       <c r="AO126" s="7"/>
-    </row>
-    <row r="127" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP126" s="7"/>
+      <c r="AQ126" s="7"/>
+      <c r="AR126" s="7"/>
+      <c r="AS126" s="7"/>
+    </row>
+    <row r="127" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C127" s="7"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
@@ -7076,8 +7675,12 @@
       <c r="AM127" s="7"/>
       <c r="AN127" s="7"/>
       <c r="AO127" s="7"/>
-    </row>
-    <row r="128" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP127" s="7"/>
+      <c r="AQ127" s="7"/>
+      <c r="AR127" s="7"/>
+      <c r="AS127" s="7"/>
+    </row>
+    <row r="128" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
       <c r="E128" s="7"/>
@@ -7117,8 +7720,12 @@
       <c r="AM128" s="7"/>
       <c r="AN128" s="7"/>
       <c r="AO128" s="7"/>
-    </row>
-    <row r="129" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP128" s="7"/>
+      <c r="AQ128" s="7"/>
+      <c r="AR128" s="7"/>
+      <c r="AS128" s="7"/>
+    </row>
+    <row r="129" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C129" s="7"/>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
@@ -7158,8 +7765,12 @@
       <c r="AM129" s="7"/>
       <c r="AN129" s="7"/>
       <c r="AO129" s="7"/>
-    </row>
-    <row r="130" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP129" s="7"/>
+      <c r="AQ129" s="7"/>
+      <c r="AR129" s="7"/>
+      <c r="AS129" s="7"/>
+    </row>
+    <row r="130" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
@@ -7199,8 +7810,12 @@
       <c r="AM130" s="7"/>
       <c r="AN130" s="7"/>
       <c r="AO130" s="7"/>
-    </row>
-    <row r="131" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP130" s="7"/>
+      <c r="AQ130" s="7"/>
+      <c r="AR130" s="7"/>
+      <c r="AS130" s="7"/>
+    </row>
+    <row r="131" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C131" s="7"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
@@ -7240,8 +7855,12 @@
       <c r="AM131" s="7"/>
       <c r="AN131" s="7"/>
       <c r="AO131" s="7"/>
-    </row>
-    <row r="132" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP131" s="7"/>
+      <c r="AQ131" s="7"/>
+      <c r="AR131" s="7"/>
+      <c r="AS131" s="7"/>
+    </row>
+    <row r="132" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7"/>
@@ -7281,8 +7900,12 @@
       <c r="AM132" s="7"/>
       <c r="AN132" s="7"/>
       <c r="AO132" s="7"/>
-    </row>
-    <row r="133" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP132" s="7"/>
+      <c r="AQ132" s="7"/>
+      <c r="AR132" s="7"/>
+      <c r="AS132" s="7"/>
+    </row>
+    <row r="133" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C133" s="7"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
@@ -7322,8 +7945,12 @@
       <c r="AM133" s="7"/>
       <c r="AN133" s="7"/>
       <c r="AO133" s="7"/>
-    </row>
-    <row r="134" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP133" s="7"/>
+      <c r="AQ133" s="7"/>
+      <c r="AR133" s="7"/>
+      <c r="AS133" s="7"/>
+    </row>
+    <row r="134" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
@@ -7363,8 +7990,12 @@
       <c r="AM134" s="7"/>
       <c r="AN134" s="7"/>
       <c r="AO134" s="7"/>
-    </row>
-    <row r="135" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP134" s="7"/>
+      <c r="AQ134" s="7"/>
+      <c r="AR134" s="7"/>
+      <c r="AS134" s="7"/>
+    </row>
+    <row r="135" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C135" s="7"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
@@ -7404,8 +8035,12 @@
       <c r="AM135" s="7"/>
       <c r="AN135" s="7"/>
       <c r="AO135" s="7"/>
-    </row>
-    <row r="136" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP135" s="7"/>
+      <c r="AQ135" s="7"/>
+      <c r="AR135" s="7"/>
+      <c r="AS135" s="7"/>
+    </row>
+    <row r="136" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C136" s="7"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7"/>
@@ -7445,8 +8080,12 @@
       <c r="AM136" s="7"/>
       <c r="AN136" s="7"/>
       <c r="AO136" s="7"/>
-    </row>
-    <row r="137" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP136" s="7"/>
+      <c r="AQ136" s="7"/>
+      <c r="AR136" s="7"/>
+      <c r="AS136" s="7"/>
+    </row>
+    <row r="137" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C137" s="7"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
@@ -7486,8 +8125,12 @@
       <c r="AM137" s="7"/>
       <c r="AN137" s="7"/>
       <c r="AO137" s="7"/>
-    </row>
-    <row r="138" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP137" s="7"/>
+      <c r="AQ137" s="7"/>
+      <c r="AR137" s="7"/>
+      <c r="AS137" s="7"/>
+    </row>
+    <row r="138" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C138" s="7"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7"/>
@@ -7527,8 +8170,12 @@
       <c r="AM138" s="7"/>
       <c r="AN138" s="7"/>
       <c r="AO138" s="7"/>
-    </row>
-    <row r="139" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP138" s="7"/>
+      <c r="AQ138" s="7"/>
+      <c r="AR138" s="7"/>
+      <c r="AS138" s="7"/>
+    </row>
+    <row r="139" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C139" s="7"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7"/>
@@ -7568,8 +8215,12 @@
       <c r="AM139" s="7"/>
       <c r="AN139" s="7"/>
       <c r="AO139" s="7"/>
-    </row>
-    <row r="140" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP139" s="7"/>
+      <c r="AQ139" s="7"/>
+      <c r="AR139" s="7"/>
+      <c r="AS139" s="7"/>
+    </row>
+    <row r="140" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7"/>
@@ -7609,8 +8260,12 @@
       <c r="AM140" s="7"/>
       <c r="AN140" s="7"/>
       <c r="AO140" s="7"/>
-    </row>
-    <row r="141" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP140" s="7"/>
+      <c r="AQ140" s="7"/>
+      <c r="AR140" s="7"/>
+      <c r="AS140" s="7"/>
+    </row>
+    <row r="141" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C141" s="7"/>
       <c r="D141" s="7"/>
       <c r="E141" s="7"/>
@@ -7650,8 +8305,12 @@
       <c r="AM141" s="7"/>
       <c r="AN141" s="7"/>
       <c r="AO141" s="7"/>
-    </row>
-    <row r="142" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP141" s="7"/>
+      <c r="AQ141" s="7"/>
+      <c r="AR141" s="7"/>
+      <c r="AS141" s="7"/>
+    </row>
+    <row r="142" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C142" s="7"/>
       <c r="D142" s="7"/>
       <c r="E142" s="7"/>
@@ -7691,8 +8350,12 @@
       <c r="AM142" s="7"/>
       <c r="AN142" s="7"/>
       <c r="AO142" s="7"/>
-    </row>
-    <row r="143" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP142" s="7"/>
+      <c r="AQ142" s="7"/>
+      <c r="AR142" s="7"/>
+      <c r="AS142" s="7"/>
+    </row>
+    <row r="143" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C143" s="7"/>
       <c r="D143" s="7"/>
       <c r="E143" s="7"/>
@@ -7732,8 +8395,12 @@
       <c r="AM143" s="7"/>
       <c r="AN143" s="7"/>
       <c r="AO143" s="7"/>
-    </row>
-    <row r="144" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP143" s="7"/>
+      <c r="AQ143" s="7"/>
+      <c r="AR143" s="7"/>
+      <c r="AS143" s="7"/>
+    </row>
+    <row r="144" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C144" s="7"/>
       <c r="D144" s="7"/>
       <c r="E144" s="7"/>
@@ -7773,8 +8440,12 @@
       <c r="AM144" s="7"/>
       <c r="AN144" s="7"/>
       <c r="AO144" s="7"/>
-    </row>
-    <row r="145" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP144" s="7"/>
+      <c r="AQ144" s="7"/>
+      <c r="AR144" s="7"/>
+      <c r="AS144" s="7"/>
+    </row>
+    <row r="145" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C145" s="7"/>
       <c r="D145" s="7"/>
       <c r="E145" s="7"/>
@@ -7814,8 +8485,12 @@
       <c r="AM145" s="7"/>
       <c r="AN145" s="7"/>
       <c r="AO145" s="7"/>
-    </row>
-    <row r="146" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP145" s="7"/>
+      <c r="AQ145" s="7"/>
+      <c r="AR145" s="7"/>
+      <c r="AS145" s="7"/>
+    </row>
+    <row r="146" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C146" s="7"/>
       <c r="D146" s="7"/>
       <c r="E146" s="7"/>
@@ -7855,8 +8530,12 @@
       <c r="AM146" s="7"/>
       <c r="AN146" s="7"/>
       <c r="AO146" s="7"/>
-    </row>
-    <row r="147" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP146" s="7"/>
+      <c r="AQ146" s="7"/>
+      <c r="AR146" s="7"/>
+      <c r="AS146" s="7"/>
+    </row>
+    <row r="147" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C147" s="7"/>
       <c r="D147" s="7"/>
       <c r="E147" s="7"/>
@@ -7896,8 +8575,12 @@
       <c r="AM147" s="7"/>
       <c r="AN147" s="7"/>
       <c r="AO147" s="7"/>
-    </row>
-    <row r="148" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP147" s="7"/>
+      <c r="AQ147" s="7"/>
+      <c r="AR147" s="7"/>
+      <c r="AS147" s="7"/>
+    </row>
+    <row r="148" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C148" s="7"/>
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
@@ -7937,8 +8620,12 @@
       <c r="AM148" s="7"/>
       <c r="AN148" s="7"/>
       <c r="AO148" s="7"/>
-    </row>
-    <row r="149" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP148" s="7"/>
+      <c r="AQ148" s="7"/>
+      <c r="AR148" s="7"/>
+      <c r="AS148" s="7"/>
+    </row>
+    <row r="149" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C149" s="7"/>
       <c r="D149" s="7"/>
       <c r="E149" s="7"/>
@@ -7978,8 +8665,12 @@
       <c r="AM149" s="7"/>
       <c r="AN149" s="7"/>
       <c r="AO149" s="7"/>
-    </row>
-    <row r="150" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP149" s="7"/>
+      <c r="AQ149" s="7"/>
+      <c r="AR149" s="7"/>
+      <c r="AS149" s="7"/>
+    </row>
+    <row r="150" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C150" s="7"/>
       <c r="D150" s="7"/>
       <c r="E150" s="7"/>
@@ -8019,8 +8710,12 @@
       <c r="AM150" s="7"/>
       <c r="AN150" s="7"/>
       <c r="AO150" s="7"/>
-    </row>
-    <row r="151" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP150" s="7"/>
+      <c r="AQ150" s="7"/>
+      <c r="AR150" s="7"/>
+      <c r="AS150" s="7"/>
+    </row>
+    <row r="151" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C151" s="7"/>
       <c r="D151" s="7"/>
       <c r="E151" s="7"/>
@@ -8060,8 +8755,12 @@
       <c r="AM151" s="7"/>
       <c r="AN151" s="7"/>
       <c r="AO151" s="7"/>
-    </row>
-    <row r="152" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP151" s="7"/>
+      <c r="AQ151" s="7"/>
+      <c r="AR151" s="7"/>
+      <c r="AS151" s="7"/>
+    </row>
+    <row r="152" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C152" s="7"/>
       <c r="D152" s="7"/>
       <c r="E152" s="7"/>
@@ -8101,8 +8800,12 @@
       <c r="AM152" s="7"/>
       <c r="AN152" s="7"/>
       <c r="AO152" s="7"/>
-    </row>
-    <row r="153" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP152" s="7"/>
+      <c r="AQ152" s="7"/>
+      <c r="AR152" s="7"/>
+      <c r="AS152" s="7"/>
+    </row>
+    <row r="153" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C153" s="7"/>
       <c r="D153" s="7"/>
       <c r="E153" s="7"/>
@@ -8142,8 +8845,12 @@
       <c r="AM153" s="7"/>
       <c r="AN153" s="7"/>
       <c r="AO153" s="7"/>
-    </row>
-    <row r="154" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP153" s="7"/>
+      <c r="AQ153" s="7"/>
+      <c r="AR153" s="7"/>
+      <c r="AS153" s="7"/>
+    </row>
+    <row r="154" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C154" s="7"/>
       <c r="D154" s="7"/>
       <c r="E154" s="7"/>
@@ -8183,8 +8890,12 @@
       <c r="AM154" s="7"/>
       <c r="AN154" s="7"/>
       <c r="AO154" s="7"/>
-    </row>
-    <row r="155" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP154" s="7"/>
+      <c r="AQ154" s="7"/>
+      <c r="AR154" s="7"/>
+      <c r="AS154" s="7"/>
+    </row>
+    <row r="155" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C155" s="7"/>
       <c r="D155" s="7"/>
       <c r="E155" s="7"/>
@@ -8224,8 +8935,12 @@
       <c r="AM155" s="7"/>
       <c r="AN155" s="7"/>
       <c r="AO155" s="7"/>
-    </row>
-    <row r="156" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP155" s="7"/>
+      <c r="AQ155" s="7"/>
+      <c r="AR155" s="7"/>
+      <c r="AS155" s="7"/>
+    </row>
+    <row r="156" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C156" s="7"/>
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
@@ -8265,8 +8980,12 @@
       <c r="AM156" s="7"/>
       <c r="AN156" s="7"/>
       <c r="AO156" s="7"/>
-    </row>
-    <row r="157" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP156" s="7"/>
+      <c r="AQ156" s="7"/>
+      <c r="AR156" s="7"/>
+      <c r="AS156" s="7"/>
+    </row>
+    <row r="157" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C157" s="7"/>
       <c r="D157" s="7"/>
       <c r="E157" s="7"/>
@@ -8306,8 +9025,12 @@
       <c r="AM157" s="7"/>
       <c r="AN157" s="7"/>
       <c r="AO157" s="7"/>
-    </row>
-    <row r="158" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP157" s="7"/>
+      <c r="AQ157" s="7"/>
+      <c r="AR157" s="7"/>
+      <c r="AS157" s="7"/>
+    </row>
+    <row r="158" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C158" s="7"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7"/>
@@ -8347,8 +9070,12 @@
       <c r="AM158" s="7"/>
       <c r="AN158" s="7"/>
       <c r="AO158" s="7"/>
-    </row>
-    <row r="159" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP158" s="7"/>
+      <c r="AQ158" s="7"/>
+      <c r="AR158" s="7"/>
+      <c r="AS158" s="7"/>
+    </row>
+    <row r="159" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C159" s="7"/>
       <c r="D159" s="7"/>
       <c r="E159" s="7"/>
@@ -8388,8 +9115,12 @@
       <c r="AM159" s="7"/>
       <c r="AN159" s="7"/>
       <c r="AO159" s="7"/>
-    </row>
-    <row r="160" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP159" s="7"/>
+      <c r="AQ159" s="7"/>
+      <c r="AR159" s="7"/>
+      <c r="AS159" s="7"/>
+    </row>
+    <row r="160" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C160" s="7"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7"/>
@@ -8429,8 +9160,12 @@
       <c r="AM160" s="7"/>
       <c r="AN160" s="7"/>
       <c r="AO160" s="7"/>
-    </row>
-    <row r="161" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP160" s="7"/>
+      <c r="AQ160" s="7"/>
+      <c r="AR160" s="7"/>
+      <c r="AS160" s="7"/>
+    </row>
+    <row r="161" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C161" s="7"/>
       <c r="D161" s="7"/>
       <c r="E161" s="7"/>
@@ -8470,8 +9205,12 @@
       <c r="AM161" s="7"/>
       <c r="AN161" s="7"/>
       <c r="AO161" s="7"/>
-    </row>
-    <row r="162" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP161" s="7"/>
+      <c r="AQ161" s="7"/>
+      <c r="AR161" s="7"/>
+      <c r="AS161" s="7"/>
+    </row>
+    <row r="162" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C162" s="7"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7"/>
@@ -8511,8 +9250,12 @@
       <c r="AM162" s="7"/>
       <c r="AN162" s="7"/>
       <c r="AO162" s="7"/>
-    </row>
-    <row r="163" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP162" s="7"/>
+      <c r="AQ162" s="7"/>
+      <c r="AR162" s="7"/>
+      <c r="AS162" s="7"/>
+    </row>
+    <row r="163" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C163" s="7"/>
       <c r="D163" s="7"/>
       <c r="E163" s="7"/>
@@ -8552,8 +9295,12 @@
       <c r="AM163" s="7"/>
       <c r="AN163" s="7"/>
       <c r="AO163" s="7"/>
-    </row>
-    <row r="164" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP163" s="7"/>
+      <c r="AQ163" s="7"/>
+      <c r="AR163" s="7"/>
+      <c r="AS163" s="7"/>
+    </row>
+    <row r="164" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C164" s="7"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7"/>
@@ -8593,8 +9340,12 @@
       <c r="AM164" s="7"/>
       <c r="AN164" s="7"/>
       <c r="AO164" s="7"/>
-    </row>
-    <row r="165" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP164" s="7"/>
+      <c r="AQ164" s="7"/>
+      <c r="AR164" s="7"/>
+      <c r="AS164" s="7"/>
+    </row>
+    <row r="165" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C165" s="7"/>
       <c r="D165" s="7"/>
       <c r="E165" s="7"/>
@@ -8634,8 +9385,12 @@
       <c r="AM165" s="7"/>
       <c r="AN165" s="7"/>
       <c r="AO165" s="7"/>
-    </row>
-    <row r="166" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP165" s="7"/>
+      <c r="AQ165" s="7"/>
+      <c r="AR165" s="7"/>
+      <c r="AS165" s="7"/>
+    </row>
+    <row r="166" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C166" s="7"/>
       <c r="D166" s="7"/>
       <c r="E166" s="7"/>
@@ -8675,8 +9430,12 @@
       <c r="AM166" s="7"/>
       <c r="AN166" s="7"/>
       <c r="AO166" s="7"/>
-    </row>
-    <row r="167" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP166" s="7"/>
+      <c r="AQ166" s="7"/>
+      <c r="AR166" s="7"/>
+      <c r="AS166" s="7"/>
+    </row>
+    <row r="167" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
       <c r="E167" s="7"/>
@@ -8716,8 +9475,12 @@
       <c r="AM167" s="7"/>
       <c r="AN167" s="7"/>
       <c r="AO167" s="7"/>
-    </row>
-    <row r="168" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP167" s="7"/>
+      <c r="AQ167" s="7"/>
+      <c r="AR167" s="7"/>
+      <c r="AS167" s="7"/>
+    </row>
+    <row r="168" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C168" s="7"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7"/>
@@ -8757,8 +9520,12 @@
       <c r="AM168" s="7"/>
       <c r="AN168" s="7"/>
       <c r="AO168" s="7"/>
-    </row>
-    <row r="169" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP168" s="7"/>
+      <c r="AQ168" s="7"/>
+      <c r="AR168" s="7"/>
+      <c r="AS168" s="7"/>
+    </row>
+    <row r="169" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C169" s="7"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7"/>
@@ -8798,8 +9565,12 @@
       <c r="AM169" s="7"/>
       <c r="AN169" s="7"/>
       <c r="AO169" s="7"/>
-    </row>
-    <row r="170" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP169" s="7"/>
+      <c r="AQ169" s="7"/>
+      <c r="AR169" s="7"/>
+      <c r="AS169" s="7"/>
+    </row>
+    <row r="170" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C170" s="7"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7"/>
@@ -8839,8 +9610,12 @@
       <c r="AM170" s="7"/>
       <c r="AN170" s="7"/>
       <c r="AO170" s="7"/>
-    </row>
-    <row r="171" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP170" s="7"/>
+      <c r="AQ170" s="7"/>
+      <c r="AR170" s="7"/>
+      <c r="AS170" s="7"/>
+    </row>
+    <row r="171" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C171" s="7"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
@@ -8880,8 +9655,12 @@
       <c r="AM171" s="7"/>
       <c r="AN171" s="7"/>
       <c r="AO171" s="7"/>
-    </row>
-    <row r="172" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP171" s="7"/>
+      <c r="AQ171" s="7"/>
+      <c r="AR171" s="7"/>
+      <c r="AS171" s="7"/>
+    </row>
+    <row r="172" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
@@ -8921,8 +9700,12 @@
       <c r="AM172" s="7"/>
       <c r="AN172" s="7"/>
       <c r="AO172" s="7"/>
-    </row>
-    <row r="173" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP172" s="7"/>
+      <c r="AQ172" s="7"/>
+      <c r="AR172" s="7"/>
+      <c r="AS172" s="7"/>
+    </row>
+    <row r="173" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C173" s="7"/>
       <c r="D173" s="7"/>
       <c r="E173" s="7"/>
@@ -8962,8 +9745,12 @@
       <c r="AM173" s="7"/>
       <c r="AN173" s="7"/>
       <c r="AO173" s="7"/>
-    </row>
-    <row r="174" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP173" s="7"/>
+      <c r="AQ173" s="7"/>
+      <c r="AR173" s="7"/>
+      <c r="AS173" s="7"/>
+    </row>
+    <row r="174" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C174" s="7"/>
       <c r="D174" s="7"/>
       <c r="E174" s="7"/>
@@ -9003,8 +9790,12 @@
       <c r="AM174" s="7"/>
       <c r="AN174" s="7"/>
       <c r="AO174" s="7"/>
-    </row>
-    <row r="175" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP174" s="7"/>
+      <c r="AQ174" s="7"/>
+      <c r="AR174" s="7"/>
+      <c r="AS174" s="7"/>
+    </row>
+    <row r="175" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C175" s="7"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7"/>
@@ -9044,8 +9835,12 @@
       <c r="AM175" s="7"/>
       <c r="AN175" s="7"/>
       <c r="AO175" s="7"/>
-    </row>
-    <row r="176" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP175" s="7"/>
+      <c r="AQ175" s="7"/>
+      <c r="AR175" s="7"/>
+      <c r="AS175" s="7"/>
+    </row>
+    <row r="176" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C176" s="7"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7"/>
@@ -9085,8 +9880,12 @@
       <c r="AM176" s="7"/>
       <c r="AN176" s="7"/>
       <c r="AO176" s="7"/>
-    </row>
-    <row r="177" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP176" s="7"/>
+      <c r="AQ176" s="7"/>
+      <c r="AR176" s="7"/>
+      <c r="AS176" s="7"/>
+    </row>
+    <row r="177" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C177" s="7"/>
       <c r="D177" s="7"/>
       <c r="E177" s="7"/>
@@ -9126,8 +9925,12 @@
       <c r="AM177" s="7"/>
       <c r="AN177" s="7"/>
       <c r="AO177" s="7"/>
-    </row>
-    <row r="178" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP177" s="7"/>
+      <c r="AQ177" s="7"/>
+      <c r="AR177" s="7"/>
+      <c r="AS177" s="7"/>
+    </row>
+    <row r="178" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C178" s="7"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7"/>
@@ -9167,8 +9970,12 @@
       <c r="AM178" s="7"/>
       <c r="AN178" s="7"/>
       <c r="AO178" s="7"/>
-    </row>
-    <row r="179" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP178" s="7"/>
+      <c r="AQ178" s="7"/>
+      <c r="AR178" s="7"/>
+      <c r="AS178" s="7"/>
+    </row>
+    <row r="179" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C179" s="7"/>
       <c r="D179" s="7"/>
       <c r="E179" s="7"/>
@@ -9208,8 +10015,12 @@
       <c r="AM179" s="7"/>
       <c r="AN179" s="7"/>
       <c r="AO179" s="7"/>
-    </row>
-    <row r="180" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP179" s="7"/>
+      <c r="AQ179" s="7"/>
+      <c r="AR179" s="7"/>
+      <c r="AS179" s="7"/>
+    </row>
+    <row r="180" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C180" s="7"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7"/>
@@ -9249,8 +10060,12 @@
       <c r="AM180" s="7"/>
       <c r="AN180" s="7"/>
       <c r="AO180" s="7"/>
-    </row>
-    <row r="181" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP180" s="7"/>
+      <c r="AQ180" s="7"/>
+      <c r="AR180" s="7"/>
+      <c r="AS180" s="7"/>
+    </row>
+    <row r="181" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C181" s="7"/>
       <c r="D181" s="7"/>
       <c r="E181" s="7"/>
@@ -9290,8 +10105,12 @@
       <c r="AM181" s="7"/>
       <c r="AN181" s="7"/>
       <c r="AO181" s="7"/>
-    </row>
-    <row r="182" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP181" s="7"/>
+      <c r="AQ181" s="7"/>
+      <c r="AR181" s="7"/>
+      <c r="AS181" s="7"/>
+    </row>
+    <row r="182" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C182" s="7"/>
       <c r="D182" s="7"/>
       <c r="E182" s="7"/>
@@ -9331,8 +10150,12 @@
       <c r="AM182" s="7"/>
       <c r="AN182" s="7"/>
       <c r="AO182" s="7"/>
-    </row>
-    <row r="183" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP182" s="7"/>
+      <c r="AQ182" s="7"/>
+      <c r="AR182" s="7"/>
+      <c r="AS182" s="7"/>
+    </row>
+    <row r="183" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C183" s="7"/>
       <c r="D183" s="7"/>
       <c r="E183" s="7"/>
@@ -9372,8 +10195,12 @@
       <c r="AM183" s="7"/>
       <c r="AN183" s="7"/>
       <c r="AO183" s="7"/>
-    </row>
-    <row r="184" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP183" s="7"/>
+      <c r="AQ183" s="7"/>
+      <c r="AR183" s="7"/>
+      <c r="AS183" s="7"/>
+    </row>
+    <row r="184" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C184" s="7"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
@@ -9413,8 +10240,12 @@
       <c r="AM184" s="7"/>
       <c r="AN184" s="7"/>
       <c r="AO184" s="7"/>
-    </row>
-    <row r="185" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP184" s="7"/>
+      <c r="AQ184" s="7"/>
+      <c r="AR184" s="7"/>
+      <c r="AS184" s="7"/>
+    </row>
+    <row r="185" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C185" s="7"/>
       <c r="D185" s="7"/>
       <c r="E185" s="7"/>
@@ -9454,8 +10285,12 @@
       <c r="AM185" s="7"/>
       <c r="AN185" s="7"/>
       <c r="AO185" s="7"/>
-    </row>
-    <row r="186" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP185" s="7"/>
+      <c r="AQ185" s="7"/>
+      <c r="AR185" s="7"/>
+      <c r="AS185" s="7"/>
+    </row>
+    <row r="186" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C186" s="7"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7"/>
@@ -9495,8 +10330,12 @@
       <c r="AM186" s="7"/>
       <c r="AN186" s="7"/>
       <c r="AO186" s="7"/>
-    </row>
-    <row r="187" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP186" s="7"/>
+      <c r="AQ186" s="7"/>
+      <c r="AR186" s="7"/>
+      <c r="AS186" s="7"/>
+    </row>
+    <row r="187" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C187" s="7"/>
       <c r="D187" s="7"/>
       <c r="E187" s="7"/>
@@ -9536,8 +10375,12 @@
       <c r="AM187" s="7"/>
       <c r="AN187" s="7"/>
       <c r="AO187" s="7"/>
-    </row>
-    <row r="188" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP187" s="7"/>
+      <c r="AQ187" s="7"/>
+      <c r="AR187" s="7"/>
+      <c r="AS187" s="7"/>
+    </row>
+    <row r="188" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C188" s="7"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7"/>
@@ -9577,8 +10420,12 @@
       <c r="AM188" s="7"/>
       <c r="AN188" s="7"/>
       <c r="AO188" s="7"/>
-    </row>
-    <row r="189" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP188" s="7"/>
+      <c r="AQ188" s="7"/>
+      <c r="AR188" s="7"/>
+      <c r="AS188" s="7"/>
+    </row>
+    <row r="189" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C189" s="7"/>
       <c r="D189" s="7"/>
       <c r="E189" s="7"/>
@@ -9618,8 +10465,12 @@
       <c r="AM189" s="7"/>
       <c r="AN189" s="7"/>
       <c r="AO189" s="7"/>
-    </row>
-    <row r="190" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP189" s="7"/>
+      <c r="AQ189" s="7"/>
+      <c r="AR189" s="7"/>
+      <c r="AS189" s="7"/>
+    </row>
+    <row r="190" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C190" s="7"/>
       <c r="D190" s="7"/>
       <c r="E190" s="7"/>
@@ -9659,8 +10510,12 @@
       <c r="AM190" s="7"/>
       <c r="AN190" s="7"/>
       <c r="AO190" s="7"/>
-    </row>
-    <row r="191" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP190" s="7"/>
+      <c r="AQ190" s="7"/>
+      <c r="AR190" s="7"/>
+      <c r="AS190" s="7"/>
+    </row>
+    <row r="191" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C191" s="7"/>
       <c r="D191" s="7"/>
       <c r="E191" s="7"/>
@@ -9700,8 +10555,12 @@
       <c r="AM191" s="7"/>
       <c r="AN191" s="7"/>
       <c r="AO191" s="7"/>
-    </row>
-    <row r="192" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP191" s="7"/>
+      <c r="AQ191" s="7"/>
+      <c r="AR191" s="7"/>
+      <c r="AS191" s="7"/>
+    </row>
+    <row r="192" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C192" s="7"/>
       <c r="D192" s="7"/>
       <c r="E192" s="7"/>
@@ -9741,8 +10600,12 @@
       <c r="AM192" s="7"/>
       <c r="AN192" s="7"/>
       <c r="AO192" s="7"/>
-    </row>
-    <row r="193" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP192" s="7"/>
+      <c r="AQ192" s="7"/>
+      <c r="AR192" s="7"/>
+      <c r="AS192" s="7"/>
+    </row>
+    <row r="193" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C193" s="7"/>
       <c r="D193" s="7"/>
       <c r="E193" s="7"/>
@@ -9782,8 +10645,12 @@
       <c r="AM193" s="7"/>
       <c r="AN193" s="7"/>
       <c r="AO193" s="7"/>
-    </row>
-    <row r="194" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP193" s="7"/>
+      <c r="AQ193" s="7"/>
+      <c r="AR193" s="7"/>
+      <c r="AS193" s="7"/>
+    </row>
+    <row r="194" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C194" s="7"/>
       <c r="D194" s="7"/>
       <c r="E194" s="7"/>
@@ -9823,8 +10690,12 @@
       <c r="AM194" s="7"/>
       <c r="AN194" s="7"/>
       <c r="AO194" s="7"/>
-    </row>
-    <row r="195" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP194" s="7"/>
+      <c r="AQ194" s="7"/>
+      <c r="AR194" s="7"/>
+      <c r="AS194" s="7"/>
+    </row>
+    <row r="195" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C195" s="7"/>
       <c r="D195" s="7"/>
       <c r="E195" s="7"/>
@@ -9864,8 +10735,12 @@
       <c r="AM195" s="7"/>
       <c r="AN195" s="7"/>
       <c r="AO195" s="7"/>
-    </row>
-    <row r="196" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP195" s="7"/>
+      <c r="AQ195" s="7"/>
+      <c r="AR195" s="7"/>
+      <c r="AS195" s="7"/>
+    </row>
+    <row r="196" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C196" s="7"/>
       <c r="D196" s="7"/>
       <c r="E196" s="7"/>
@@ -9905,8 +10780,12 @@
       <c r="AM196" s="7"/>
       <c r="AN196" s="7"/>
       <c r="AO196" s="7"/>
-    </row>
-    <row r="197" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP196" s="7"/>
+      <c r="AQ196" s="7"/>
+      <c r="AR196" s="7"/>
+      <c r="AS196" s="7"/>
+    </row>
+    <row r="197" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C197" s="7"/>
       <c r="D197" s="7"/>
       <c r="E197" s="7"/>
@@ -9946,8 +10825,12 @@
       <c r="AM197" s="7"/>
       <c r="AN197" s="7"/>
       <c r="AO197" s="7"/>
-    </row>
-    <row r="198" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP197" s="7"/>
+      <c r="AQ197" s="7"/>
+      <c r="AR197" s="7"/>
+      <c r="AS197" s="7"/>
+    </row>
+    <row r="198" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C198" s="7"/>
       <c r="D198" s="7"/>
       <c r="E198" s="7"/>
@@ -9987,8 +10870,12 @@
       <c r="AM198" s="7"/>
       <c r="AN198" s="7"/>
       <c r="AO198" s="7"/>
-    </row>
-    <row r="199" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP198" s="7"/>
+      <c r="AQ198" s="7"/>
+      <c r="AR198" s="7"/>
+      <c r="AS198" s="7"/>
+    </row>
+    <row r="199" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C199" s="7"/>
       <c r="D199" s="7"/>
       <c r="E199" s="7"/>
@@ -10028,8 +10915,12 @@
       <c r="AM199" s="7"/>
       <c r="AN199" s="7"/>
       <c r="AO199" s="7"/>
-    </row>
-    <row r="200" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP199" s="7"/>
+      <c r="AQ199" s="7"/>
+      <c r="AR199" s="7"/>
+      <c r="AS199" s="7"/>
+    </row>
+    <row r="200" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C200" s="7"/>
       <c r="D200" s="7"/>
       <c r="E200" s="7"/>
@@ -10069,8 +10960,12 @@
       <c r="AM200" s="7"/>
       <c r="AN200" s="7"/>
       <c r="AO200" s="7"/>
-    </row>
-    <row r="201" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP200" s="7"/>
+      <c r="AQ200" s="7"/>
+      <c r="AR200" s="7"/>
+      <c r="AS200" s="7"/>
+    </row>
+    <row r="201" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C201" s="7"/>
       <c r="D201" s="7"/>
       <c r="E201" s="7"/>
@@ -10110,8 +11005,12 @@
       <c r="AM201" s="7"/>
       <c r="AN201" s="7"/>
       <c r="AO201" s="7"/>
-    </row>
-    <row r="202" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP201" s="7"/>
+      <c r="AQ201" s="7"/>
+      <c r="AR201" s="7"/>
+      <c r="AS201" s="7"/>
+    </row>
+    <row r="202" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C202" s="7"/>
       <c r="D202" s="7"/>
       <c r="E202" s="7"/>
@@ -10151,8 +11050,12 @@
       <c r="AM202" s="7"/>
       <c r="AN202" s="7"/>
       <c r="AO202" s="7"/>
-    </row>
-    <row r="203" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP202" s="7"/>
+      <c r="AQ202" s="7"/>
+      <c r="AR202" s="7"/>
+      <c r="AS202" s="7"/>
+    </row>
+    <row r="203" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C203" s="7"/>
       <c r="D203" s="7"/>
       <c r="E203" s="7"/>
@@ -10192,8 +11095,12 @@
       <c r="AM203" s="7"/>
       <c r="AN203" s="7"/>
       <c r="AO203" s="7"/>
-    </row>
-    <row r="204" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP203" s="7"/>
+      <c r="AQ203" s="7"/>
+      <c r="AR203" s="7"/>
+      <c r="AS203" s="7"/>
+    </row>
+    <row r="204" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C204" s="7"/>
       <c r="D204" s="7"/>
       <c r="E204" s="7"/>
@@ -10233,8 +11140,12 @@
       <c r="AM204" s="7"/>
       <c r="AN204" s="7"/>
       <c r="AO204" s="7"/>
-    </row>
-    <row r="205" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP204" s="7"/>
+      <c r="AQ204" s="7"/>
+      <c r="AR204" s="7"/>
+      <c r="AS204" s="7"/>
+    </row>
+    <row r="205" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
       <c r="E205" s="7"/>
@@ -10274,8 +11185,12 @@
       <c r="AM205" s="7"/>
       <c r="AN205" s="7"/>
       <c r="AO205" s="7"/>
-    </row>
-    <row r="206" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP205" s="7"/>
+      <c r="AQ205" s="7"/>
+      <c r="AR205" s="7"/>
+      <c r="AS205" s="7"/>
+    </row>
+    <row r="206" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C206" s="7"/>
       <c r="D206" s="7"/>
       <c r="E206" s="7"/>
@@ -10315,8 +11230,12 @@
       <c r="AM206" s="7"/>
       <c r="AN206" s="7"/>
       <c r="AO206" s="7"/>
-    </row>
-    <row r="207" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP206" s="7"/>
+      <c r="AQ206" s="7"/>
+      <c r="AR206" s="7"/>
+      <c r="AS206" s="7"/>
+    </row>
+    <row r="207" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
       <c r="E207" s="7"/>
@@ -10356,8 +11275,12 @@
       <c r="AM207" s="7"/>
       <c r="AN207" s="7"/>
       <c r="AO207" s="7"/>
-    </row>
-    <row r="208" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP207" s="7"/>
+      <c r="AQ207" s="7"/>
+      <c r="AR207" s="7"/>
+      <c r="AS207" s="7"/>
+    </row>
+    <row r="208" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C208" s="7"/>
       <c r="D208" s="7"/>
       <c r="E208" s="7"/>
@@ -10397,8 +11320,12 @@
       <c r="AM208" s="7"/>
       <c r="AN208" s="7"/>
       <c r="AO208" s="7"/>
-    </row>
-    <row r="209" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP208" s="7"/>
+      <c r="AQ208" s="7"/>
+      <c r="AR208" s="7"/>
+      <c r="AS208" s="7"/>
+    </row>
+    <row r="209" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C209" s="7"/>
       <c r="D209" s="7"/>
       <c r="E209" s="7"/>
@@ -10438,8 +11365,12 @@
       <c r="AM209" s="7"/>
       <c r="AN209" s="7"/>
       <c r="AO209" s="7"/>
-    </row>
-    <row r="210" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP209" s="7"/>
+      <c r="AQ209" s="7"/>
+      <c r="AR209" s="7"/>
+      <c r="AS209" s="7"/>
+    </row>
+    <row r="210" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C210" s="7"/>
       <c r="D210" s="7"/>
       <c r="E210" s="7"/>
@@ -10479,8 +11410,12 @@
       <c r="AM210" s="7"/>
       <c r="AN210" s="7"/>
       <c r="AO210" s="7"/>
-    </row>
-    <row r="211" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP210" s="7"/>
+      <c r="AQ210" s="7"/>
+      <c r="AR210" s="7"/>
+      <c r="AS210" s="7"/>
+    </row>
+    <row r="211" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C211" s="7"/>
       <c r="D211" s="7"/>
       <c r="E211" s="7"/>
@@ -10520,8 +11455,12 @@
       <c r="AM211" s="7"/>
       <c r="AN211" s="7"/>
       <c r="AO211" s="7"/>
-    </row>
-    <row r="212" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP211" s="7"/>
+      <c r="AQ211" s="7"/>
+      <c r="AR211" s="7"/>
+      <c r="AS211" s="7"/>
+    </row>
+    <row r="212" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C212" s="7"/>
       <c r="D212" s="7"/>
       <c r="E212" s="7"/>
@@ -10561,8 +11500,12 @@
       <c r="AM212" s="7"/>
       <c r="AN212" s="7"/>
       <c r="AO212" s="7"/>
-    </row>
-    <row r="213" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP212" s="7"/>
+      <c r="AQ212" s="7"/>
+      <c r="AR212" s="7"/>
+      <c r="AS212" s="7"/>
+    </row>
+    <row r="213" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C213" s="7"/>
       <c r="D213" s="7"/>
       <c r="E213" s="7"/>
@@ -10602,8 +11545,12 @@
       <c r="AM213" s="7"/>
       <c r="AN213" s="7"/>
       <c r="AO213" s="7"/>
-    </row>
-    <row r="214" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP213" s="7"/>
+      <c r="AQ213" s="7"/>
+      <c r="AR213" s="7"/>
+      <c r="AS213" s="7"/>
+    </row>
+    <row r="214" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C214" s="7"/>
       <c r="D214" s="7"/>
       <c r="E214" s="7"/>
@@ -10643,8 +11590,12 @@
       <c r="AM214" s="7"/>
       <c r="AN214" s="7"/>
       <c r="AO214" s="7"/>
-    </row>
-    <row r="215" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP214" s="7"/>
+      <c r="AQ214" s="7"/>
+      <c r="AR214" s="7"/>
+      <c r="AS214" s="7"/>
+    </row>
+    <row r="215" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C215" s="7"/>
       <c r="D215" s="7"/>
       <c r="E215" s="7"/>
@@ -10684,8 +11635,12 @@
       <c r="AM215" s="7"/>
       <c r="AN215" s="7"/>
       <c r="AO215" s="7"/>
-    </row>
-    <row r="216" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP215" s="7"/>
+      <c r="AQ215" s="7"/>
+      <c r="AR215" s="7"/>
+      <c r="AS215" s="7"/>
+    </row>
+    <row r="216" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C216" s="7"/>
       <c r="D216" s="7"/>
       <c r="E216" s="7"/>
@@ -10725,8 +11680,12 @@
       <c r="AM216" s="7"/>
       <c r="AN216" s="7"/>
       <c r="AO216" s="7"/>
-    </row>
-    <row r="217" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP216" s="7"/>
+      <c r="AQ216" s="7"/>
+      <c r="AR216" s="7"/>
+      <c r="AS216" s="7"/>
+    </row>
+    <row r="217" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C217" s="7"/>
       <c r="D217" s="7"/>
       <c r="E217" s="7"/>
@@ -10766,8 +11725,12 @@
       <c r="AM217" s="7"/>
       <c r="AN217" s="7"/>
       <c r="AO217" s="7"/>
-    </row>
-    <row r="218" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP217" s="7"/>
+      <c r="AQ217" s="7"/>
+      <c r="AR217" s="7"/>
+      <c r="AS217" s="7"/>
+    </row>
+    <row r="218" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C218" s="7"/>
       <c r="D218" s="7"/>
       <c r="E218" s="7"/>
@@ -10807,8 +11770,12 @@
       <c r="AM218" s="7"/>
       <c r="AN218" s="7"/>
       <c r="AO218" s="7"/>
-    </row>
-    <row r="219" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP218" s="7"/>
+      <c r="AQ218" s="7"/>
+      <c r="AR218" s="7"/>
+      <c r="AS218" s="7"/>
+    </row>
+    <row r="219" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C219" s="7"/>
       <c r="D219" s="7"/>
       <c r="E219" s="7"/>
@@ -10848,8 +11815,12 @@
       <c r="AM219" s="7"/>
       <c r="AN219" s="7"/>
       <c r="AO219" s="7"/>
-    </row>
-    <row r="220" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP219" s="7"/>
+      <c r="AQ219" s="7"/>
+      <c r="AR219" s="7"/>
+      <c r="AS219" s="7"/>
+    </row>
+    <row r="220" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C220" s="7"/>
       <c r="D220" s="7"/>
       <c r="E220" s="7"/>
@@ -10889,8 +11860,12 @@
       <c r="AM220" s="7"/>
       <c r="AN220" s="7"/>
       <c r="AO220" s="7"/>
-    </row>
-    <row r="221" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP220" s="7"/>
+      <c r="AQ220" s="7"/>
+      <c r="AR220" s="7"/>
+      <c r="AS220" s="7"/>
+    </row>
+    <row r="221" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C221" s="7"/>
       <c r="D221" s="7"/>
       <c r="E221" s="7"/>
@@ -10930,8 +11905,12 @@
       <c r="AM221" s="7"/>
       <c r="AN221" s="7"/>
       <c r="AO221" s="7"/>
-    </row>
-    <row r="222" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP221" s="7"/>
+      <c r="AQ221" s="7"/>
+      <c r="AR221" s="7"/>
+      <c r="AS221" s="7"/>
+    </row>
+    <row r="222" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C222" s="7"/>
       <c r="D222" s="7"/>
       <c r="E222" s="7"/>
@@ -10971,8 +11950,12 @@
       <c r="AM222" s="7"/>
       <c r="AN222" s="7"/>
       <c r="AO222" s="7"/>
-    </row>
-    <row r="223" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP222" s="7"/>
+      <c r="AQ222" s="7"/>
+      <c r="AR222" s="7"/>
+      <c r="AS222" s="7"/>
+    </row>
+    <row r="223" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C223" s="7"/>
       <c r="D223" s="7"/>
       <c r="E223" s="7"/>
@@ -11012,8 +11995,12 @@
       <c r="AM223" s="7"/>
       <c r="AN223" s="7"/>
       <c r="AO223" s="7"/>
-    </row>
-    <row r="224" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP223" s="7"/>
+      <c r="AQ223" s="7"/>
+      <c r="AR223" s="7"/>
+      <c r="AS223" s="7"/>
+    </row>
+    <row r="224" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C224" s="7"/>
       <c r="D224" s="7"/>
       <c r="E224" s="7"/>
@@ -11053,8 +12040,12 @@
       <c r="AM224" s="7"/>
       <c r="AN224" s="7"/>
       <c r="AO224" s="7"/>
-    </row>
-    <row r="225" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP224" s="7"/>
+      <c r="AQ224" s="7"/>
+      <c r="AR224" s="7"/>
+      <c r="AS224" s="7"/>
+    </row>
+    <row r="225" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C225" s="7"/>
       <c r="D225" s="7"/>
       <c r="E225" s="7"/>
@@ -11094,8 +12085,12 @@
       <c r="AM225" s="7"/>
       <c r="AN225" s="7"/>
       <c r="AO225" s="7"/>
-    </row>
-    <row r="226" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP225" s="7"/>
+      <c r="AQ225" s="7"/>
+      <c r="AR225" s="7"/>
+      <c r="AS225" s="7"/>
+    </row>
+    <row r="226" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C226" s="7"/>
       <c r="D226" s="7"/>
       <c r="E226" s="7"/>
@@ -11135,8 +12130,12 @@
       <c r="AM226" s="7"/>
       <c r="AN226" s="7"/>
       <c r="AO226" s="7"/>
-    </row>
-    <row r="227" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP226" s="7"/>
+      <c r="AQ226" s="7"/>
+      <c r="AR226" s="7"/>
+      <c r="AS226" s="7"/>
+    </row>
+    <row r="227" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C227" s="7"/>
       <c r="D227" s="7"/>
       <c r="E227" s="7"/>
@@ -11176,8 +12175,12 @@
       <c r="AM227" s="7"/>
       <c r="AN227" s="7"/>
       <c r="AO227" s="7"/>
-    </row>
-    <row r="228" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP227" s="7"/>
+      <c r="AQ227" s="7"/>
+      <c r="AR227" s="7"/>
+      <c r="AS227" s="7"/>
+    </row>
+    <row r="228" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C228" s="7"/>
       <c r="D228" s="7"/>
       <c r="E228" s="7"/>
@@ -11217,8 +12220,12 @@
       <c r="AM228" s="7"/>
       <c r="AN228" s="7"/>
       <c r="AO228" s="7"/>
-    </row>
-    <row r="229" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP228" s="7"/>
+      <c r="AQ228" s="7"/>
+      <c r="AR228" s="7"/>
+      <c r="AS228" s="7"/>
+    </row>
+    <row r="229" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C229" s="7"/>
       <c r="D229" s="7"/>
       <c r="E229" s="7"/>
@@ -11258,8 +12265,12 @@
       <c r="AM229" s="7"/>
       <c r="AN229" s="7"/>
       <c r="AO229" s="7"/>
-    </row>
-    <row r="230" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP229" s="7"/>
+      <c r="AQ229" s="7"/>
+      <c r="AR229" s="7"/>
+      <c r="AS229" s="7"/>
+    </row>
+    <row r="230" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C230" s="7"/>
       <c r="D230" s="7"/>
       <c r="E230" s="7"/>
@@ -11299,8 +12310,12 @@
       <c r="AM230" s="7"/>
       <c r="AN230" s="7"/>
       <c r="AO230" s="7"/>
-    </row>
-    <row r="231" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP230" s="7"/>
+      <c r="AQ230" s="7"/>
+      <c r="AR230" s="7"/>
+      <c r="AS230" s="7"/>
+    </row>
+    <row r="231" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C231" s="7"/>
       <c r="D231" s="7"/>
       <c r="E231" s="7"/>
@@ -11340,8 +12355,12 @@
       <c r="AM231" s="7"/>
       <c r="AN231" s="7"/>
       <c r="AO231" s="7"/>
-    </row>
-    <row r="232" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP231" s="7"/>
+      <c r="AQ231" s="7"/>
+      <c r="AR231" s="7"/>
+      <c r="AS231" s="7"/>
+    </row>
+    <row r="232" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C232" s="7"/>
       <c r="D232" s="7"/>
       <c r="E232" s="7"/>
@@ -11381,8 +12400,12 @@
       <c r="AM232" s="7"/>
       <c r="AN232" s="7"/>
       <c r="AO232" s="7"/>
-    </row>
-    <row r="233" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP232" s="7"/>
+      <c r="AQ232" s="7"/>
+      <c r="AR232" s="7"/>
+      <c r="AS232" s="7"/>
+    </row>
+    <row r="233" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C233" s="7"/>
       <c r="D233" s="7"/>
       <c r="E233" s="7"/>
@@ -11422,8 +12445,12 @@
       <c r="AM233" s="7"/>
       <c r="AN233" s="7"/>
       <c r="AO233" s="7"/>
-    </row>
-    <row r="234" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP233" s="7"/>
+      <c r="AQ233" s="7"/>
+      <c r="AR233" s="7"/>
+      <c r="AS233" s="7"/>
+    </row>
+    <row r="234" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C234" s="7"/>
       <c r="D234" s="7"/>
       <c r="E234" s="7"/>
@@ -11463,8 +12490,12 @@
       <c r="AM234" s="7"/>
       <c r="AN234" s="7"/>
       <c r="AO234" s="7"/>
-    </row>
-    <row r="235" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP234" s="7"/>
+      <c r="AQ234" s="7"/>
+      <c r="AR234" s="7"/>
+      <c r="AS234" s="7"/>
+    </row>
+    <row r="235" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C235" s="7"/>
       <c r="D235" s="7"/>
       <c r="E235" s="7"/>
@@ -11504,8 +12535,12 @@
       <c r="AM235" s="7"/>
       <c r="AN235" s="7"/>
       <c r="AO235" s="7"/>
-    </row>
-    <row r="236" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP235" s="7"/>
+      <c r="AQ235" s="7"/>
+      <c r="AR235" s="7"/>
+      <c r="AS235" s="7"/>
+    </row>
+    <row r="236" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C236" s="7"/>
       <c r="D236" s="7"/>
       <c r="E236" s="7"/>
@@ -11545,8 +12580,12 @@
       <c r="AM236" s="7"/>
       <c r="AN236" s="7"/>
       <c r="AO236" s="7"/>
-    </row>
-    <row r="237" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP236" s="7"/>
+      <c r="AQ236" s="7"/>
+      <c r="AR236" s="7"/>
+      <c r="AS236" s="7"/>
+    </row>
+    <row r="237" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C237" s="7"/>
       <c r="D237" s="7"/>
       <c r="E237" s="7"/>
@@ -11586,8 +12625,12 @@
       <c r="AM237" s="7"/>
       <c r="AN237" s="7"/>
       <c r="AO237" s="7"/>
-    </row>
-    <row r="238" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP237" s="7"/>
+      <c r="AQ237" s="7"/>
+      <c r="AR237" s="7"/>
+      <c r="AS237" s="7"/>
+    </row>
+    <row r="238" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C238" s="7"/>
       <c r="D238" s="7"/>
       <c r="E238" s="7"/>
@@ -11627,8 +12670,12 @@
       <c r="AM238" s="7"/>
       <c r="AN238" s="7"/>
       <c r="AO238" s="7"/>
-    </row>
-    <row r="239" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP238" s="7"/>
+      <c r="AQ238" s="7"/>
+      <c r="AR238" s="7"/>
+      <c r="AS238" s="7"/>
+    </row>
+    <row r="239" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C239" s="7"/>
       <c r="D239" s="7"/>
       <c r="E239" s="7"/>
@@ -11668,8 +12715,12 @@
       <c r="AM239" s="7"/>
       <c r="AN239" s="7"/>
       <c r="AO239" s="7"/>
-    </row>
-    <row r="240" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP239" s="7"/>
+      <c r="AQ239" s="7"/>
+      <c r="AR239" s="7"/>
+      <c r="AS239" s="7"/>
+    </row>
+    <row r="240" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C240" s="7"/>
       <c r="D240" s="7"/>
       <c r="E240" s="7"/>
@@ -11709,8 +12760,12 @@
       <c r="AM240" s="7"/>
       <c r="AN240" s="7"/>
       <c r="AO240" s="7"/>
-    </row>
-    <row r="241" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP240" s="7"/>
+      <c r="AQ240" s="7"/>
+      <c r="AR240" s="7"/>
+      <c r="AS240" s="7"/>
+    </row>
+    <row r="241" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C241" s="7"/>
       <c r="D241" s="7"/>
       <c r="E241" s="7"/>
@@ -11750,8 +12805,12 @@
       <c r="AM241" s="7"/>
       <c r="AN241" s="7"/>
       <c r="AO241" s="7"/>
-    </row>
-    <row r="242" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP241" s="7"/>
+      <c r="AQ241" s="7"/>
+      <c r="AR241" s="7"/>
+      <c r="AS241" s="7"/>
+    </row>
+    <row r="242" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C242" s="7"/>
       <c r="D242" s="7"/>
       <c r="E242" s="7"/>
@@ -11791,8 +12850,12 @@
       <c r="AM242" s="7"/>
       <c r="AN242" s="7"/>
       <c r="AO242" s="7"/>
-    </row>
-    <row r="243" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP242" s="7"/>
+      <c r="AQ242" s="7"/>
+      <c r="AR242" s="7"/>
+      <c r="AS242" s="7"/>
+    </row>
+    <row r="243" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C243" s="7"/>
       <c r="D243" s="7"/>
       <c r="E243" s="7"/>
@@ -11832,8 +12895,12 @@
       <c r="AM243" s="7"/>
       <c r="AN243" s="7"/>
       <c r="AO243" s="7"/>
-    </row>
-    <row r="244" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP243" s="7"/>
+      <c r="AQ243" s="7"/>
+      <c r="AR243" s="7"/>
+      <c r="AS243" s="7"/>
+    </row>
+    <row r="244" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C244" s="7"/>
       <c r="D244" s="7"/>
       <c r="E244" s="7"/>
@@ -11873,8 +12940,12 @@
       <c r="AM244" s="7"/>
       <c r="AN244" s="7"/>
       <c r="AO244" s="7"/>
-    </row>
-    <row r="245" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP244" s="7"/>
+      <c r="AQ244" s="7"/>
+      <c r="AR244" s="7"/>
+      <c r="AS244" s="7"/>
+    </row>
+    <row r="245" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C245" s="7"/>
       <c r="D245" s="7"/>
       <c r="E245" s="7"/>
@@ -11914,8 +12985,12 @@
       <c r="AM245" s="7"/>
       <c r="AN245" s="7"/>
       <c r="AO245" s="7"/>
-    </row>
-    <row r="246" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP245" s="7"/>
+      <c r="AQ245" s="7"/>
+      <c r="AR245" s="7"/>
+      <c r="AS245" s="7"/>
+    </row>
+    <row r="246" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C246" s="7"/>
       <c r="D246" s="7"/>
       <c r="E246" s="7"/>
@@ -11955,8 +13030,12 @@
       <c r="AM246" s="7"/>
       <c r="AN246" s="7"/>
       <c r="AO246" s="7"/>
-    </row>
-    <row r="247" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP246" s="7"/>
+      <c r="AQ246" s="7"/>
+      <c r="AR246" s="7"/>
+      <c r="AS246" s="7"/>
+    </row>
+    <row r="247" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C247" s="7"/>
       <c r="D247" s="7"/>
       <c r="E247" s="7"/>
@@ -11996,8 +13075,12 @@
       <c r="AM247" s="7"/>
       <c r="AN247" s="7"/>
       <c r="AO247" s="7"/>
-    </row>
-    <row r="248" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP247" s="7"/>
+      <c r="AQ247" s="7"/>
+      <c r="AR247" s="7"/>
+      <c r="AS247" s="7"/>
+    </row>
+    <row r="248" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C248" s="7"/>
       <c r="D248" s="7"/>
       <c r="E248" s="7"/>
@@ -12037,8 +13120,12 @@
       <c r="AM248" s="7"/>
       <c r="AN248" s="7"/>
       <c r="AO248" s="7"/>
-    </row>
-    <row r="249" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP248" s="7"/>
+      <c r="AQ248" s="7"/>
+      <c r="AR248" s="7"/>
+      <c r="AS248" s="7"/>
+    </row>
+    <row r="249" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C249" s="7"/>
       <c r="D249" s="7"/>
       <c r="E249" s="7"/>
@@ -12078,8 +13165,12 @@
       <c r="AM249" s="7"/>
       <c r="AN249" s="7"/>
       <c r="AO249" s="7"/>
-    </row>
-    <row r="250" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP249" s="7"/>
+      <c r="AQ249" s="7"/>
+      <c r="AR249" s="7"/>
+      <c r="AS249" s="7"/>
+    </row>
+    <row r="250" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C250" s="7"/>
       <c r="D250" s="7"/>
       <c r="E250" s="7"/>
@@ -12119,8 +13210,12 @@
       <c r="AM250" s="7"/>
       <c r="AN250" s="7"/>
       <c r="AO250" s="7"/>
-    </row>
-    <row r="251" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP250" s="7"/>
+      <c r="AQ250" s="7"/>
+      <c r="AR250" s="7"/>
+      <c r="AS250" s="7"/>
+    </row>
+    <row r="251" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C251" s="7"/>
       <c r="D251" s="7"/>
       <c r="E251" s="7"/>
@@ -12160,8 +13255,12 @@
       <c r="AM251" s="7"/>
       <c r="AN251" s="7"/>
       <c r="AO251" s="7"/>
-    </row>
-    <row r="252" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP251" s="7"/>
+      <c r="AQ251" s="7"/>
+      <c r="AR251" s="7"/>
+      <c r="AS251" s="7"/>
+    </row>
+    <row r="252" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C252" s="7"/>
       <c r="D252" s="7"/>
       <c r="E252" s="7"/>
@@ -12201,8 +13300,12 @@
       <c r="AM252" s="7"/>
       <c r="AN252" s="7"/>
       <c r="AO252" s="7"/>
-    </row>
-    <row r="253" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP252" s="7"/>
+      <c r="AQ252" s="7"/>
+      <c r="AR252" s="7"/>
+      <c r="AS252" s="7"/>
+    </row>
+    <row r="253" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C253" s="7"/>
       <c r="D253" s="7"/>
       <c r="E253" s="7"/>
@@ -12242,8 +13345,12 @@
       <c r="AM253" s="7"/>
       <c r="AN253" s="7"/>
       <c r="AO253" s="7"/>
-    </row>
-    <row r="254" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP253" s="7"/>
+      <c r="AQ253" s="7"/>
+      <c r="AR253" s="7"/>
+      <c r="AS253" s="7"/>
+    </row>
+    <row r="254" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C254" s="7"/>
       <c r="D254" s="7"/>
       <c r="E254" s="7"/>
@@ -12283,8 +13390,12 @@
       <c r="AM254" s="7"/>
       <c r="AN254" s="7"/>
       <c r="AO254" s="7"/>
-    </row>
-    <row r="255" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP254" s="7"/>
+      <c r="AQ254" s="7"/>
+      <c r="AR254" s="7"/>
+      <c r="AS254" s="7"/>
+    </row>
+    <row r="255" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C255" s="7"/>
       <c r="D255" s="7"/>
       <c r="E255" s="7"/>
@@ -12324,8 +13435,12 @@
       <c r="AM255" s="7"/>
       <c r="AN255" s="7"/>
       <c r="AO255" s="7"/>
-    </row>
-    <row r="256" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP255" s="7"/>
+      <c r="AQ255" s="7"/>
+      <c r="AR255" s="7"/>
+      <c r="AS255" s="7"/>
+    </row>
+    <row r="256" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C256" s="7"/>
       <c r="D256" s="7"/>
       <c r="E256" s="7"/>
@@ -12365,8 +13480,12 @@
       <c r="AM256" s="7"/>
       <c r="AN256" s="7"/>
       <c r="AO256" s="7"/>
-    </row>
-    <row r="257" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP256" s="7"/>
+      <c r="AQ256" s="7"/>
+      <c r="AR256" s="7"/>
+      <c r="AS256" s="7"/>
+    </row>
+    <row r="257" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C257" s="7"/>
       <c r="D257" s="7"/>
       <c r="E257" s="7"/>
@@ -12406,8 +13525,12 @@
       <c r="AM257" s="7"/>
       <c r="AN257" s="7"/>
       <c r="AO257" s="7"/>
-    </row>
-    <row r="258" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP257" s="7"/>
+      <c r="AQ257" s="7"/>
+      <c r="AR257" s="7"/>
+      <c r="AS257" s="7"/>
+    </row>
+    <row r="258" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C258" s="7"/>
       <c r="D258" s="7"/>
       <c r="E258" s="7"/>
@@ -12447,8 +13570,12 @@
       <c r="AM258" s="7"/>
       <c r="AN258" s="7"/>
       <c r="AO258" s="7"/>
-    </row>
-    <row r="259" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP258" s="7"/>
+      <c r="AQ258" s="7"/>
+      <c r="AR258" s="7"/>
+      <c r="AS258" s="7"/>
+    </row>
+    <row r="259" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C259" s="7"/>
       <c r="D259" s="7"/>
       <c r="E259" s="7"/>
@@ -12488,8 +13615,12 @@
       <c r="AM259" s="7"/>
       <c r="AN259" s="7"/>
       <c r="AO259" s="7"/>
-    </row>
-    <row r="260" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP259" s="7"/>
+      <c r="AQ259" s="7"/>
+      <c r="AR259" s="7"/>
+      <c r="AS259" s="7"/>
+    </row>
+    <row r="260" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C260" s="7"/>
       <c r="D260" s="7"/>
       <c r="E260" s="7"/>
@@ -12529,8 +13660,12 @@
       <c r="AM260" s="7"/>
       <c r="AN260" s="7"/>
       <c r="AO260" s="7"/>
-    </row>
-    <row r="261" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP260" s="7"/>
+      <c r="AQ260" s="7"/>
+      <c r="AR260" s="7"/>
+      <c r="AS260" s="7"/>
+    </row>
+    <row r="261" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C261" s="7"/>
       <c r="D261" s="7"/>
       <c r="E261" s="7"/>
@@ -12570,8 +13705,12 @@
       <c r="AM261" s="7"/>
       <c r="AN261" s="7"/>
       <c r="AO261" s="7"/>
-    </row>
-    <row r="262" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP261" s="7"/>
+      <c r="AQ261" s="7"/>
+      <c r="AR261" s="7"/>
+      <c r="AS261" s="7"/>
+    </row>
+    <row r="262" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C262" s="7"/>
       <c r="D262" s="7"/>
       <c r="E262" s="7"/>
@@ -12611,8 +13750,12 @@
       <c r="AM262" s="7"/>
       <c r="AN262" s="7"/>
       <c r="AO262" s="7"/>
-    </row>
-    <row r="263" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP262" s="7"/>
+      <c r="AQ262" s="7"/>
+      <c r="AR262" s="7"/>
+      <c r="AS262" s="7"/>
+    </row>
+    <row r="263" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C263" s="7"/>
       <c r="D263" s="7"/>
       <c r="E263" s="7"/>
@@ -12652,8 +13795,12 @@
       <c r="AM263" s="7"/>
       <c r="AN263" s="7"/>
       <c r="AO263" s="7"/>
-    </row>
-    <row r="264" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP263" s="7"/>
+      <c r="AQ263" s="7"/>
+      <c r="AR263" s="7"/>
+      <c r="AS263" s="7"/>
+    </row>
+    <row r="264" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C264" s="7"/>
       <c r="D264" s="7"/>
       <c r="E264" s="7"/>
@@ -12693,8 +13840,12 @@
       <c r="AM264" s="7"/>
       <c r="AN264" s="7"/>
       <c r="AO264" s="7"/>
-    </row>
-    <row r="265" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP264" s="7"/>
+      <c r="AQ264" s="7"/>
+      <c r="AR264" s="7"/>
+      <c r="AS264" s="7"/>
+    </row>
+    <row r="265" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C265" s="7"/>
       <c r="D265" s="7"/>
       <c r="E265" s="7"/>
@@ -12734,8 +13885,12 @@
       <c r="AM265" s="7"/>
       <c r="AN265" s="7"/>
       <c r="AO265" s="7"/>
-    </row>
-    <row r="266" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP265" s="7"/>
+      <c r="AQ265" s="7"/>
+      <c r="AR265" s="7"/>
+      <c r="AS265" s="7"/>
+    </row>
+    <row r="266" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C266" s="7"/>
       <c r="D266" s="7"/>
       <c r="E266" s="7"/>
@@ -12775,8 +13930,12 @@
       <c r="AM266" s="7"/>
       <c r="AN266" s="7"/>
       <c r="AO266" s="7"/>
-    </row>
-    <row r="267" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP266" s="7"/>
+      <c r="AQ266" s="7"/>
+      <c r="AR266" s="7"/>
+      <c r="AS266" s="7"/>
+    </row>
+    <row r="267" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C267" s="7"/>
       <c r="D267" s="7"/>
       <c r="E267" s="7"/>
@@ -12816,8 +13975,12 @@
       <c r="AM267" s="7"/>
       <c r="AN267" s="7"/>
       <c r="AO267" s="7"/>
-    </row>
-    <row r="268" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP267" s="7"/>
+      <c r="AQ267" s="7"/>
+      <c r="AR267" s="7"/>
+      <c r="AS267" s="7"/>
+    </row>
+    <row r="268" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C268" s="7"/>
       <c r="D268" s="7"/>
       <c r="E268" s="7"/>
@@ -12857,8 +14020,12 @@
       <c r="AM268" s="7"/>
       <c r="AN268" s="7"/>
       <c r="AO268" s="7"/>
-    </row>
-    <row r="269" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP268" s="7"/>
+      <c r="AQ268" s="7"/>
+      <c r="AR268" s="7"/>
+      <c r="AS268" s="7"/>
+    </row>
+    <row r="269" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C269" s="7"/>
       <c r="D269" s="7"/>
       <c r="E269" s="7"/>
@@ -12898,8 +14065,12 @@
       <c r="AM269" s="7"/>
       <c r="AN269" s="7"/>
       <c r="AO269" s="7"/>
-    </row>
-    <row r="270" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP269" s="7"/>
+      <c r="AQ269" s="7"/>
+      <c r="AR269" s="7"/>
+      <c r="AS269" s="7"/>
+    </row>
+    <row r="270" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C270" s="7"/>
       <c r="D270" s="7"/>
       <c r="E270" s="7"/>
@@ -12939,8 +14110,12 @@
       <c r="AM270" s="7"/>
       <c r="AN270" s="7"/>
       <c r="AO270" s="7"/>
-    </row>
-    <row r="271" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP270" s="7"/>
+      <c r="AQ270" s="7"/>
+      <c r="AR270" s="7"/>
+      <c r="AS270" s="7"/>
+    </row>
+    <row r="271" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C271" s="7"/>
       <c r="D271" s="7"/>
       <c r="E271" s="7"/>
@@ -12980,8 +14155,12 @@
       <c r="AM271" s="7"/>
       <c r="AN271" s="7"/>
       <c r="AO271" s="7"/>
-    </row>
-    <row r="272" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP271" s="7"/>
+      <c r="AQ271" s="7"/>
+      <c r="AR271" s="7"/>
+      <c r="AS271" s="7"/>
+    </row>
+    <row r="272" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C272" s="7"/>
       <c r="D272" s="7"/>
       <c r="E272" s="7"/>
@@ -13021,8 +14200,12 @@
       <c r="AM272" s="7"/>
       <c r="AN272" s="7"/>
       <c r="AO272" s="7"/>
-    </row>
-    <row r="273" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP272" s="7"/>
+      <c r="AQ272" s="7"/>
+      <c r="AR272" s="7"/>
+      <c r="AS272" s="7"/>
+    </row>
+    <row r="273" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C273" s="7"/>
       <c r="D273" s="7"/>
       <c r="E273" s="7"/>
@@ -13062,8 +14245,12 @@
       <c r="AM273" s="7"/>
       <c r="AN273" s="7"/>
       <c r="AO273" s="7"/>
-    </row>
-    <row r="274" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP273" s="7"/>
+      <c r="AQ273" s="7"/>
+      <c r="AR273" s="7"/>
+      <c r="AS273" s="7"/>
+    </row>
+    <row r="274" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C274" s="7"/>
       <c r="D274" s="7"/>
       <c r="E274" s="7"/>
@@ -13103,8 +14290,12 @@
       <c r="AM274" s="7"/>
       <c r="AN274" s="7"/>
       <c r="AO274" s="7"/>
-    </row>
-    <row r="275" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP274" s="7"/>
+      <c r="AQ274" s="7"/>
+      <c r="AR274" s="7"/>
+      <c r="AS274" s="7"/>
+    </row>
+    <row r="275" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C275" s="7"/>
       <c r="D275" s="7"/>
       <c r="E275" s="7"/>
@@ -13144,8 +14335,12 @@
       <c r="AM275" s="7"/>
       <c r="AN275" s="7"/>
       <c r="AO275" s="7"/>
-    </row>
-    <row r="276" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP275" s="7"/>
+      <c r="AQ275" s="7"/>
+      <c r="AR275" s="7"/>
+      <c r="AS275" s="7"/>
+    </row>
+    <row r="276" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C276" s="7"/>
       <c r="D276" s="7"/>
       <c r="E276" s="7"/>
@@ -13185,8 +14380,12 @@
       <c r="AM276" s="7"/>
       <c r="AN276" s="7"/>
       <c r="AO276" s="7"/>
-    </row>
-    <row r="277" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP276" s="7"/>
+      <c r="AQ276" s="7"/>
+      <c r="AR276" s="7"/>
+      <c r="AS276" s="7"/>
+    </row>
+    <row r="277" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C277" s="7"/>
       <c r="D277" s="7"/>
       <c r="E277" s="7"/>
@@ -13226,8 +14425,12 @@
       <c r="AM277" s="7"/>
       <c r="AN277" s="7"/>
       <c r="AO277" s="7"/>
-    </row>
-    <row r="278" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP277" s="7"/>
+      <c r="AQ277" s="7"/>
+      <c r="AR277" s="7"/>
+      <c r="AS277" s="7"/>
+    </row>
+    <row r="278" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C278" s="7"/>
       <c r="D278" s="7"/>
       <c r="E278" s="7"/>
@@ -13267,8 +14470,12 @@
       <c r="AM278" s="7"/>
       <c r="AN278" s="7"/>
       <c r="AO278" s="7"/>
-    </row>
-    <row r="279" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP278" s="7"/>
+      <c r="AQ278" s="7"/>
+      <c r="AR278" s="7"/>
+      <c r="AS278" s="7"/>
+    </row>
+    <row r="279" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C279" s="7"/>
       <c r="D279" s="7"/>
       <c r="E279" s="7"/>
@@ -13308,8 +14515,12 @@
       <c r="AM279" s="7"/>
       <c r="AN279" s="7"/>
       <c r="AO279" s="7"/>
-    </row>
-    <row r="280" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP279" s="7"/>
+      <c r="AQ279" s="7"/>
+      <c r="AR279" s="7"/>
+      <c r="AS279" s="7"/>
+    </row>
+    <row r="280" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C280" s="7"/>
       <c r="D280" s="7"/>
       <c r="E280" s="7"/>
@@ -13349,8 +14560,12 @@
       <c r="AM280" s="7"/>
       <c r="AN280" s="7"/>
       <c r="AO280" s="7"/>
-    </row>
-    <row r="281" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP280" s="7"/>
+      <c r="AQ280" s="7"/>
+      <c r="AR280" s="7"/>
+      <c r="AS280" s="7"/>
+    </row>
+    <row r="281" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C281" s="7"/>
       <c r="D281" s="7"/>
       <c r="E281" s="7"/>
@@ -13390,8 +14605,12 @@
       <c r="AM281" s="7"/>
       <c r="AN281" s="7"/>
       <c r="AO281" s="7"/>
-    </row>
-    <row r="282" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP281" s="7"/>
+      <c r="AQ281" s="7"/>
+      <c r="AR281" s="7"/>
+      <c r="AS281" s="7"/>
+    </row>
+    <row r="282" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C282" s="7"/>
       <c r="D282" s="7"/>
       <c r="E282" s="7"/>
@@ -13431,8 +14650,12 @@
       <c r="AM282" s="7"/>
       <c r="AN282" s="7"/>
       <c r="AO282" s="7"/>
-    </row>
-    <row r="283" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP282" s="7"/>
+      <c r="AQ282" s="7"/>
+      <c r="AR282" s="7"/>
+      <c r="AS282" s="7"/>
+    </row>
+    <row r="283" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C283" s="7"/>
       <c r="D283" s="7"/>
       <c r="E283" s="7"/>
@@ -13472,8 +14695,12 @@
       <c r="AM283" s="7"/>
       <c r="AN283" s="7"/>
       <c r="AO283" s="7"/>
-    </row>
-    <row r="284" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP283" s="7"/>
+      <c r="AQ283" s="7"/>
+      <c r="AR283" s="7"/>
+      <c r="AS283" s="7"/>
+    </row>
+    <row r="284" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C284" s="7"/>
       <c r="D284" s="7"/>
       <c r="E284" s="7"/>
@@ -13513,8 +14740,12 @@
       <c r="AM284" s="7"/>
       <c r="AN284" s="7"/>
       <c r="AO284" s="7"/>
-    </row>
-    <row r="285" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP284" s="7"/>
+      <c r="AQ284" s="7"/>
+      <c r="AR284" s="7"/>
+      <c r="AS284" s="7"/>
+    </row>
+    <row r="285" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C285" s="7"/>
       <c r="D285" s="7"/>
       <c r="E285" s="7"/>
@@ -13554,8 +14785,12 @@
       <c r="AM285" s="7"/>
       <c r="AN285" s="7"/>
       <c r="AO285" s="7"/>
-    </row>
-    <row r="286" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP285" s="7"/>
+      <c r="AQ285" s="7"/>
+      <c r="AR285" s="7"/>
+      <c r="AS285" s="7"/>
+    </row>
+    <row r="286" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C286" s="7"/>
       <c r="D286" s="7"/>
       <c r="E286" s="7"/>
@@ -13595,8 +14830,12 @@
       <c r="AM286" s="7"/>
       <c r="AN286" s="7"/>
       <c r="AO286" s="7"/>
-    </row>
-    <row r="287" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP286" s="7"/>
+      <c r="AQ286" s="7"/>
+      <c r="AR286" s="7"/>
+      <c r="AS286" s="7"/>
+    </row>
+    <row r="287" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C287" s="7"/>
       <c r="D287" s="7"/>
       <c r="E287" s="7"/>
@@ -13636,8 +14875,12 @@
       <c r="AM287" s="7"/>
       <c r="AN287" s="7"/>
       <c r="AO287" s="7"/>
-    </row>
-    <row r="288" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP287" s="7"/>
+      <c r="AQ287" s="7"/>
+      <c r="AR287" s="7"/>
+      <c r="AS287" s="7"/>
+    </row>
+    <row r="288" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C288" s="7"/>
       <c r="D288" s="7"/>
       <c r="E288" s="7"/>
@@ -13677,8 +14920,12 @@
       <c r="AM288" s="7"/>
       <c r="AN288" s="7"/>
       <c r="AO288" s="7"/>
-    </row>
-    <row r="289" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP288" s="7"/>
+      <c r="AQ288" s="7"/>
+      <c r="AR288" s="7"/>
+      <c r="AS288" s="7"/>
+    </row>
+    <row r="289" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C289" s="7"/>
       <c r="D289" s="7"/>
       <c r="E289" s="7"/>
@@ -13718,8 +14965,12 @@
       <c r="AM289" s="7"/>
       <c r="AN289" s="7"/>
       <c r="AO289" s="7"/>
-    </row>
-    <row r="290" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP289" s="7"/>
+      <c r="AQ289" s="7"/>
+      <c r="AR289" s="7"/>
+      <c r="AS289" s="7"/>
+    </row>
+    <row r="290" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C290" s="7"/>
       <c r="D290" s="7"/>
       <c r="E290" s="7"/>
@@ -13759,8 +15010,12 @@
       <c r="AM290" s="7"/>
       <c r="AN290" s="7"/>
       <c r="AO290" s="7"/>
-    </row>
-    <row r="291" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP290" s="7"/>
+      <c r="AQ290" s="7"/>
+      <c r="AR290" s="7"/>
+      <c r="AS290" s="7"/>
+    </row>
+    <row r="291" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C291" s="7"/>
       <c r="D291" s="7"/>
       <c r="E291" s="7"/>
@@ -13800,8 +15055,12 @@
       <c r="AM291" s="7"/>
       <c r="AN291" s="7"/>
       <c r="AO291" s="7"/>
-    </row>
-    <row r="292" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP291" s="7"/>
+      <c r="AQ291" s="7"/>
+      <c r="AR291" s="7"/>
+      <c r="AS291" s="7"/>
+    </row>
+    <row r="292" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C292" s="7"/>
       <c r="D292" s="7"/>
       <c r="E292" s="7"/>
@@ -13841,8 +15100,12 @@
       <c r="AM292" s="7"/>
       <c r="AN292" s="7"/>
       <c r="AO292" s="7"/>
-    </row>
-    <row r="293" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP292" s="7"/>
+      <c r="AQ292" s="7"/>
+      <c r="AR292" s="7"/>
+      <c r="AS292" s="7"/>
+    </row>
+    <row r="293" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C293" s="7"/>
       <c r="D293" s="7"/>
       <c r="E293" s="7"/>
@@ -13882,8 +15145,12 @@
       <c r="AM293" s="7"/>
       <c r="AN293" s="7"/>
       <c r="AO293" s="7"/>
-    </row>
-    <row r="294" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP293" s="7"/>
+      <c r="AQ293" s="7"/>
+      <c r="AR293" s="7"/>
+      <c r="AS293" s="7"/>
+    </row>
+    <row r="294" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C294" s="7"/>
       <c r="D294" s="7"/>
       <c r="E294" s="7"/>
@@ -13923,8 +15190,12 @@
       <c r="AM294" s="7"/>
       <c r="AN294" s="7"/>
       <c r="AO294" s="7"/>
-    </row>
-    <row r="295" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP294" s="7"/>
+      <c r="AQ294" s="7"/>
+      <c r="AR294" s="7"/>
+      <c r="AS294" s="7"/>
+    </row>
+    <row r="295" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C295" s="7"/>
       <c r="D295" s="7"/>
       <c r="E295" s="7"/>
@@ -13964,8 +15235,12 @@
       <c r="AM295" s="7"/>
       <c r="AN295" s="7"/>
       <c r="AO295" s="7"/>
-    </row>
-    <row r="296" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP295" s="7"/>
+      <c r="AQ295" s="7"/>
+      <c r="AR295" s="7"/>
+      <c r="AS295" s="7"/>
+    </row>
+    <row r="296" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C296" s="7"/>
       <c r="D296" s="7"/>
       <c r="E296" s="7"/>
@@ -14005,8 +15280,12 @@
       <c r="AM296" s="7"/>
       <c r="AN296" s="7"/>
       <c r="AO296" s="7"/>
-    </row>
-    <row r="297" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP296" s="7"/>
+      <c r="AQ296" s="7"/>
+      <c r="AR296" s="7"/>
+      <c r="AS296" s="7"/>
+    </row>
+    <row r="297" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C297" s="7"/>
       <c r="D297" s="7"/>
       <c r="E297" s="7"/>
@@ -14046,8 +15325,12 @@
       <c r="AM297" s="7"/>
       <c r="AN297" s="7"/>
       <c r="AO297" s="7"/>
-    </row>
-    <row r="298" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP297" s="7"/>
+      <c r="AQ297" s="7"/>
+      <c r="AR297" s="7"/>
+      <c r="AS297" s="7"/>
+    </row>
+    <row r="298" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C298" s="7"/>
       <c r="D298" s="7"/>
       <c r="E298" s="7"/>
@@ -14087,8 +15370,12 @@
       <c r="AM298" s="7"/>
       <c r="AN298" s="7"/>
       <c r="AO298" s="7"/>
-    </row>
-    <row r="299" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP298" s="7"/>
+      <c r="AQ298" s="7"/>
+      <c r="AR298" s="7"/>
+      <c r="AS298" s="7"/>
+    </row>
+    <row r="299" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C299" s="7"/>
       <c r="D299" s="7"/>
       <c r="E299" s="7"/>
@@ -14128,8 +15415,12 @@
       <c r="AM299" s="7"/>
       <c r="AN299" s="7"/>
       <c r="AO299" s="7"/>
-    </row>
-    <row r="300" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP299" s="7"/>
+      <c r="AQ299" s="7"/>
+      <c r="AR299" s="7"/>
+      <c r="AS299" s="7"/>
+    </row>
+    <row r="300" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C300" s="7"/>
       <c r="D300" s="7"/>
       <c r="E300" s="7"/>
@@ -14169,8 +15460,12 @@
       <c r="AM300" s="7"/>
       <c r="AN300" s="7"/>
       <c r="AO300" s="7"/>
-    </row>
-    <row r="301" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP300" s="7"/>
+      <c r="AQ300" s="7"/>
+      <c r="AR300" s="7"/>
+      <c r="AS300" s="7"/>
+    </row>
+    <row r="301" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C301" s="7"/>
       <c r="D301" s="7"/>
       <c r="E301" s="7"/>
@@ -14210,8 +15505,12 @@
       <c r="AM301" s="7"/>
       <c r="AN301" s="7"/>
       <c r="AO301" s="7"/>
-    </row>
-    <row r="302" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP301" s="7"/>
+      <c r="AQ301" s="7"/>
+      <c r="AR301" s="7"/>
+      <c r="AS301" s="7"/>
+    </row>
+    <row r="302" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C302" s="7"/>
       <c r="D302" s="7"/>
       <c r="E302" s="7"/>
@@ -14251,8 +15550,12 @@
       <c r="AM302" s="7"/>
       <c r="AN302" s="7"/>
       <c r="AO302" s="7"/>
-    </row>
-    <row r="303" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP302" s="7"/>
+      <c r="AQ302" s="7"/>
+      <c r="AR302" s="7"/>
+      <c r="AS302" s="7"/>
+    </row>
+    <row r="303" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C303" s="7"/>
       <c r="D303" s="7"/>
       <c r="E303" s="7"/>
@@ -14292,8 +15595,12 @@
       <c r="AM303" s="7"/>
       <c r="AN303" s="7"/>
       <c r="AO303" s="7"/>
-    </row>
-    <row r="304" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP303" s="7"/>
+      <c r="AQ303" s="7"/>
+      <c r="AR303" s="7"/>
+      <c r="AS303" s="7"/>
+    </row>
+    <row r="304" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C304" s="7"/>
       <c r="D304" s="7"/>
       <c r="E304" s="7"/>
@@ -14333,8 +15640,12 @@
       <c r="AM304" s="7"/>
       <c r="AN304" s="7"/>
       <c r="AO304" s="7"/>
-    </row>
-    <row r="305" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP304" s="7"/>
+      <c r="AQ304" s="7"/>
+      <c r="AR304" s="7"/>
+      <c r="AS304" s="7"/>
+    </row>
+    <row r="305" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C305" s="7"/>
       <c r="D305" s="7"/>
       <c r="E305" s="7"/>
@@ -14374,8 +15685,12 @@
       <c r="AM305" s="7"/>
       <c r="AN305" s="7"/>
       <c r="AO305" s="7"/>
-    </row>
-    <row r="306" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP305" s="7"/>
+      <c r="AQ305" s="7"/>
+      <c r="AR305" s="7"/>
+      <c r="AS305" s="7"/>
+    </row>
+    <row r="306" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C306" s="7"/>
       <c r="D306" s="7"/>
       <c r="E306" s="7"/>
@@ -14415,8 +15730,12 @@
       <c r="AM306" s="7"/>
       <c r="AN306" s="7"/>
       <c r="AO306" s="7"/>
-    </row>
-    <row r="307" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP306" s="7"/>
+      <c r="AQ306" s="7"/>
+      <c r="AR306" s="7"/>
+      <c r="AS306" s="7"/>
+    </row>
+    <row r="307" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C307" s="7"/>
       <c r="D307" s="7"/>
       <c r="E307" s="7"/>
@@ -14456,8 +15775,12 @@
       <c r="AM307" s="7"/>
       <c r="AN307" s="7"/>
       <c r="AO307" s="7"/>
-    </row>
-    <row r="308" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP307" s="7"/>
+      <c r="AQ307" s="7"/>
+      <c r="AR307" s="7"/>
+      <c r="AS307" s="7"/>
+    </row>
+    <row r="308" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C308" s="7"/>
       <c r="D308" s="7"/>
       <c r="E308" s="7"/>
@@ -14497,8 +15820,12 @@
       <c r="AM308" s="7"/>
       <c r="AN308" s="7"/>
       <c r="AO308" s="7"/>
-    </row>
-    <row r="309" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP308" s="7"/>
+      <c r="AQ308" s="7"/>
+      <c r="AR308" s="7"/>
+      <c r="AS308" s="7"/>
+    </row>
+    <row r="309" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C309" s="7"/>
       <c r="D309" s="7"/>
       <c r="E309" s="7"/>
@@ -14538,8 +15865,12 @@
       <c r="AM309" s="7"/>
       <c r="AN309" s="7"/>
       <c r="AO309" s="7"/>
-    </row>
-    <row r="310" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP309" s="7"/>
+      <c r="AQ309" s="7"/>
+      <c r="AR309" s="7"/>
+      <c r="AS309" s="7"/>
+    </row>
+    <row r="310" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C310" s="7"/>
       <c r="D310" s="7"/>
       <c r="E310" s="7"/>
@@ -14579,8 +15910,12 @@
       <c r="AM310" s="7"/>
       <c r="AN310" s="7"/>
       <c r="AO310" s="7"/>
-    </row>
-    <row r="311" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP310" s="7"/>
+      <c r="AQ310" s="7"/>
+      <c r="AR310" s="7"/>
+      <c r="AS310" s="7"/>
+    </row>
+    <row r="311" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C311" s="7"/>
       <c r="D311" s="7"/>
       <c r="E311" s="7"/>
@@ -14620,8 +15955,12 @@
       <c r="AM311" s="7"/>
       <c r="AN311" s="7"/>
       <c r="AO311" s="7"/>
-    </row>
-    <row r="312" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP311" s="7"/>
+      <c r="AQ311" s="7"/>
+      <c r="AR311" s="7"/>
+      <c r="AS311" s="7"/>
+    </row>
+    <row r="312" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C312" s="7"/>
       <c r="D312" s="7"/>
       <c r="E312" s="7"/>
@@ -14661,8 +16000,12 @@
       <c r="AM312" s="7"/>
       <c r="AN312" s="7"/>
       <c r="AO312" s="7"/>
-    </row>
-    <row r="313" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP312" s="7"/>
+      <c r="AQ312" s="7"/>
+      <c r="AR312" s="7"/>
+      <c r="AS312" s="7"/>
+    </row>
+    <row r="313" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C313" s="7"/>
       <c r="D313" s="7"/>
       <c r="E313" s="7"/>
@@ -14702,8 +16045,12 @@
       <c r="AM313" s="7"/>
       <c r="AN313" s="7"/>
       <c r="AO313" s="7"/>
-    </row>
-    <row r="314" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP313" s="7"/>
+      <c r="AQ313" s="7"/>
+      <c r="AR313" s="7"/>
+      <c r="AS313" s="7"/>
+    </row>
+    <row r="314" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C314" s="7"/>
       <c r="D314" s="7"/>
       <c r="E314" s="7"/>
@@ -14743,8 +16090,12 @@
       <c r="AM314" s="7"/>
       <c r="AN314" s="7"/>
       <c r="AO314" s="7"/>
-    </row>
-    <row r="315" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP314" s="7"/>
+      <c r="AQ314" s="7"/>
+      <c r="AR314" s="7"/>
+      <c r="AS314" s="7"/>
+    </row>
+    <row r="315" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C315" s="7"/>
       <c r="D315" s="7"/>
       <c r="E315" s="7"/>
@@ -14784,8 +16135,12 @@
       <c r="AM315" s="7"/>
       <c r="AN315" s="7"/>
       <c r="AO315" s="7"/>
-    </row>
-    <row r="316" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP315" s="7"/>
+      <c r="AQ315" s="7"/>
+      <c r="AR315" s="7"/>
+      <c r="AS315" s="7"/>
+    </row>
+    <row r="316" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C316" s="7"/>
       <c r="D316" s="7"/>
       <c r="E316" s="7"/>
@@ -14825,8 +16180,12 @@
       <c r="AM316" s="7"/>
       <c r="AN316" s="7"/>
       <c r="AO316" s="7"/>
-    </row>
-    <row r="317" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP316" s="7"/>
+      <c r="AQ316" s="7"/>
+      <c r="AR316" s="7"/>
+      <c r="AS316" s="7"/>
+    </row>
+    <row r="317" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C317" s="7"/>
       <c r="D317" s="7"/>
       <c r="E317" s="7"/>
@@ -14866,8 +16225,12 @@
       <c r="AM317" s="7"/>
       <c r="AN317" s="7"/>
       <c r="AO317" s="7"/>
-    </row>
-    <row r="318" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP317" s="7"/>
+      <c r="AQ317" s="7"/>
+      <c r="AR317" s="7"/>
+      <c r="AS317" s="7"/>
+    </row>
+    <row r="318" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C318" s="7"/>
       <c r="D318" s="7"/>
       <c r="E318" s="7"/>
@@ -14907,8 +16270,12 @@
       <c r="AM318" s="7"/>
       <c r="AN318" s="7"/>
       <c r="AO318" s="7"/>
-    </row>
-    <row r="319" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP318" s="7"/>
+      <c r="AQ318" s="7"/>
+      <c r="AR318" s="7"/>
+      <c r="AS318" s="7"/>
+    </row>
+    <row r="319" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C319" s="7"/>
       <c r="D319" s="7"/>
       <c r="E319" s="7"/>
@@ -14948,8 +16315,12 @@
       <c r="AM319" s="7"/>
       <c r="AN319" s="7"/>
       <c r="AO319" s="7"/>
-    </row>
-    <row r="320" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP319" s="7"/>
+      <c r="AQ319" s="7"/>
+      <c r="AR319" s="7"/>
+      <c r="AS319" s="7"/>
+    </row>
+    <row r="320" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C320" s="7"/>
       <c r="D320" s="7"/>
       <c r="E320" s="7"/>
@@ -14989,8 +16360,12 @@
       <c r="AM320" s="7"/>
       <c r="AN320" s="7"/>
       <c r="AO320" s="7"/>
-    </row>
-    <row r="321" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP320" s="7"/>
+      <c r="AQ320" s="7"/>
+      <c r="AR320" s="7"/>
+      <c r="AS320" s="7"/>
+    </row>
+    <row r="321" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C321" s="7"/>
       <c r="D321" s="7"/>
       <c r="E321" s="7"/>
@@ -15030,8 +16405,12 @@
       <c r="AM321" s="7"/>
       <c r="AN321" s="7"/>
       <c r="AO321" s="7"/>
-    </row>
-    <row r="322" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP321" s="7"/>
+      <c r="AQ321" s="7"/>
+      <c r="AR321" s="7"/>
+      <c r="AS321" s="7"/>
+    </row>
+    <row r="322" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C322" s="7"/>
       <c r="D322" s="7"/>
       <c r="E322" s="7"/>
@@ -15071,8 +16450,12 @@
       <c r="AM322" s="7"/>
       <c r="AN322" s="7"/>
       <c r="AO322" s="7"/>
-    </row>
-    <row r="323" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP322" s="7"/>
+      <c r="AQ322" s="7"/>
+      <c r="AR322" s="7"/>
+      <c r="AS322" s="7"/>
+    </row>
+    <row r="323" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C323" s="7"/>
       <c r="D323" s="7"/>
       <c r="E323" s="7"/>
@@ -15112,8 +16495,12 @@
       <c r="AM323" s="7"/>
       <c r="AN323" s="7"/>
       <c r="AO323" s="7"/>
-    </row>
-    <row r="324" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP323" s="7"/>
+      <c r="AQ323" s="7"/>
+      <c r="AR323" s="7"/>
+      <c r="AS323" s="7"/>
+    </row>
+    <row r="324" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C324" s="7"/>
       <c r="D324" s="7"/>
       <c r="E324" s="7"/>
@@ -15153,8 +16540,12 @@
       <c r="AM324" s="7"/>
       <c r="AN324" s="7"/>
       <c r="AO324" s="7"/>
-    </row>
-    <row r="325" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP324" s="7"/>
+      <c r="AQ324" s="7"/>
+      <c r="AR324" s="7"/>
+      <c r="AS324" s="7"/>
+    </row>
+    <row r="325" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C325" s="7"/>
       <c r="D325" s="7"/>
       <c r="E325" s="7"/>
@@ -15194,8 +16585,12 @@
       <c r="AM325" s="7"/>
       <c r="AN325" s="7"/>
       <c r="AO325" s="7"/>
-    </row>
-    <row r="326" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP325" s="7"/>
+      <c r="AQ325" s="7"/>
+      <c r="AR325" s="7"/>
+      <c r="AS325" s="7"/>
+    </row>
+    <row r="326" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C326" s="7"/>
       <c r="D326" s="7"/>
       <c r="E326" s="7"/>
@@ -15235,8 +16630,12 @@
       <c r="AM326" s="7"/>
       <c r="AN326" s="7"/>
       <c r="AO326" s="7"/>
-    </row>
-    <row r="327" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP326" s="7"/>
+      <c r="AQ326" s="7"/>
+      <c r="AR326" s="7"/>
+      <c r="AS326" s="7"/>
+    </row>
+    <row r="327" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C327" s="7"/>
       <c r="D327" s="7"/>
       <c r="E327" s="7"/>
@@ -15276,8 +16675,12 @@
       <c r="AM327" s="7"/>
       <c r="AN327" s="7"/>
       <c r="AO327" s="7"/>
-    </row>
-    <row r="328" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP327" s="7"/>
+      <c r="AQ327" s="7"/>
+      <c r="AR327" s="7"/>
+      <c r="AS327" s="7"/>
+    </row>
+    <row r="328" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C328" s="7"/>
       <c r="D328" s="7"/>
       <c r="E328" s="7"/>
@@ -15317,8 +16720,12 @@
       <c r="AM328" s="7"/>
       <c r="AN328" s="7"/>
       <c r="AO328" s="7"/>
-    </row>
-    <row r="329" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP328" s="7"/>
+      <c r="AQ328" s="7"/>
+      <c r="AR328" s="7"/>
+      <c r="AS328" s="7"/>
+    </row>
+    <row r="329" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C329" s="7"/>
       <c r="D329" s="7"/>
       <c r="E329" s="7"/>
@@ -15358,8 +16765,12 @@
       <c r="AM329" s="7"/>
       <c r="AN329" s="7"/>
       <c r="AO329" s="7"/>
-    </row>
-    <row r="330" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP329" s="7"/>
+      <c r="AQ329" s="7"/>
+      <c r="AR329" s="7"/>
+      <c r="AS329" s="7"/>
+    </row>
+    <row r="330" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C330" s="7"/>
       <c r="D330" s="7"/>
       <c r="E330" s="7"/>
@@ -15399,8 +16810,12 @@
       <c r="AM330" s="7"/>
       <c r="AN330" s="7"/>
       <c r="AO330" s="7"/>
-    </row>
-    <row r="331" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP330" s="7"/>
+      <c r="AQ330" s="7"/>
+      <c r="AR330" s="7"/>
+      <c r="AS330" s="7"/>
+    </row>
+    <row r="331" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C331" s="7"/>
       <c r="D331" s="7"/>
       <c r="E331" s="7"/>
@@ -15440,8 +16855,12 @@
       <c r="AM331" s="7"/>
       <c r="AN331" s="7"/>
       <c r="AO331" s="7"/>
-    </row>
-    <row r="332" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP331" s="7"/>
+      <c r="AQ331" s="7"/>
+      <c r="AR331" s="7"/>
+      <c r="AS331" s="7"/>
+    </row>
+    <row r="332" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C332" s="7"/>
       <c r="D332" s="7"/>
       <c r="E332" s="7"/>
@@ -15481,8 +16900,12 @@
       <c r="AM332" s="7"/>
       <c r="AN332" s="7"/>
       <c r="AO332" s="7"/>
-    </row>
-    <row r="333" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP332" s="7"/>
+      <c r="AQ332" s="7"/>
+      <c r="AR332" s="7"/>
+      <c r="AS332" s="7"/>
+    </row>
+    <row r="333" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C333" s="7"/>
       <c r="D333" s="7"/>
       <c r="E333" s="7"/>
@@ -15522,8 +16945,12 @@
       <c r="AM333" s="7"/>
       <c r="AN333" s="7"/>
       <c r="AO333" s="7"/>
-    </row>
-    <row r="334" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP333" s="7"/>
+      <c r="AQ333" s="7"/>
+      <c r="AR333" s="7"/>
+      <c r="AS333" s="7"/>
+    </row>
+    <row r="334" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C334" s="7"/>
       <c r="D334" s="7"/>
       <c r="E334" s="7"/>
@@ -15563,8 +16990,12 @@
       <c r="AM334" s="7"/>
       <c r="AN334" s="7"/>
       <c r="AO334" s="7"/>
-    </row>
-    <row r="335" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP334" s="7"/>
+      <c r="AQ334" s="7"/>
+      <c r="AR334" s="7"/>
+      <c r="AS334" s="7"/>
+    </row>
+    <row r="335" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C335" s="7"/>
       <c r="D335" s="7"/>
       <c r="E335" s="7"/>
@@ -15604,8 +17035,12 @@
       <c r="AM335" s="7"/>
       <c r="AN335" s="7"/>
       <c r="AO335" s="7"/>
-    </row>
-    <row r="336" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP335" s="7"/>
+      <c r="AQ335" s="7"/>
+      <c r="AR335" s="7"/>
+      <c r="AS335" s="7"/>
+    </row>
+    <row r="336" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C336" s="7"/>
       <c r="D336" s="7"/>
       <c r="E336" s="7"/>
@@ -15645,8 +17080,12 @@
       <c r="AM336" s="7"/>
       <c r="AN336" s="7"/>
       <c r="AO336" s="7"/>
-    </row>
-    <row r="337" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP336" s="7"/>
+      <c r="AQ336" s="7"/>
+      <c r="AR336" s="7"/>
+      <c r="AS336" s="7"/>
+    </row>
+    <row r="337" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C337" s="7"/>
       <c r="D337" s="7"/>
       <c r="E337" s="7"/>
@@ -15686,8 +17125,12 @@
       <c r="AM337" s="7"/>
       <c r="AN337" s="7"/>
       <c r="AO337" s="7"/>
-    </row>
-    <row r="338" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP337" s="7"/>
+      <c r="AQ337" s="7"/>
+      <c r="AR337" s="7"/>
+      <c r="AS337" s="7"/>
+    </row>
+    <row r="338" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C338" s="7"/>
       <c r="D338" s="7"/>
       <c r="E338" s="7"/>
@@ -15727,8 +17170,12 @@
       <c r="AM338" s="7"/>
       <c r="AN338" s="7"/>
       <c r="AO338" s="7"/>
-    </row>
-    <row r="339" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP338" s="7"/>
+      <c r="AQ338" s="7"/>
+      <c r="AR338" s="7"/>
+      <c r="AS338" s="7"/>
+    </row>
+    <row r="339" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C339" s="7"/>
       <c r="D339" s="7"/>
       <c r="E339" s="7"/>
@@ -15768,8 +17215,12 @@
       <c r="AM339" s="7"/>
       <c r="AN339" s="7"/>
       <c r="AO339" s="7"/>
-    </row>
-    <row r="340" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP339" s="7"/>
+      <c r="AQ339" s="7"/>
+      <c r="AR339" s="7"/>
+      <c r="AS339" s="7"/>
+    </row>
+    <row r="340" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C340" s="7"/>
       <c r="D340" s="7"/>
       <c r="E340" s="7"/>
@@ -15809,8 +17260,12 @@
       <c r="AM340" s="7"/>
       <c r="AN340" s="7"/>
       <c r="AO340" s="7"/>
-    </row>
-    <row r="341" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP340" s="7"/>
+      <c r="AQ340" s="7"/>
+      <c r="AR340" s="7"/>
+      <c r="AS340" s="7"/>
+    </row>
+    <row r="341" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C341" s="7"/>
       <c r="D341" s="7"/>
       <c r="E341" s="7"/>
@@ -15850,8 +17305,12 @@
       <c r="AM341" s="7"/>
       <c r="AN341" s="7"/>
       <c r="AO341" s="7"/>
-    </row>
-    <row r="342" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP341" s="7"/>
+      <c r="AQ341" s="7"/>
+      <c r="AR341" s="7"/>
+      <c r="AS341" s="7"/>
+    </row>
+    <row r="342" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C342" s="7"/>
       <c r="D342" s="7"/>
       <c r="E342" s="7"/>
@@ -15891,8 +17350,12 @@
       <c r="AM342" s="7"/>
       <c r="AN342" s="7"/>
       <c r="AO342" s="7"/>
-    </row>
-    <row r="343" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP342" s="7"/>
+      <c r="AQ342" s="7"/>
+      <c r="AR342" s="7"/>
+      <c r="AS342" s="7"/>
+    </row>
+    <row r="343" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C343" s="7"/>
       <c r="D343" s="7"/>
       <c r="E343" s="7"/>
@@ -15932,8 +17395,12 @@
       <c r="AM343" s="7"/>
       <c r="AN343" s="7"/>
       <c r="AO343" s="7"/>
-    </row>
-    <row r="344" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP343" s="7"/>
+      <c r="AQ343" s="7"/>
+      <c r="AR343" s="7"/>
+      <c r="AS343" s="7"/>
+    </row>
+    <row r="344" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C344" s="7"/>
       <c r="D344" s="7"/>
       <c r="E344" s="7"/>
@@ -15973,8 +17440,12 @@
       <c r="AM344" s="7"/>
       <c r="AN344" s="7"/>
       <c r="AO344" s="7"/>
-    </row>
-    <row r="345" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP344" s="7"/>
+      <c r="AQ344" s="7"/>
+      <c r="AR344" s="7"/>
+      <c r="AS344" s="7"/>
+    </row>
+    <row r="345" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C345" s="7"/>
       <c r="D345" s="7"/>
       <c r="E345" s="7"/>
@@ -16014,8 +17485,12 @@
       <c r="AM345" s="7"/>
       <c r="AN345" s="7"/>
       <c r="AO345" s="7"/>
-    </row>
-    <row r="346" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP345" s="7"/>
+      <c r="AQ345" s="7"/>
+      <c r="AR345" s="7"/>
+      <c r="AS345" s="7"/>
+    </row>
+    <row r="346" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C346" s="7"/>
       <c r="D346" s="7"/>
       <c r="E346" s="7"/>
@@ -16055,8 +17530,12 @@
       <c r="AM346" s="7"/>
       <c r="AN346" s="7"/>
       <c r="AO346" s="7"/>
-    </row>
-    <row r="347" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP346" s="7"/>
+      <c r="AQ346" s="7"/>
+      <c r="AR346" s="7"/>
+      <c r="AS346" s="7"/>
+    </row>
+    <row r="347" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C347" s="7"/>
       <c r="D347" s="7"/>
       <c r="E347" s="7"/>
@@ -16096,8 +17575,12 @@
       <c r="AM347" s="7"/>
       <c r="AN347" s="7"/>
       <c r="AO347" s="7"/>
-    </row>
-    <row r="348" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP347" s="7"/>
+      <c r="AQ347" s="7"/>
+      <c r="AR347" s="7"/>
+      <c r="AS347" s="7"/>
+    </row>
+    <row r="348" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C348" s="7"/>
       <c r="D348" s="7"/>
       <c r="E348" s="7"/>
@@ -16137,8 +17620,12 @@
       <c r="AM348" s="7"/>
       <c r="AN348" s="7"/>
       <c r="AO348" s="7"/>
-    </row>
-    <row r="349" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP348" s="7"/>
+      <c r="AQ348" s="7"/>
+      <c r="AR348" s="7"/>
+      <c r="AS348" s="7"/>
+    </row>
+    <row r="349" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C349" s="7"/>
       <c r="D349" s="7"/>
       <c r="E349" s="7"/>
@@ -16178,8 +17665,12 @@
       <c r="AM349" s="7"/>
       <c r="AN349" s="7"/>
       <c r="AO349" s="7"/>
-    </row>
-    <row r="350" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP349" s="7"/>
+      <c r="AQ349" s="7"/>
+      <c r="AR349" s="7"/>
+      <c r="AS349" s="7"/>
+    </row>
+    <row r="350" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C350" s="7"/>
       <c r="D350" s="7"/>
       <c r="E350" s="7"/>
@@ -16219,8 +17710,12 @@
       <c r="AM350" s="7"/>
       <c r="AN350" s="7"/>
       <c r="AO350" s="7"/>
-    </row>
-    <row r="351" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP350" s="7"/>
+      <c r="AQ350" s="7"/>
+      <c r="AR350" s="7"/>
+      <c r="AS350" s="7"/>
+    </row>
+    <row r="351" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C351" s="7"/>
       <c r="D351" s="7"/>
       <c r="E351" s="7"/>
@@ -16260,8 +17755,12 @@
       <c r="AM351" s="7"/>
       <c r="AN351" s="7"/>
       <c r="AO351" s="7"/>
-    </row>
-    <row r="352" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP351" s="7"/>
+      <c r="AQ351" s="7"/>
+      <c r="AR351" s="7"/>
+      <c r="AS351" s="7"/>
+    </row>
+    <row r="352" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C352" s="7"/>
       <c r="D352" s="7"/>
       <c r="E352" s="7"/>
@@ -16301,8 +17800,12 @@
       <c r="AM352" s="7"/>
       <c r="AN352" s="7"/>
       <c r="AO352" s="7"/>
-    </row>
-    <row r="353" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP352" s="7"/>
+      <c r="AQ352" s="7"/>
+      <c r="AR352" s="7"/>
+      <c r="AS352" s="7"/>
+    </row>
+    <row r="353" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C353" s="7"/>
       <c r="D353" s="7"/>
       <c r="E353" s="7"/>
@@ -16342,8 +17845,12 @@
       <c r="AM353" s="7"/>
       <c r="AN353" s="7"/>
       <c r="AO353" s="7"/>
-    </row>
-    <row r="354" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP353" s="7"/>
+      <c r="AQ353" s="7"/>
+      <c r="AR353" s="7"/>
+      <c r="AS353" s="7"/>
+    </row>
+    <row r="354" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C354" s="7"/>
       <c r="D354" s="7"/>
       <c r="E354" s="7"/>
@@ -16383,8 +17890,12 @@
       <c r="AM354" s="7"/>
       <c r="AN354" s="7"/>
       <c r="AO354" s="7"/>
-    </row>
-    <row r="355" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP354" s="7"/>
+      <c r="AQ354" s="7"/>
+      <c r="AR354" s="7"/>
+      <c r="AS354" s="7"/>
+    </row>
+    <row r="355" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C355" s="7"/>
       <c r="D355" s="7"/>
       <c r="E355" s="7"/>
@@ -16424,8 +17935,12 @@
       <c r="AM355" s="7"/>
       <c r="AN355" s="7"/>
       <c r="AO355" s="7"/>
-    </row>
-    <row r="356" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP355" s="7"/>
+      <c r="AQ355" s="7"/>
+      <c r="AR355" s="7"/>
+      <c r="AS355" s="7"/>
+    </row>
+    <row r="356" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C356" s="7"/>
       <c r="D356" s="7"/>
       <c r="E356" s="7"/>
@@ -16465,8 +17980,12 @@
       <c r="AM356" s="7"/>
       <c r="AN356" s="7"/>
       <c r="AO356" s="7"/>
-    </row>
-    <row r="357" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP356" s="7"/>
+      <c r="AQ356" s="7"/>
+      <c r="AR356" s="7"/>
+      <c r="AS356" s="7"/>
+    </row>
+    <row r="357" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C357" s="7"/>
       <c r="D357" s="7"/>
       <c r="E357" s="7"/>
@@ -16506,8 +18025,12 @@
       <c r="AM357" s="7"/>
       <c r="AN357" s="7"/>
       <c r="AO357" s="7"/>
-    </row>
-    <row r="358" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP357" s="7"/>
+      <c r="AQ357" s="7"/>
+      <c r="AR357" s="7"/>
+      <c r="AS357" s="7"/>
+    </row>
+    <row r="358" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C358" s="7"/>
       <c r="D358" s="7"/>
       <c r="E358" s="7"/>
@@ -16547,8 +18070,12 @@
       <c r="AM358" s="7"/>
       <c r="AN358" s="7"/>
       <c r="AO358" s="7"/>
-    </row>
-    <row r="359" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP358" s="7"/>
+      <c r="AQ358" s="7"/>
+      <c r="AR358" s="7"/>
+      <c r="AS358" s="7"/>
+    </row>
+    <row r="359" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C359" s="7"/>
       <c r="D359" s="7"/>
       <c r="E359" s="7"/>
@@ -16588,8 +18115,12 @@
       <c r="AM359" s="7"/>
       <c r="AN359" s="7"/>
       <c r="AO359" s="7"/>
-    </row>
-    <row r="360" spans="3:41" x14ac:dyDescent="0.2">
+      <c r="AP359" s="7"/>
+      <c r="AQ359" s="7"/>
+      <c r="AR359" s="7"/>
+      <c r="AS359" s="7"/>
+    </row>
+    <row r="360" spans="3:45" x14ac:dyDescent="0.2">
       <c r="C360" s="7"/>
       <c r="D360" s="7"/>
       <c r="E360" s="7"/>
@@ -16629,6 +18160,10 @@
       <c r="AM360" s="7"/>
       <c r="AN360" s="7"/>
       <c r="AO360" s="7"/>
+      <c r="AP360" s="7"/>
+      <c r="AQ360" s="7"/>
+      <c r="AR360" s="7"/>
+      <c r="AS360" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/ASML.xlsx
+++ b/ASML.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BB28B4-8873-4B45-9F3B-C46881BC08FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B32A80-1D7A-407C-8326-3041430C4D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{40E26FA9-FA23-47D9-8A0D-17BDAE3930EB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="60">
   <si>
     <t>numbers in mio EUR</t>
   </si>
@@ -228,13 +228,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -310,30 +316,34 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -747,19 +757,19 @@
       <c r="G2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="2">
-        <v>1250.8</v>
+      <c r="H2" s="3">
+        <v>1537</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="7">
-        <v>385.4</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>44</v>
+      <c r="H3" s="15">
+        <v>384.5</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -777,7 +787,7 @@
       </c>
       <c r="H4" s="3">
         <f>+H2*H3</f>
-        <v>482058.31999999995</v>
+        <v>590976.5</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -788,11 +798,11 @@
         <v>5</v>
       </c>
       <c r="H5" s="3">
-        <f>7970.4+405.9</f>
-        <v>8376.2999999999993</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>44</v>
+        <f>6671.9+909.6</f>
+        <v>7581.5</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -800,10 +810,10 @@
         <v>6</v>
       </c>
       <c r="H6" s="3">
-        <v>2705.6</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>44</v>
+        <v>1984.4</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -812,7 +822,7 @@
       </c>
       <c r="H7" s="3">
         <f>+H4-H5+H6</f>
-        <v>476387.61999999994</v>
+        <v>585379.4</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -955,7 +965,9 @@
       <c r="O3" s="7">
         <v>6279.4</v>
       </c>
-      <c r="P3" s="7"/>
+      <c r="P3" s="7">
+        <v>6564.8</v>
+      </c>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
@@ -1031,7 +1043,9 @@
       <c r="O4" s="7">
         <v>2487.5</v>
       </c>
-      <c r="P4" s="7"/>
+      <c r="P4" s="7">
+        <v>2761.7</v>
+      </c>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
@@ -1099,7 +1113,7 @@
         <v>6902.3</v>
       </c>
       <c r="I5" s="8">
-        <f t="shared" ref="I5:O5" si="1">+I3+I4</f>
+        <f t="shared" ref="I5:P5" si="1">+I3+I4</f>
         <v>6673</v>
       </c>
       <c r="J5" s="8">
@@ -1126,7 +1140,10 @@
         <f t="shared" si="1"/>
         <v>8766.9</v>
       </c>
-      <c r="P5" s="8"/>
+      <c r="P5" s="8">
+        <f t="shared" si="1"/>
+        <v>9326.5</v>
+      </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
       <c r="S5" s="7"/>
@@ -1215,7 +1232,9 @@
       <c r="O6" s="7">
         <v>4121.8999999999996</v>
       </c>
-      <c r="P6" s="7"/>
+      <c r="P6" s="7">
+        <v>4291.1000000000004</v>
+      </c>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
@@ -1297,7 +1316,9 @@
       <c r="O7" s="7">
         <v>0</v>
       </c>
-      <c r="P7" s="7"/>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
@@ -1349,7 +1370,7 @@
         <v>3212.1999999999994</v>
       </c>
       <c r="E8" s="7">
-        <f t="shared" ref="E8:O8" si="3">+E5-E6</f>
+        <f t="shared" ref="E8:P8" si="3">+E5-E6</f>
         <v>3717.3</v>
       </c>
       <c r="F8" s="7">
@@ -1392,7 +1413,10 @@
         <f t="shared" si="3"/>
         <v>4645</v>
       </c>
-      <c r="P8" s="7"/>
+      <c r="P8" s="7">
+        <f t="shared" si="3"/>
+        <v>5035.3999999999996</v>
+      </c>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
@@ -1481,7 +1505,9 @@
       <c r="O9" s="7">
         <v>1184.9000000000001</v>
       </c>
-      <c r="P9" s="7"/>
+      <c r="P9" s="7">
+        <v>1276.5999999999999</v>
+      </c>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
@@ -1557,7 +1583,9 @@
       <c r="O10" s="7">
         <v>302.3</v>
       </c>
-      <c r="P10" s="7"/>
+      <c r="P10" s="7">
+        <v>302.7</v>
+      </c>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
@@ -1652,7 +1680,10 @@
         <f t="shared" si="5"/>
         <v>3157.8</v>
       </c>
-      <c r="P11" s="7"/>
+      <c r="P11" s="7">
+        <f t="shared" si="5"/>
+        <v>3456.0999999999995</v>
+      </c>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
@@ -1741,7 +1772,9 @@
       <c r="O12" s="7">
         <v>40.9</v>
       </c>
-      <c r="P12" s="7"/>
+      <c r="P12" s="7">
+        <v>30</v>
+      </c>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
@@ -1836,7 +1869,10 @@
         <f t="shared" si="7"/>
         <v>3198.7000000000003</v>
       </c>
-      <c r="P13" s="7"/>
+      <c r="P13" s="7">
+        <f t="shared" si="7"/>
+        <v>3486.0999999999995</v>
+      </c>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
@@ -1925,7 +1961,9 @@
       <c r="O14" s="7">
         <v>546.6</v>
       </c>
-      <c r="P14" s="7"/>
+      <c r="P14" s="7">
+        <v>609.6</v>
+      </c>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
@@ -2020,7 +2058,10 @@
         <f t="shared" si="9"/>
         <v>2652.1000000000004</v>
       </c>
-      <c r="P15" s="7"/>
+      <c r="P15" s="7">
+        <f t="shared" si="9"/>
+        <v>2876.4999999999995</v>
+      </c>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
@@ -2109,7 +2150,9 @@
       <c r="O16" s="7">
         <v>104.6</v>
       </c>
-      <c r="P16" s="7"/>
+      <c r="P16" s="7">
+        <v>41.1</v>
+      </c>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
@@ -2204,7 +2247,10 @@
         <f t="shared" si="11"/>
         <v>2756.7000000000003</v>
       </c>
-      <c r="P17" s="7"/>
+      <c r="P17" s="7">
+        <f t="shared" si="11"/>
+        <v>2917.5999999999995</v>
+      </c>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
@@ -2334,7 +2380,7 @@
         <v>4.8129130655821033</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" ref="J19:O19" si="13">+J17/J20</f>
+        <f t="shared" ref="J19:P19" si="13">+J17/J20</f>
         <v>6.8482074752097626</v>
       </c>
       <c r="K19" s="9">
@@ -2357,7 +2403,10 @@
         <f t="shared" si="13"/>
         <v>7.1528282304099644</v>
       </c>
-      <c r="P19" s="9"/>
+      <c r="P19" s="9">
+        <f t="shared" si="13"/>
+        <v>7.5880364109232756</v>
+      </c>
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
       <c r="S19" s="7"/>
@@ -2435,7 +2484,9 @@
       <c r="O20" s="7">
         <v>385.4</v>
       </c>
-      <c r="P20" s="7"/>
+      <c r="P20" s="15">
+        <v>384.5</v>
+      </c>
       <c r="Q20" s="7"/>
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
@@ -2563,7 +2614,10 @@
         <f t="shared" si="22"/>
         <v>9.3895895756393344E-2</v>
       </c>
-      <c r="P22" s="10"/>
+      <c r="P22" s="10">
+        <f t="shared" ref="P22:P24" si="23">+P3/L3-1</f>
+        <v>0.17310269652079113</v>
+      </c>
       <c r="Q22" s="10"/>
       <c r="R22" s="10"/>
       <c r="S22" s="7"/>
@@ -2572,15 +2626,15 @@
       <c r="V22" s="7"/>
       <c r="W22" s="7"/>
       <c r="X22" s="10">
-        <f t="shared" ref="X22:Z23" si="23">+X3/W3-1</f>
+        <f t="shared" ref="X22:Z23" si="24">+X3/W3-1</f>
         <v>0.42178700349312703</v>
       </c>
       <c r="Y22" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-7.7443410244955047E-3</v>
       </c>
       <c r="Z22" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.12428854272418643</v>
       </c>
       <c r="AA22" s="7"/>
@@ -2647,7 +2701,10 @@
         <f t="shared" si="22"/>
         <v>0.24306631352755992</v>
       </c>
-      <c r="P23" s="10"/>
+      <c r="P23" s="10">
+        <f t="shared" si="23"/>
+        <v>0.31785646115670918</v>
+      </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
       <c r="S23" s="7"/>
@@ -2656,15 +2713,15 @@
       <c r="V23" s="7"/>
       <c r="W23" s="7"/>
       <c r="X23" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>-2.1451829151503676E-2</v>
       </c>
       <c r="Y23" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.15557216320575096</v>
       </c>
       <c r="Z23" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.26158726248036723</v>
       </c>
       <c r="AA23" s="7"/>
@@ -2731,7 +2788,10 @@
         <f t="shared" si="22"/>
         <v>0.13245495059097068</v>
       </c>
-      <c r="P24" s="11"/>
+      <c r="P24" s="11">
+        <f t="shared" si="23"/>
+        <v>0.21254079072246701</v>
+      </c>
       <c r="Q24" s="11"/>
       <c r="R24" s="11"/>
       <c r="S24" s="7"/>
@@ -2739,11 +2799,11 @@
       <c r="U24" s="7"/>
       <c r="V24" s="7"/>
       <c r="W24" s="11" t="e">
-        <f t="shared" ref="W24:X24" si="24">+W5/V5-1</f>
+        <f t="shared" ref="W24:X24" si="25">+W5/V5-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="X24" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.30156233765007023</v>
       </c>
       <c r="Y24" s="11">
@@ -2817,7 +2877,9 @@
       <c r="O25" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="P25" s="12"/>
+      <c r="P25" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="Q25" s="12"/>
       <c r="R25" s="12"/>
       <c r="S25" s="7"/>
@@ -2825,11 +2887,11 @@
       <c r="U25" s="7"/>
       <c r="V25" s="7"/>
       <c r="W25" s="10">
-        <f t="shared" ref="W25:X25" si="25">+(W3-W6)/W3</f>
+        <f t="shared" ref="W25:X25" si="26">+(W3-W6)/W3</f>
         <v>0.50860968354471392</v>
       </c>
       <c r="X25" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.53729955421038711</v>
       </c>
       <c r="Y25" s="10">
@@ -2903,7 +2965,9 @@
       <c r="O26" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="P26" s="12"/>
+      <c r="P26" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="Q26" s="12"/>
       <c r="R26" s="12"/>
       <c r="S26" s="7"/>
@@ -2911,11 +2975,11 @@
       <c r="U26" s="7"/>
       <c r="V26" s="7"/>
       <c r="W26" s="10">
-        <f t="shared" ref="W26:X26" si="26">+(W4-W7)/W4</f>
+        <f t="shared" ref="W26:X26" si="27">+(W4-W7)/W4</f>
         <v>0.49661332729710439</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.41788999804266974</v>
       </c>
       <c r="Y26" s="10">
@@ -2951,27 +3015,27 @@
         <v>48</v>
       </c>
       <c r="C27" s="10" t="e">
-        <f t="shared" ref="C27:H27" si="27">+C8/C5</f>
+        <f t="shared" ref="C27:H27" si="28">+C8/C5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D27" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.51454475555840329</v>
       </c>
       <c r="E27" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.5136520657731104</v>
       </c>
       <c r="F27" s="10" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G27" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.50975425330812851</v>
       </c>
       <c r="H27" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.5134520377265549</v>
       </c>
       <c r="I27" s="10">
@@ -2979,59 +3043,62 @@
         <v>0.51874719016933912</v>
       </c>
       <c r="J27" s="10">
-        <f t="shared" ref="J27:N27" si="28">+J8/J5</f>
+        <f t="shared" ref="J27:N27" si="29">+J8/J5</f>
         <v>0.51710066070734551</v>
       </c>
       <c r="K27" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.53990828650778266</v>
       </c>
       <c r="L27" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.53687741331565197</v>
       </c>
       <c r="M27" s="10">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.51627195316657803</v>
       </c>
       <c r="N27" s="10" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O27" s="10">
-        <f t="shared" ref="O27" si="29">+O8/O5</f>
+        <f t="shared" ref="O27:P27" si="30">+O8/O5</f>
         <v>0.52983380670476454</v>
       </c>
-      <c r="P27" s="10"/>
+      <c r="P27" s="10">
+        <f t="shared" si="30"/>
+        <v>0.53990242856376991</v>
+      </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7"/>
       <c r="T27" s="10" t="e">
-        <f t="shared" ref="T27:Y27" si="30">+T8/T5</f>
+        <f t="shared" ref="T27:Y27" si="31">+T8/T5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U27" s="10" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V27" s="10" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W27" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.50535577658760522</v>
       </c>
       <c r="X27" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.51294881796904768</v>
       </c>
       <c r="Y27" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.51275700653506895</v>
       </c>
       <c r="Z27" s="10">
-        <f t="shared" ref="Z27" si="31">+Z8/Z5</f>
+        <f t="shared" ref="Z27" si="32">+Z8/Z5</f>
         <v>0.52829587997783722</v>
       </c>
       <c r="AA27" s="7"/>
@@ -3059,27 +3126,27 @@
         <v>49</v>
       </c>
       <c r="C28" s="10" t="e">
-        <f t="shared" ref="C28:H28" si="32">+C11/C5</f>
+        <f t="shared" ref="C28:H28" si="33">+C11/C5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.29387454347408209</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.33050987978444107</v>
       </c>
       <c r="F28" s="10" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.26302457466918711</v>
       </c>
       <c r="H28" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.32786172725033685</v>
       </c>
       <c r="I28" s="10">
@@ -3087,59 +3154,62 @@
         <v>0.32704930316199604</v>
       </c>
       <c r="J28" s="10">
-        <f t="shared" ref="J28:N28" si="33">+J11/J5</f>
+        <f t="shared" ref="J28:N28" si="34">+J11/J5</f>
         <v>0.36224467763527224</v>
       </c>
       <c r="K28" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.35366531034037324</v>
       </c>
       <c r="L28" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.34636036246863511</v>
       </c>
       <c r="M28" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.32841937200638638</v>
       </c>
       <c r="N28" s="10" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O28" s="10">
-        <f t="shared" ref="O28" si="34">+O11/O5</f>
+        <f t="shared" ref="O28:P28" si="35">+O11/O5</f>
         <v>0.36019573623515727</v>
       </c>
-      <c r="P28" s="10"/>
+      <c r="P28" s="10">
+        <f t="shared" si="35"/>
+        <v>0.37056773709322893</v>
+      </c>
       <c r="Q28" s="10"/>
       <c r="R28" s="10"/>
       <c r="S28" s="7"/>
       <c r="T28" s="10" t="e">
-        <f t="shared" ref="T28:Y28" si="35">+T11/T5</f>
+        <f t="shared" ref="T28:Y28" si="36">+T11/T5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U28" s="10" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V28" s="10" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W28" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.30702201819263802</v>
       </c>
       <c r="X28" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.3281129234174574</v>
       </c>
       <c r="Y28" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.3192382947255944</v>
       </c>
       <c r="Z28" s="10">
-        <f t="shared" ref="Z28" si="36">+Z11/Z5</f>
+        <f t="shared" ref="Z28" si="37">+Z11/Z5</f>
         <v>0.34595451720833986</v>
       </c>
       <c r="AA28" s="7"/>
@@ -3167,27 +3237,27 @@
         <v>50</v>
       </c>
       <c r="C29" s="10" t="e">
-        <f t="shared" ref="C29:H29" si="37">+C14/C13</f>
+        <f t="shared" ref="C29:H29" si="38">+C14/C13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D29" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.15998244362758551</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.1608610404238455</v>
       </c>
       <c r="F29" s="10" t="e">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G29" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.1580135440180587</v>
       </c>
       <c r="H29" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.17717243496951354</v>
       </c>
       <c r="I29" s="10">
@@ -3195,59 +3265,62 @@
         <v>0.15697647864809319</v>
       </c>
       <c r="J29" s="10">
-        <f t="shared" ref="J29:N29" si="38">+J14/J13</f>
+        <f t="shared" ref="J29:N29" si="39">+J14/J13</f>
         <v>0.21530773120742483</v>
       </c>
       <c r="K29" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.16687596426393028</v>
       </c>
       <c r="L29" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.1812637137863066</v>
       </c>
       <c r="M29" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.17774740734785752</v>
       </c>
       <c r="N29" s="10" t="e">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O29" s="10">
-        <f t="shared" ref="O29" si="39">+O14/O13</f>
+        <f t="shared" ref="O29:P29" si="40">+O14/O13</f>
         <v>0.170881920780317</v>
       </c>
-      <c r="P29" s="10"/>
+      <c r="P29" s="10">
+        <f t="shared" si="40"/>
+        <v>0.17486589598691951</v>
+      </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
       <c r="S29" s="7"/>
       <c r="T29" s="10" t="e">
-        <f t="shared" ref="T29:Y29" si="40">+T14/T13</f>
+        <f t="shared" ref="T29:Y29" si="41">+T14/T13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U29" s="10" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V29" s="10" t="e">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W29" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.15023001502455038</v>
       </c>
       <c r="X29" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.15806682446193648</v>
       </c>
       <c r="Y29" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.18585773688401305</v>
       </c>
       <c r="Z29" s="10">
-        <f t="shared" ref="Z29" si="41">+Z14/Z13</f>
+        <f t="shared" ref="Z29" si="42">+Z14/Z13</f>
         <v>0.17651958162737483</v>
       </c>
       <c r="AA29" s="7"/>
